--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -1126,7 +1126,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128521447</v>
+        <v>128521797</v>
       </c>
       <c r="B6" t="n">
         <v>57685</v>
@@ -1162,14 +1162,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kyrkflon, Kyrkflon, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555466</v>
+        <v>555597</v>
       </c>
       <c r="R6" t="n">
-        <v>7045933</v>
+        <v>7045947</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1243,7 +1243,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128521797</v>
+        <v>128521447</v>
       </c>
       <c r="B7" t="n">
         <v>57685</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Kyrkflon, Kyrkflon, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555597</v>
+        <v>555466</v>
       </c>
       <c r="R7" t="n">
-        <v>7045947</v>
+        <v>7045933</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -2825,37 +2825,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128521772</v>
+        <v>128522142</v>
       </c>
       <c r="B21" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2864,10 +2865,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555589</v>
+        <v>555536</v>
       </c>
       <c r="R21" t="n">
-        <v>7045959</v>
+        <v>7046029</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2899,7 +2900,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2909,7 +2910,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,50 +2930,49 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128522142</v>
+        <v>128521772</v>
       </c>
       <c r="B22" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2976,10 +2981,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555536</v>
+        <v>555589</v>
       </c>
       <c r="R22" t="n">
-        <v>7046029</v>
+        <v>7045959</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3011,7 +3016,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3021,12 +3026,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3041,12 +3041,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -2256,50 +2256,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128521497</v>
+        <v>128521887</v>
       </c>
       <c r="B16" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kyrkflon, Kyrkflon, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555494</v>
+        <v>555580</v>
       </c>
       <c r="R16" t="n">
-        <v>7045947</v>
+        <v>7045983</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2331,7 +2330,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,12 +2340,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2361,19 +2355,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128522037</v>
+        <v>128521497</v>
       </c>
       <c r="B17" t="n">
         <v>57685</v>
@@ -2404,19 +2398,19 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Kyrkflon, Kyrkflon, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555545</v>
+        <v>555494</v>
       </c>
       <c r="R17" t="n">
-        <v>7046023</v>
+        <v>7045947</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2448,7 +2442,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2458,12 +2452,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2490,37 +2484,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128521887</v>
+        <v>128522037</v>
       </c>
       <c r="B18" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2529,10 +2524,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555580</v>
+        <v>555545</v>
       </c>
       <c r="R18" t="n">
-        <v>7045983</v>
+        <v>7046023</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2564,7 +2559,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2574,7 +2569,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,12 +2589,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128521580</v>
       </c>
       <c r="B2" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>128522099</v>
       </c>
       <c r="B3" t="n">
-        <v>57789</v>
+        <v>57793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>128521434</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>128521664</v>
       </c>
       <c r="B5" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128521797</v>
+        <v>128521447</v>
       </c>
       <c r="B6" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1162,14 +1162,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Kyrkflon, Kyrkflon, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555597</v>
+        <v>555466</v>
       </c>
       <c r="R6" t="n">
-        <v>7045947</v>
+        <v>7045933</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1243,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128521447</v>
+        <v>128521797</v>
       </c>
       <c r="B7" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kyrkflon, Kyrkflon, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555466</v>
+        <v>555597</v>
       </c>
       <c r="R7" t="n">
-        <v>7045933</v>
+        <v>7045947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1363,7 +1363,7 @@
         <v>128521610</v>
       </c>
       <c r="B8" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>128522112</v>
       </c>
       <c r="B9" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>128522092</v>
       </c>
       <c r="B10" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>128521953</v>
       </c>
       <c r="B11" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>128521663</v>
       </c>
       <c r="B12" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>128521719</v>
       </c>
       <c r="B13" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>128521629</v>
       </c>
       <c r="B14" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>128521728</v>
       </c>
       <c r="B15" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,37 +2256,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128521887</v>
+        <v>128522037</v>
       </c>
       <c r="B16" t="n">
-        <v>98571</v>
+        <v>57689</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2295,10 +2296,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555580</v>
+        <v>555545</v>
       </c>
       <c r="R16" t="n">
-        <v>7045983</v>
+        <v>7046023</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2330,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2340,7 +2341,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,12 +2361,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2370,7 +2376,7 @@
         <v>128521497</v>
       </c>
       <c r="B17" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,38 +2490,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128522037</v>
+        <v>128521887</v>
       </c>
       <c r="B18" t="n">
-        <v>57685</v>
+        <v>98579</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2524,10 +2529,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555545</v>
+        <v>555580</v>
       </c>
       <c r="R18" t="n">
-        <v>7046023</v>
+        <v>7045983</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2559,7 +2564,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2569,12 +2574,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,12 +2589,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2604,7 +2604,7 @@
         <v>128521908</v>
       </c>
       <c r="B19" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>128521539</v>
       </c>
       <c r="B20" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>128522142</v>
       </c>
       <c r="B21" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128521772</v>
       </c>
       <c r="B22" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128521580</v>
+        <v>128522099</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
+        <v>57793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,10 +703,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555515</v>
+        <v>555541</v>
       </c>
       <c r="R2" t="n">
-        <v>7045921</v>
+        <v>7046009</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,39 +779,39 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128522099</v>
+        <v>128521580</v>
       </c>
       <c r="B3" t="n">
-        <v>57793</v>
+        <v>57689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -820,14 +819,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555541</v>
+        <v>555515</v>
       </c>
       <c r="R3" t="n">
-        <v>7046009</v>
+        <v>7045921</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,12 +896,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1018,7 +1018,7 @@
         <v>128521664</v>
       </c>
       <c r="B5" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128521447</v>
+        <v>128521797</v>
       </c>
       <c r="B6" t="n">
         <v>57689</v>
@@ -1162,14 +1162,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kyrkflon, Kyrkflon, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555466</v>
+        <v>555597</v>
       </c>
       <c r="R6" t="n">
-        <v>7045933</v>
+        <v>7045947</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1243,7 +1243,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128521797</v>
+        <v>128521447</v>
       </c>
       <c r="B7" t="n">
         <v>57689</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Kyrkflon, Kyrkflon, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555597</v>
+        <v>555466</v>
       </c>
       <c r="R7" t="n">
-        <v>7045947</v>
+        <v>7045933</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1363,7 +1363,7 @@
         <v>128521610</v>
       </c>
       <c r="B8" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>128521719</v>
       </c>
       <c r="B13" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2256,38 +2256,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128522037</v>
+        <v>128521887</v>
       </c>
       <c r="B16" t="n">
-        <v>57689</v>
+        <v>98585</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2296,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555545</v>
+        <v>555580</v>
       </c>
       <c r="R16" t="n">
-        <v>7046023</v>
+        <v>7045983</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2331,7 +2330,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,12 +2340,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2361,12 +2355,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2490,37 +2484,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128521887</v>
+        <v>128522037</v>
       </c>
       <c r="B18" t="n">
-        <v>98579</v>
+        <v>57689</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2529,10 +2524,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555580</v>
+        <v>555545</v>
       </c>
       <c r="R18" t="n">
-        <v>7045983</v>
+        <v>7046023</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2564,7 +2559,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2574,7 +2569,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,12 +2589,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2945,7 +2945,7 @@
         <v>128521772</v>
       </c>
       <c r="B22" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128522099</v>
+        <v>128521580</v>
       </c>
       <c r="B2" t="n">
-        <v>57793</v>
+        <v>57689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,14 +703,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555541</v>
+        <v>555515</v>
       </c>
       <c r="R2" t="n">
-        <v>7046009</v>
+        <v>7045921</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,39 +780,39 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128521580</v>
+        <v>128522099</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>57793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,10 +820,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555515</v>
+        <v>555541</v>
       </c>
       <c r="R3" t="n">
-        <v>7045921</v>
+        <v>7046009</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,12 +896,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>128521434</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>128521664</v>
       </c>
       <c r="B5" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>128521610</v>
       </c>
       <c r="B8" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>128521953</v>
       </c>
       <c r="B11" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>128521719</v>
       </c>
       <c r="B13" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>128521728</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,49 +2256,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128521887</v>
+        <v>128521497</v>
       </c>
       <c r="B16" t="n">
-        <v>98585</v>
+        <v>57689</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Kyrkflon, Kyrkflon, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555580</v>
+        <v>555494</v>
       </c>
       <c r="R16" t="n">
-        <v>7045983</v>
+        <v>7045947</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2330,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2340,7 +2341,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,19 +2361,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128521497</v>
+        <v>128522037</v>
       </c>
       <c r="B17" t="n">
         <v>57689</v>
@@ -2398,19 +2404,19 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kyrkflon, Kyrkflon, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555494</v>
+        <v>555545</v>
       </c>
       <c r="R17" t="n">
-        <v>7045947</v>
+        <v>7046023</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2442,7 +2448,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2452,12 +2458,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2484,38 +2490,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128522037</v>
+        <v>128521887</v>
       </c>
       <c r="B18" t="n">
-        <v>57689</v>
+        <v>98588</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2524,10 +2529,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555545</v>
+        <v>555580</v>
       </c>
       <c r="R18" t="n">
-        <v>7046023</v>
+        <v>7045983</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2559,7 +2564,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2569,12 +2574,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,12 +2589,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2604,7 +2604,7 @@
         <v>128521908</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2825,38 +2825,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128522142</v>
+        <v>128521772</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>98588</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2865,10 +2864,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555536</v>
+        <v>555589</v>
       </c>
       <c r="R21" t="n">
-        <v>7046029</v>
+        <v>7045959</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2900,7 +2899,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2910,12 +2909,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2930,49 +2924,50 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128521772</v>
+        <v>128522142</v>
       </c>
       <c r="B22" t="n">
-        <v>98585</v>
+        <v>57689</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2981,10 +2976,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555589</v>
+        <v>555536</v>
       </c>
       <c r="R22" t="n">
-        <v>7045959</v>
+        <v>7046029</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3016,7 +3011,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3026,7 +3021,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3041,12 +3041,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>128521664</v>
       </c>
       <c r="B5" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>128521887</v>
       </c>
       <c r="B18" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2825,37 +2825,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128521772</v>
+        <v>128522142</v>
       </c>
       <c r="B21" t="n">
-        <v>98588</v>
+        <v>57689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2864,10 +2865,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555589</v>
+        <v>555536</v>
       </c>
       <c r="R21" t="n">
-        <v>7045959</v>
+        <v>7046029</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2899,7 +2900,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2909,7 +2910,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,50 +2930,49 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128522142</v>
+        <v>128521772</v>
       </c>
       <c r="B22" t="n">
-        <v>57689</v>
+        <v>98591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2976,10 +2981,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555536</v>
+        <v>555589</v>
       </c>
       <c r="R22" t="n">
-        <v>7046029</v>
+        <v>7045959</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3011,7 +3016,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3021,12 +3026,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3041,12 +3041,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>128521664</v>
       </c>
       <c r="B5" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128521797</v>
+        <v>128521447</v>
       </c>
       <c r="B6" t="n">
         <v>57689</v>
@@ -1162,14 +1162,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Kyrkflon, Kyrkflon, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555597</v>
+        <v>555466</v>
       </c>
       <c r="R6" t="n">
-        <v>7045947</v>
+        <v>7045933</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1243,7 +1243,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128521447</v>
+        <v>128521797</v>
       </c>
       <c r="B7" t="n">
         <v>57689</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kyrkflon, Kyrkflon, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555466</v>
+        <v>555597</v>
       </c>
       <c r="R7" t="n">
-        <v>7045933</v>
+        <v>7045947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1363,7 +1363,7 @@
         <v>128521610</v>
       </c>
       <c r="B8" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>128521719</v>
       </c>
       <c r="B13" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128521497</v>
+        <v>128522037</v>
       </c>
       <c r="B16" t="n">
         <v>57689</v>
@@ -2287,19 +2287,19 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kyrkflon, Kyrkflon, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555494</v>
+        <v>555545</v>
       </c>
       <c r="R16" t="n">
-        <v>7045947</v>
+        <v>7046023</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2373,7 +2373,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128522037</v>
+        <v>128521497</v>
       </c>
       <c r="B17" t="n">
         <v>57689</v>
@@ -2404,19 +2404,19 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Kyrkflon, Kyrkflon, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555545</v>
+        <v>555494</v>
       </c>
       <c r="R17" t="n">
-        <v>7046023</v>
+        <v>7045947</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2493,7 +2493,7 @@
         <v>128521887</v>
       </c>
       <c r="B18" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128521772</v>
       </c>
       <c r="B22" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128521580</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>128522099</v>
       </c>
       <c r="B3" t="n">
-        <v>57793</v>
+        <v>57820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>128521434</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>128521664</v>
       </c>
       <c r="B5" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>128521447</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>128521797</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>128521610</v>
       </c>
       <c r="B8" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>128522112</v>
       </c>
       <c r="B9" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>128522092</v>
       </c>
       <c r="B10" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>128521953</v>
       </c>
       <c r="B11" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>128521663</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>128521719</v>
       </c>
       <c r="B13" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>128521629</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>128521728</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128522037</v>
+        <v>128521497</v>
       </c>
       <c r="B16" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2287,19 +2287,19 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Kyrkflon, Kyrkflon, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555545</v>
+        <v>555494</v>
       </c>
       <c r="R16" t="n">
-        <v>7046023</v>
+        <v>7045947</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2373,10 +2373,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128521497</v>
+        <v>128522037</v>
       </c>
       <c r="B17" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2404,19 +2404,19 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kyrkflon, Kyrkflon, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555494</v>
+        <v>555545</v>
       </c>
       <c r="R17" t="n">
-        <v>7045947</v>
+        <v>7046023</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2493,7 +2493,7 @@
         <v>128521887</v>
       </c>
       <c r="B18" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128521908</v>
+        <v>128521539</v>
       </c>
       <c r="B19" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,34 +2612,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Kyrkflon, Kyrkflon, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555577</v>
+        <v>555510</v>
       </c>
       <c r="R19" t="n">
-        <v>7045995</v>
+        <v>7045927</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2671,7 +2676,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2681,7 +2686,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,22 +2706,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128521539</v>
+        <v>128521908</v>
       </c>
       <c r="B20" t="n">
-        <v>57689</v>
+        <v>79116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2719,39 +2729,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kyrkflon, Kyrkflon, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555510</v>
+        <v>555577</v>
       </c>
       <c r="R20" t="n">
-        <v>7045927</v>
+        <v>7045995</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2783,7 +2788,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2793,12 +2798,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,12 +2813,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2828,7 +2828,7 @@
         <v>128522142</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128521772</v>
       </c>
       <c r="B22" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -2601,10 +2601,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128521539</v>
+        <v>128521908</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,39 +2612,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kyrkflon, Kyrkflon, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555510</v>
+        <v>555577</v>
       </c>
       <c r="R19" t="n">
-        <v>7045927</v>
+        <v>7045995</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,7 +2671,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2686,12 +2681,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,22 +2696,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128521908</v>
+        <v>128521539</v>
       </c>
       <c r="B20" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,34 +2719,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Kyrkflon, Kyrkflon, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555577</v>
+        <v>555510</v>
       </c>
       <c r="R20" t="n">
-        <v>7045995</v>
+        <v>7045927</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2788,7 +2783,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2798,7 +2793,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,12 +2813,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>128521434</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>128521664</v>
       </c>
       <c r="B5" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>128521610</v>
       </c>
       <c r="B8" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>128521953</v>
       </c>
       <c r="B11" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>128521719</v>
       </c>
       <c r="B13" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>128521728</v>
       </c>
       <c r="B15" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>128521887</v>
       </c>
       <c r="B18" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>128521908</v>
       </c>
       <c r="B19" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128521772</v>
       </c>
       <c r="B22" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>128521664</v>
       </c>
       <c r="B5" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128521447</v>
+        <v>128521797</v>
       </c>
       <c r="B6" t="n">
         <v>57716</v>
@@ -1162,14 +1162,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kyrkflon, Kyrkflon, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555466</v>
+        <v>555597</v>
       </c>
       <c r="R6" t="n">
-        <v>7045933</v>
+        <v>7045947</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1243,7 +1243,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128521797</v>
+        <v>128521447</v>
       </c>
       <c r="B7" t="n">
         <v>57716</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Kyrkflon, Kyrkflon, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555597</v>
+        <v>555466</v>
       </c>
       <c r="R7" t="n">
-        <v>7045947</v>
+        <v>7045933</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1363,7 +1363,7 @@
         <v>128521610</v>
       </c>
       <c r="B8" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>128521719</v>
       </c>
       <c r="B13" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>128521887</v>
       </c>
       <c r="B18" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128521772</v>
       </c>
       <c r="B22" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128521580</v>
+        <v>128522099</v>
       </c>
       <c r="B2" t="n">
-        <v>57716</v>
+        <v>57820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,10 +703,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555515</v>
+        <v>555541</v>
       </c>
       <c r="R2" t="n">
-        <v>7045921</v>
+        <v>7046009</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,39 +779,39 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128522099</v>
+        <v>128521580</v>
       </c>
       <c r="B3" t="n">
-        <v>57820</v>
+        <v>57716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -820,14 +819,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555541</v>
+        <v>555515</v>
       </c>
       <c r="R3" t="n">
-        <v>7046009</v>
+        <v>7045921</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,12 +896,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128521797</v>
+        <v>128521447</v>
       </c>
       <c r="B6" t="n">
         <v>57716</v>
@@ -1162,14 +1162,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Kyrkflon, Kyrkflon, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555597</v>
+        <v>555466</v>
       </c>
       <c r="R6" t="n">
-        <v>7045947</v>
+        <v>7045933</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1243,7 +1243,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128521447</v>
+        <v>128521797</v>
       </c>
       <c r="B7" t="n">
         <v>57716</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kyrkflon, Kyrkflon, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555466</v>
+        <v>555597</v>
       </c>
       <c r="R7" t="n">
-        <v>7045933</v>
+        <v>7045947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -2601,10 +2601,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128521908</v>
+        <v>128521539</v>
       </c>
       <c r="B19" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,34 +2612,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Kyrkflon, Kyrkflon, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555577</v>
+        <v>555510</v>
       </c>
       <c r="R19" t="n">
-        <v>7045995</v>
+        <v>7045927</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2671,7 +2676,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2681,7 +2686,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,22 +2706,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128521539</v>
+        <v>128521908</v>
       </c>
       <c r="B20" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2719,39 +2729,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kyrkflon, Kyrkflon, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555510</v>
+        <v>555577</v>
       </c>
       <c r="R20" t="n">
-        <v>7045927</v>
+        <v>7045995</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2783,7 +2788,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2793,12 +2798,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,12 +2813,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -2256,50 +2256,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128521497</v>
+        <v>128521887</v>
       </c>
       <c r="B16" t="n">
-        <v>57716</v>
+        <v>98632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kyrkflon, Kyrkflon, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555494</v>
+        <v>555580</v>
       </c>
       <c r="R16" t="n">
-        <v>7045947</v>
+        <v>7045983</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2331,7 +2330,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,12 +2340,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2361,19 +2355,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128522037</v>
+        <v>128521497</v>
       </c>
       <c r="B17" t="n">
         <v>57716</v>
@@ -2404,19 +2398,19 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Kyrkflon, Kyrkflon, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555545</v>
+        <v>555494</v>
       </c>
       <c r="R17" t="n">
-        <v>7046023</v>
+        <v>7045947</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2448,7 +2442,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2458,12 +2452,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2490,37 +2484,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128521887</v>
+        <v>128522037</v>
       </c>
       <c r="B18" t="n">
-        <v>98632</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2529,10 +2524,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555580</v>
+        <v>555545</v>
       </c>
       <c r="R18" t="n">
-        <v>7045983</v>
+        <v>7046023</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2564,7 +2559,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2574,7 +2569,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,12 +2589,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128522099</v>
       </c>
       <c r="B2" t="n">
-        <v>57820</v>
+        <v>57824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>128521580</v>
       </c>
       <c r="B3" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>128521434</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>128521664</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>128521447</v>
       </c>
       <c r="B6" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>128521797</v>
       </c>
       <c r="B7" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>128521610</v>
       </c>
       <c r="B8" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>128522112</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>128522092</v>
       </c>
       <c r="B10" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>128521953</v>
       </c>
       <c r="B11" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>128521663</v>
       </c>
       <c r="B12" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>128521719</v>
       </c>
       <c r="B13" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>128521629</v>
       </c>
       <c r="B14" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>128521728</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>128521887</v>
       </c>
       <c r="B16" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>128521497</v>
       </c>
       <c r="B17" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>128522037</v>
       </c>
       <c r="B18" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>128521539</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>128521908</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>128522142</v>
       </c>
       <c r="B21" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128521772</v>
       </c>
       <c r="B22" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128522099</v>
+        <v>128521580</v>
       </c>
       <c r="B2" t="n">
-        <v>57824</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,14 +703,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555541</v>
+        <v>555515</v>
       </c>
       <c r="R2" t="n">
-        <v>7046009</v>
+        <v>7045921</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,39 +780,39 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128521580</v>
+        <v>128522099</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57824</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,10 +820,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555515</v>
+        <v>555541</v>
       </c>
       <c r="R3" t="n">
-        <v>7045921</v>
+        <v>7046009</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,12 +896,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -2256,49 +2256,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128521887</v>
+        <v>128521497</v>
       </c>
       <c r="B16" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Kyrkflon, Kyrkflon, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555580</v>
+        <v>555494</v>
       </c>
       <c r="R16" t="n">
-        <v>7045983</v>
+        <v>7045947</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2330,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2340,7 +2341,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,19 +2361,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128521497</v>
+        <v>128522037</v>
       </c>
       <c r="B17" t="n">
         <v>57720</v>
@@ -2398,19 +2404,19 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kyrkflon, Kyrkflon, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555494</v>
+        <v>555545</v>
       </c>
       <c r="R17" t="n">
-        <v>7045947</v>
+        <v>7046023</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2442,7 +2448,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2452,12 +2458,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2484,38 +2490,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128522037</v>
+        <v>128521887</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>98636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2524,10 +2529,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555545</v>
+        <v>555580</v>
       </c>
       <c r="R18" t="n">
-        <v>7046023</v>
+        <v>7045983</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2559,7 +2564,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2569,12 +2574,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,22 +2589,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128521539</v>
+        <v>128521908</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,39 +2612,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kyrkflon, Kyrkflon, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555510</v>
+        <v>555577</v>
       </c>
       <c r="R19" t="n">
-        <v>7045927</v>
+        <v>7045995</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,7 +2671,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2686,12 +2681,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,22 +2696,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128521908</v>
+        <v>128521539</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2729,34 +2719,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Kyrkflon, Kyrkflon, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555577</v>
+        <v>555510</v>
       </c>
       <c r="R20" t="n">
-        <v>7045995</v>
+        <v>7045927</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2788,7 +2783,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2798,7 +2793,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,50 +2813,49 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128522142</v>
+        <v>128521772</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>98636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2865,10 +2864,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555536</v>
+        <v>555589</v>
       </c>
       <c r="R21" t="n">
-        <v>7046029</v>
+        <v>7045959</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2900,7 +2899,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2910,12 +2909,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2930,49 +2924,50 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128521772</v>
+        <v>128522142</v>
       </c>
       <c r="B22" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2981,10 +2976,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555589</v>
+        <v>555536</v>
       </c>
       <c r="R22" t="n">
-        <v>7045959</v>
+        <v>7046029</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3016,7 +3011,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3026,7 +3021,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3041,12 +3041,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128521580</v>
+        <v>128522099</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,10 +703,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555515</v>
+        <v>555541</v>
       </c>
       <c r="R2" t="n">
-        <v>7045921</v>
+        <v>7046009</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,39 +779,39 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128522099</v>
+        <v>128521580</v>
       </c>
       <c r="B3" t="n">
-        <v>57824</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -820,14 +819,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555541</v>
+        <v>555515</v>
       </c>
       <c r="R3" t="n">
-        <v>7046009</v>
+        <v>7045921</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,12 +896,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128521447</v>
+        <v>128521797</v>
       </c>
       <c r="B6" t="n">
         <v>57720</v>
@@ -1162,14 +1162,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kyrkflon, Kyrkflon, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555466</v>
+        <v>555597</v>
       </c>
       <c r="R6" t="n">
-        <v>7045933</v>
+        <v>7045947</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1243,7 +1243,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128521797</v>
+        <v>128521447</v>
       </c>
       <c r="B7" t="n">
         <v>57720</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Kyrkflon, Kyrkflon, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555597</v>
+        <v>555466</v>
       </c>
       <c r="R7" t="n">
-        <v>7045947</v>
+        <v>7045933</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1701,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128521953</v>
+        <v>128521663</v>
       </c>
       <c r="B11" t="n">
-        <v>80229</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,34 +1712,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555585</v>
+        <v>555571</v>
       </c>
       <c r="R11" t="n">
-        <v>7046028</v>
+        <v>7045891</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1786,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,10 +1818,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128521663</v>
+        <v>128521953</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>80229</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,39 +1829,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555571</v>
+        <v>555585</v>
       </c>
       <c r="R12" t="n">
-        <v>7045891</v>
+        <v>7046028</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1888,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,12 +1898,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2825,37 +2825,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128521772</v>
+        <v>128522142</v>
       </c>
       <c r="B21" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2864,10 +2865,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555589</v>
+        <v>555536</v>
       </c>
       <c r="R21" t="n">
-        <v>7045959</v>
+        <v>7046029</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2899,7 +2900,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2909,7 +2910,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,50 +2930,49 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128522142</v>
+        <v>128521772</v>
       </c>
       <c r="B22" t="n">
-        <v>57720</v>
+        <v>98636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2976,10 +2981,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555536</v>
+        <v>555589</v>
       </c>
       <c r="R22" t="n">
-        <v>7046029</v>
+        <v>7045959</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3011,7 +3016,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3021,12 +3026,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3041,12 +3041,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128522099</v>
+        <v>128521580</v>
       </c>
       <c r="B2" t="n">
-        <v>57824</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,14 +703,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555541</v>
+        <v>555515</v>
       </c>
       <c r="R2" t="n">
-        <v>7046009</v>
+        <v>7045921</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,39 +780,39 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128521580</v>
+        <v>128522099</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,10 +820,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555515</v>
+        <v>555541</v>
       </c>
       <c r="R3" t="n">
-        <v>7045921</v>
+        <v>7046009</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:53</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,12 +896,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -911,7 +911,7 @@
         <v>128521434</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>128521664</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128521797</v>
+        <v>128521447</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1162,14 +1162,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Kyrkflon, Kyrkflon, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555597</v>
+        <v>555466</v>
       </c>
       <c r="R6" t="n">
-        <v>7045947</v>
+        <v>7045933</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1243,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128521447</v>
+        <v>128521797</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kyrkflon, Kyrkflon, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555466</v>
+        <v>555597</v>
       </c>
       <c r="R7" t="n">
-        <v>7045933</v>
+        <v>7045947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1363,7 +1363,7 @@
         <v>128521610</v>
       </c>
       <c r="B8" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>128522112</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>128522092</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128521663</v>
+        <v>128521953</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>80134</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,39 +1712,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555571</v>
+        <v>555585</v>
       </c>
       <c r="R11" t="n">
-        <v>7045891</v>
+        <v>7046028</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,12 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128521953</v>
+        <v>128521663</v>
       </c>
       <c r="B12" t="n">
-        <v>80229</v>
+        <v>57723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,34 +1819,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555585</v>
+        <v>555571</v>
       </c>
       <c r="R12" t="n">
-        <v>7046028</v>
+        <v>7045891</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1888,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1898,7 +1893,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,7 +1928,7 @@
         <v>128521719</v>
       </c>
       <c r="B13" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>128521629</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>128521728</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,50 +2256,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128521497</v>
+        <v>128521887</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>98643</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kyrkflon, Kyrkflon, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555494</v>
+        <v>555580</v>
       </c>
       <c r="R16" t="n">
-        <v>7045947</v>
+        <v>7045983</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2331,7 +2330,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,12 +2340,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2361,22 +2355,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128522037</v>
+        <v>128521497</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2404,19 +2398,19 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Kyrkflon, Kyrkflon, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>555545</v>
+        <v>555494</v>
       </c>
       <c r="R17" t="n">
-        <v>7046023</v>
+        <v>7045947</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2448,7 +2442,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2458,12 +2452,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2490,37 +2484,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128521887</v>
+        <v>128522037</v>
       </c>
       <c r="B18" t="n">
-        <v>98636</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2529,10 +2524,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>555580</v>
+        <v>555545</v>
       </c>
       <c r="R18" t="n">
-        <v>7045983</v>
+        <v>7046023</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2564,7 +2559,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2574,7 +2569,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,22 +2589,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128521908</v>
+        <v>128521539</v>
       </c>
       <c r="B19" t="n">
-        <v>79124</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,34 +2612,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Kyrkflon, Kyrkflon, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>555577</v>
+        <v>555510</v>
       </c>
       <c r="R19" t="n">
-        <v>7045995</v>
+        <v>7045927</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2671,7 +2676,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2681,7 +2686,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,22 +2706,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128521539</v>
+        <v>128521908</v>
       </c>
       <c r="B20" t="n">
-        <v>57720</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2719,39 +2729,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kyrkflon, Kyrkflon, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>555510</v>
+        <v>555577</v>
       </c>
       <c r="R20" t="n">
-        <v>7045927</v>
+        <v>7045995</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2783,7 +2788,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2793,12 +2798,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:51</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,12 +2813,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2828,7 +2828,7 @@
         <v>128522142</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>128521772</v>
       </c>
       <c r="B22" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>128521434</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>128521664</v>
       </c>
       <c r="B5" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>128521610</v>
       </c>
       <c r="B8" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1701,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128521953</v>
+        <v>128521663</v>
       </c>
       <c r="B11" t="n">
-        <v>80134</v>
+        <v>57723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,34 +1712,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555585</v>
+        <v>555571</v>
       </c>
       <c r="R11" t="n">
-        <v>7046028</v>
+        <v>7045891</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1786,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,10 +1818,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128521663</v>
+        <v>128521953</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>80139</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1819,39 +1829,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555571</v>
+        <v>555585</v>
       </c>
       <c r="R12" t="n">
-        <v>7045891</v>
+        <v>7046028</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1888,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,12 +1898,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,7 +1928,7 @@
         <v>128521719</v>
       </c>
       <c r="B13" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>128521728</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>128521887</v>
       </c>
       <c r="B18" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>128521908</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2825,37 +2825,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128521772</v>
+        <v>128522142</v>
       </c>
       <c r="B21" t="n">
-        <v>98646</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2864,10 +2865,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555589</v>
+        <v>555536</v>
       </c>
       <c r="R21" t="n">
-        <v>7045959</v>
+        <v>7046029</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2899,7 +2900,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2909,7 +2910,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,50 +2930,49 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128522142</v>
+        <v>128521772</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>98651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2976,10 +2981,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555536</v>
+        <v>555589</v>
       </c>
       <c r="R22" t="n">
-        <v>7046029</v>
+        <v>7045959</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3011,7 +3016,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3021,12 +3026,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3041,12 +3041,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -1701,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128521663</v>
+        <v>128521953</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>80139</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,39 +1712,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555571</v>
+        <v>555585</v>
       </c>
       <c r="R11" t="n">
-        <v>7045891</v>
+        <v>7046028</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,12 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,10 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128521953</v>
+        <v>128521663</v>
       </c>
       <c r="B12" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,34 +1819,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555585</v>
+        <v>555571</v>
       </c>
       <c r="R12" t="n">
-        <v>7046028</v>
+        <v>7045891</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1888,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1898,7 +1893,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2825,38 +2825,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128522142</v>
+        <v>128521772</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>98651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2865,10 +2864,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>555536</v>
+        <v>555589</v>
       </c>
       <c r="R21" t="n">
-        <v>7046029</v>
+        <v>7045959</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2900,7 +2899,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2910,12 +2909,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2930,49 +2924,50 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128521772</v>
+        <v>128522142</v>
       </c>
       <c r="B22" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2981,10 +2976,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>555589</v>
+        <v>555536</v>
       </c>
       <c r="R22" t="n">
-        <v>7045959</v>
+        <v>7046029</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3016,7 +3011,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3026,7 +3021,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3041,12 +3041,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3051,6 +3051,783 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129298314</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80145</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>555754</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7045811</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129298193</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98669</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>555771</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7045828</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129298243</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98669</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>555757</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7045831</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129298267</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>555754</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7045827</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129298152</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>555792</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7045804</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129298285</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91818</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>658</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>555760</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7045817</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129298204</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>555763</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7045835</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3163,7 +3163,7 @@
         <v>129298193</v>
       </c>
       <c r="B24" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129298243</v>
       </c>
       <c r="B25" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>129298285</v>
       </c>
       <c r="B28" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3056,7 +3056,7 @@
         <v>129298314</v>
       </c>
       <c r="B23" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>129298193</v>
       </c>
       <c r="B24" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129298243</v>
       </c>
       <c r="B25" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>129298267</v>
       </c>
       <c r="B26" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>129298152</v>
       </c>
       <c r="B27" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>129298285</v>
       </c>
       <c r="B28" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>129298204</v>
       </c>
       <c r="B29" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3163,7 +3163,7 @@
         <v>129298193</v>
       </c>
       <c r="B24" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129298243</v>
       </c>
       <c r="B25" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>129298285</v>
       </c>
       <c r="B28" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3163,7 +3163,7 @@
         <v>129298193</v>
       </c>
       <c r="B24" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129298243</v>
       </c>
       <c r="B25" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>129298285</v>
       </c>
       <c r="B28" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3163,7 +3163,7 @@
         <v>129298193</v>
       </c>
       <c r="B24" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129298243</v>
       </c>
       <c r="B25" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3616,10 +3616,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298285</v>
+        <v>129298204</v>
       </c>
       <c r="B28" t="n">
-        <v>91838</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3627,21 +3627,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555760</v>
+        <v>555763</v>
       </c>
       <c r="R28" t="n">
-        <v>7045817</v>
+        <v>7045835</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3723,10 +3723,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298204</v>
+        <v>129298285</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>91838</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3734,21 +3734,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555763</v>
+        <v>555760</v>
       </c>
       <c r="R29" t="n">
-        <v>7045835</v>
+        <v>7045817</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3056,7 +3056,7 @@
         <v>129298314</v>
       </c>
       <c r="B23" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>129298193</v>
       </c>
       <c r="B24" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129298243</v>
       </c>
       <c r="B25" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3616,10 +3616,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298204</v>
+        <v>129298285</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>91841</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3627,21 +3627,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555763</v>
+        <v>555760</v>
       </c>
       <c r="R28" t="n">
-        <v>7045835</v>
+        <v>7045817</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3723,10 +3723,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298285</v>
+        <v>129298204</v>
       </c>
       <c r="B29" t="n">
-        <v>91838</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3734,21 +3734,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555760</v>
+        <v>555763</v>
       </c>
       <c r="R29" t="n">
-        <v>7045817</v>
+        <v>7045835</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3056,7 +3056,7 @@
         <v>129298314</v>
       </c>
       <c r="B23" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>129298193</v>
       </c>
       <c r="B24" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129298243</v>
       </c>
       <c r="B25" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>129298285</v>
       </c>
       <c r="B28" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>129298204</v>
       </c>
       <c r="B29" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3163,7 +3163,7 @@
         <v>129298193</v>
       </c>
       <c r="B24" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129298243</v>
       </c>
       <c r="B25" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>129298285</v>
       </c>
       <c r="B28" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3163,7 +3163,7 @@
         <v>129298193</v>
       </c>
       <c r="B24" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129298243</v>
       </c>
       <c r="B25" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3616,10 +3616,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298285</v>
+        <v>129298204</v>
       </c>
       <c r="B28" t="n">
-        <v>91847</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3627,21 +3627,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555760</v>
+        <v>555763</v>
       </c>
       <c r="R28" t="n">
-        <v>7045817</v>
+        <v>7045835</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3723,10 +3723,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298204</v>
+        <v>129298285</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>91848</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3734,21 +3734,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555763</v>
+        <v>555760</v>
       </c>
       <c r="R29" t="n">
-        <v>7045835</v>
+        <v>7045817</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3382,7 +3382,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298267</v>
+        <v>129298152</v>
       </c>
       <c r="B26" t="n">
         <v>57727</v>
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555754</v>
+        <v>555792</v>
       </c>
       <c r="R26" t="n">
-        <v>7045827</v>
+        <v>7045804</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3499,7 +3499,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298152</v>
+        <v>129298267</v>
       </c>
       <c r="B27" t="n">
         <v>57727</v>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555792</v>
+        <v>555754</v>
       </c>
       <c r="R27" t="n">
-        <v>7045804</v>
+        <v>7045827</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3382,7 +3382,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129298152</v>
+        <v>129298267</v>
       </c>
       <c r="B26" t="n">
         <v>57727</v>
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555792</v>
+        <v>555754</v>
       </c>
       <c r="R26" t="n">
-        <v>7045804</v>
+        <v>7045827</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3499,7 +3499,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129298267</v>
+        <v>129298152</v>
       </c>
       <c r="B27" t="n">
         <v>57727</v>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>555754</v>
+        <v>555792</v>
       </c>
       <c r="R27" t="n">
-        <v>7045827</v>
+        <v>7045804</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3163,7 +3163,7 @@
         <v>129298193</v>
       </c>
       <c r="B24" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129298243</v>
       </c>
       <c r="B25" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3616,10 +3616,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298204</v>
+        <v>129298285</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>91851</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3627,21 +3627,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555763</v>
+        <v>555760</v>
       </c>
       <c r="R28" t="n">
-        <v>7045835</v>
+        <v>7045817</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3723,10 +3723,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298285</v>
+        <v>129298204</v>
       </c>
       <c r="B29" t="n">
-        <v>91848</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3734,21 +3734,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555760</v>
+        <v>555763</v>
       </c>
       <c r="R29" t="n">
-        <v>7045817</v>
+        <v>7045835</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3830,32 +3830,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129602332</v>
+        <v>129601128</v>
       </c>
       <c r="B30" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3865,13 +3865,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555835</v>
+        <v>555698</v>
       </c>
       <c r="R30" t="n">
-        <v>7045850</v>
+        <v>7046187</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3898,19 +3898,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3925,22 +3915,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129602543</v>
+        <v>129602332</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3948,39 +3938,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555769</v>
+        <v>555835</v>
       </c>
       <c r="R31" t="n">
-        <v>7045881</v>
+        <v>7045850</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4012,7 +3997,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4022,12 +4007,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4042,57 +4022,61 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129601128</v>
+        <v>129602260</v>
       </c>
       <c r="B32" t="n">
-        <v>80178</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555698</v>
+        <v>555747</v>
       </c>
       <c r="R32" t="n">
-        <v>7046187</v>
+        <v>7045963</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4151,7 +4135,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129602260</v>
+        <v>129600015</v>
       </c>
       <c r="B33" t="n">
         <v>98727</v>
@@ -4181,22 +4165,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555747</v>
+        <v>555553</v>
       </c>
       <c r="R33" t="n">
-        <v>7045963</v>
+        <v>7046074</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4223,9 +4212,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4240,69 +4239,65 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129600015</v>
+        <v>129602543</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555553</v>
+        <v>555769</v>
       </c>
       <c r="R34" t="n">
-        <v>7046074</v>
+        <v>7045881</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4331,7 +4326,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4341,7 +4336,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4356,19 +4356,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129602548</v>
+        <v>129601775</v>
       </c>
       <c r="B35" t="n">
         <v>98727</v>
@@ -4398,12 +4398,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4412,13 +4407,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555770</v>
+        <v>555746</v>
       </c>
       <c r="R35" t="n">
-        <v>7045888</v>
+        <v>7046137</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4447,7 +4442,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4457,7 +4452,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4472,19 +4467,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129601775</v>
+        <v>129602548</v>
       </c>
       <c r="B36" t="n">
         <v>98727</v>
@@ -4514,7 +4509,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4523,13 +4523,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555746</v>
+        <v>555770</v>
       </c>
       <c r="R36" t="n">
-        <v>7046137</v>
+        <v>7045888</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4583,12 +4583,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4692,10 +4692,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129602638</v>
+        <v>129601909</v>
       </c>
       <c r="B38" t="n">
-        <v>91851</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4703,37 +4703,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555826</v>
+        <v>555726</v>
       </c>
       <c r="R38" t="n">
-        <v>7045880</v>
+        <v>7046072</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4760,9 +4765,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4777,74 +4797,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129602085</v>
+        <v>129601485</v>
       </c>
       <c r="B39" t="n">
-        <v>57887</v>
+        <v>80178</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555725</v>
+        <v>555696</v>
       </c>
       <c r="R39" t="n">
-        <v>7046023</v>
+        <v>7046160</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4871,19 +4877,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4898,44 +4894,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129601485</v>
+        <v>129602219</v>
       </c>
       <c r="B40" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4945,10 +4941,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555696</v>
+        <v>555697</v>
       </c>
       <c r="R40" t="n">
-        <v>7046160</v>
+        <v>7045963</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5007,10 +5003,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129602219</v>
+        <v>129602638</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>91851</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5018,21 +5014,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5042,10 +5038,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555697</v>
+        <v>555826</v>
       </c>
       <c r="R41" t="n">
-        <v>7045963</v>
+        <v>7045880</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5104,10 +5100,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129601909</v>
+        <v>129601980</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5115,42 +5111,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>555726</v>
+        <v>555724</v>
       </c>
       <c r="R42" t="n">
-        <v>7046072</v>
+        <v>7046089</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5177,24 +5168,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5209,22 +5185,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129601980</v>
+        <v>129602085</v>
       </c>
       <c r="B43" t="n">
-        <v>91553</v>
+        <v>57887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5232,37 +5208,51 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>555724</v>
+        <v>555725</v>
       </c>
       <c r="R43" t="n">
-        <v>7046089</v>
+        <v>7046023</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5289,9 +5279,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5306,19 +5306,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129602321</v>
+        <v>129600463</v>
       </c>
       <c r="B44" t="n">
         <v>98727</v>
@@ -5348,22 +5348,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>555847</v>
+        <v>555579</v>
       </c>
       <c r="R44" t="n">
-        <v>7045866</v>
+        <v>7046146</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5392,7 +5397,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5402,7 +5407,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5417,19 +5422,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129600463</v>
+        <v>129602321</v>
       </c>
       <c r="B45" t="n">
         <v>98727</v>
@@ -5459,27 +5464,22 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>555579</v>
+        <v>555847</v>
       </c>
       <c r="R45" t="n">
-        <v>7046146</v>
+        <v>7045866</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5533,64 +5533,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129602134</v>
+        <v>129600640</v>
       </c>
       <c r="B46" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555825</v>
+        <v>555615</v>
       </c>
       <c r="R46" t="n">
-        <v>7045910</v>
+        <v>7046128</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5619,7 +5615,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5629,7 +5625,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5644,61 +5640,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129603244</v>
+        <v>129601971</v>
       </c>
       <c r="B47" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555877</v>
+        <v>555791</v>
       </c>
       <c r="R47" t="n">
-        <v>7045808</v>
+        <v>7045965</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5730,7 +5722,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5740,7 +5732,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5767,7 +5759,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129600640</v>
+        <v>129601113</v>
       </c>
       <c r="B48" t="n">
         <v>80149</v>
@@ -5802,13 +5794,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>555615</v>
+        <v>555677</v>
       </c>
       <c r="R48" t="n">
-        <v>7046128</v>
+        <v>7046225</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5835,19 +5827,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5862,60 +5844,64 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129601113</v>
+        <v>129603244</v>
       </c>
       <c r="B49" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>555677</v>
+        <v>555877</v>
       </c>
       <c r="R49" t="n">
-        <v>7046225</v>
+        <v>7045808</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5942,9 +5928,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5959,57 +5955,61 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129601971</v>
+        <v>129602134</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555791</v>
+        <v>555825</v>
       </c>
       <c r="R50" t="n">
-        <v>7045965</v>
+        <v>7045910</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6041,7 +6041,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6408,52 +6408,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129600692</v>
+        <v>129600139</v>
       </c>
       <c r="B54" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555611</v>
+        <v>555553</v>
       </c>
       <c r="R54" t="n">
-        <v>7046241</v>
+        <v>7046074</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6480,9 +6476,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6497,60 +6503,64 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129600139</v>
+        <v>129600692</v>
       </c>
       <c r="B55" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555553</v>
+        <v>555611</v>
       </c>
       <c r="R55" t="n">
-        <v>7046074</v>
+        <v>7046241</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6577,19 +6587,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6604,22 +6604,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129602952</v>
+        <v>129602004</v>
       </c>
       <c r="B56" t="n">
-        <v>91517</v>
+        <v>58097</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6627,37 +6627,41 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>103015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555778</v>
+        <v>555738</v>
       </c>
       <c r="R56" t="n">
-        <v>7045842</v>
+        <v>7046093</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6684,19 +6688,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>14:49</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6711,44 +6705,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129602459</v>
+        <v>129602952</v>
       </c>
       <c r="B57" t="n">
-        <v>91553</v>
+        <v>91517</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6758,13 +6752,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555835</v>
+        <v>555778</v>
       </c>
       <c r="R57" t="n">
-        <v>7045881</v>
+        <v>7045842</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6791,9 +6785,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6808,22 +6812,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129600865</v>
+        <v>129601480</v>
       </c>
       <c r="B58" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6831,21 +6835,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6855,13 +6859,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555679</v>
+        <v>555697</v>
       </c>
       <c r="R58" t="n">
-        <v>7046243</v>
+        <v>7046157</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6888,19 +6892,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6915,64 +6909,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129600524</v>
+        <v>129600865</v>
       </c>
       <c r="B59" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>555564</v>
+        <v>555679</v>
       </c>
       <c r="R59" t="n">
-        <v>7046096</v>
+        <v>7046243</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6999,9 +6989,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7016,12 +7016,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7135,10 +7135,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129600317</v>
+        <v>129602023</v>
       </c>
       <c r="B61" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7146,37 +7146,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555575</v>
+        <v>555819</v>
       </c>
       <c r="R61" t="n">
-        <v>7046182</v>
+        <v>7045946</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7203,9 +7203,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7220,22 +7230,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129601480</v>
+        <v>129600317</v>
       </c>
       <c r="B62" t="n">
-        <v>80149</v>
+        <v>91851</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7243,34 +7253,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555697</v>
+        <v>555575</v>
       </c>
       <c r="R62" t="n">
-        <v>7046157</v>
+        <v>7046182</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7329,7 +7339,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129602023</v>
+        <v>129602459</v>
       </c>
       <c r="B63" t="n">
         <v>91553</v>
@@ -7364,13 +7374,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555819</v>
+        <v>555835</v>
       </c>
       <c r="R63" t="n">
-        <v>7045946</v>
+        <v>7045881</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7397,19 +7407,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7424,61 +7424,61 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129602004</v>
+        <v>129600524</v>
       </c>
       <c r="B64" t="n">
-        <v>58097</v>
+        <v>98727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>555738</v>
+        <v>555564</v>
       </c>
       <c r="R64" t="n">
-        <v>7046093</v>
+        <v>7046096</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7644,10 +7644,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129601541</v>
+        <v>129600977</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7655,42 +7655,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>555702</v>
+        <v>555704</v>
       </c>
       <c r="R66" t="n">
-        <v>7046142</v>
+        <v>7046202</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7717,14 +7712,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7739,22 +7739,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129602371</v>
+        <v>129601012</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7762,42 +7762,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>555825</v>
+        <v>555680</v>
       </c>
       <c r="R67" t="n">
-        <v>7045806</v>
+        <v>7046211</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7824,24 +7819,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7856,22 +7836,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129600977</v>
+        <v>129601541</v>
       </c>
       <c r="B68" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7879,37 +7859,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>555704</v>
+        <v>555702</v>
       </c>
       <c r="R68" t="n">
-        <v>7046202</v>
+        <v>7046142</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7936,19 +7921,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>13:13</t>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7963,22 +7943,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129601012</v>
+        <v>129602371</v>
       </c>
       <c r="B69" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7986,37 +7966,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>555680</v>
+        <v>555825</v>
       </c>
       <c r="R69" t="n">
-        <v>7046211</v>
+        <v>7045806</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8043,9 +8028,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8060,22 +8060,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129602553</v>
+        <v>129601748</v>
       </c>
       <c r="B70" t="n">
-        <v>91851</v>
+        <v>80149</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8083,21 +8083,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8107,13 +8107,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>555844</v>
+        <v>555703</v>
       </c>
       <c r="R70" t="n">
-        <v>7045852</v>
+        <v>7046100</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8140,9 +8140,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8157,66 +8167,57 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129600733</v>
+        <v>129601725</v>
       </c>
       <c r="B71" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>555649</v>
+        <v>555750</v>
       </c>
       <c r="R71" t="n">
-        <v>7046243</v>
+        <v>7046140</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8248,7 +8249,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8258,7 +8259,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8273,22 +8274,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129601725</v>
+        <v>129602553</v>
       </c>
       <c r="B72" t="n">
-        <v>80149</v>
+        <v>91851</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8296,21 +8297,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8320,13 +8321,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>555750</v>
+        <v>555844</v>
       </c>
       <c r="R72" t="n">
-        <v>7046140</v>
+        <v>7045852</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8353,19 +8354,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>13:49</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8380,57 +8371,66 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129601748</v>
+        <v>129600733</v>
       </c>
       <c r="B73" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>555703</v>
+        <v>555649</v>
       </c>
       <c r="R73" t="n">
-        <v>7046100</v>
+        <v>7046243</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8721,10 +8721,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129602315</v>
+        <v>129601872</v>
       </c>
       <c r="B76" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8732,37 +8732,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>555729</v>
+        <v>555721</v>
       </c>
       <c r="R76" t="n">
-        <v>7045970</v>
+        <v>7046072</v>
       </c>
       <c r="S76" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8791,7 +8796,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8801,7 +8806,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8816,50 +8826,49 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129601872</v>
+        <v>129602094</v>
       </c>
       <c r="B77" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8868,10 +8877,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>555721</v>
+        <v>555852</v>
       </c>
       <c r="R77" t="n">
-        <v>7046072</v>
+        <v>7045941</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8903,7 +8912,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8913,12 +8922,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8933,64 +8937,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129602094</v>
+        <v>129602315</v>
       </c>
       <c r="B78" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>555852</v>
+        <v>555729</v>
       </c>
       <c r="R78" t="n">
-        <v>7045941</v>
+        <v>7045970</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9044,12 +9044,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9173,10 +9173,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129600975</v>
+        <v>129600219</v>
       </c>
       <c r="B80" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9184,37 +9184,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555633</v>
+        <v>555572</v>
       </c>
       <c r="R80" t="n">
-        <v>7046096</v>
+        <v>7046181</v>
       </c>
       <c r="S80" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9241,19 +9241,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>13:13</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9268,44 +9258,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129601148</v>
+        <v>129601548</v>
       </c>
       <c r="B81" t="n">
-        <v>80149</v>
+        <v>80177</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9315,13 +9305,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555654</v>
+        <v>555707</v>
       </c>
       <c r="R81" t="n">
-        <v>7046170</v>
+        <v>7046135</v>
       </c>
       <c r="S81" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9348,19 +9338,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>13:22</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9375,22 +9355,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129600219</v>
+        <v>129600975</v>
       </c>
       <c r="B82" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9398,37 +9378,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555572</v>
+        <v>555633</v>
       </c>
       <c r="R82" t="n">
-        <v>7046181</v>
+        <v>7046096</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9455,9 +9435,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9472,44 +9462,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129601548</v>
+        <v>129601421</v>
       </c>
       <c r="B83" t="n">
-        <v>80177</v>
+        <v>80149</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9519,13 +9509,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555707</v>
+        <v>555653</v>
       </c>
       <c r="R83" t="n">
-        <v>7046135</v>
+        <v>7046187</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9552,9 +9542,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9569,19 +9569,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129601421</v>
+        <v>129601148</v>
       </c>
       <c r="B84" t="n">
         <v>80149</v>
@@ -9616,13 +9616,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555653</v>
+        <v>555654</v>
       </c>
       <c r="R84" t="n">
-        <v>7046187</v>
+        <v>7046170</v>
       </c>
       <c r="S84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9915,57 +9915,53 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129602716</v>
+        <v>129600090</v>
       </c>
       <c r="B87" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>555762</v>
+        <v>555491</v>
       </c>
       <c r="R87" t="n">
-        <v>7045845</v>
+        <v>7046111</v>
       </c>
       <c r="S87" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9994,7 +9990,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10004,7 +10000,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10019,19 +10020,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129600090</v>
+        <v>129602108</v>
       </c>
       <c r="B88" t="n">
         <v>57727</v>
@@ -10067,14 +10068,14 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>555491</v>
+        <v>555854</v>
       </c>
       <c r="R88" t="n">
-        <v>7046111</v>
+        <v>7045940</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10106,7 +10107,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10116,12 +10117,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10136,19 +10137,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129603549</v>
+        <v>129602716</v>
       </c>
       <c r="B89" t="n">
         <v>98727</v>
@@ -10178,7 +10179,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10192,13 +10193,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>555865</v>
+        <v>555762</v>
       </c>
       <c r="R89" t="n">
-        <v>7045842</v>
+        <v>7045845</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10227,7 +10228,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10237,7 +10238,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10252,12 +10253,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -10380,48 +10381,57 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129602154</v>
+        <v>129603549</v>
       </c>
       <c r="B91" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>555676</v>
+        <v>555865</v>
       </c>
       <c r="R91" t="n">
-        <v>7045998</v>
+        <v>7045842</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10448,9 +10458,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10465,50 +10485,54 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129602108</v>
+        <v>129601760</v>
       </c>
       <c r="B92" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -10517,13 +10541,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>555854</v>
+        <v>555694</v>
       </c>
       <c r="R92" t="n">
-        <v>7045940</v>
+        <v>7046166</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10552,7 +10576,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10562,12 +10586,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10582,69 +10601,60 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129601760</v>
+        <v>129602154</v>
       </c>
       <c r="B93" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>555694</v>
+        <v>555676</v>
       </c>
       <c r="R93" t="n">
-        <v>7046166</v>
+        <v>7045998</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10671,19 +10681,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10698,22 +10698,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129600095</v>
+        <v>129600756</v>
       </c>
       <c r="B94" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10721,37 +10721,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>555473</v>
+        <v>555626</v>
       </c>
       <c r="R94" t="n">
-        <v>7046098</v>
+        <v>7046163</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10778,19 +10778,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>12:36</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10805,12 +10795,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10924,57 +10914,48 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129602185</v>
+        <v>129600095</v>
       </c>
       <c r="B96" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>555729</v>
+        <v>555473</v>
       </c>
       <c r="R96" t="n">
-        <v>7045984</v>
+        <v>7046098</v>
       </c>
       <c r="S96" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11003,7 +10984,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11013,7 +10994,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11028,50 +11009,54 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129602416</v>
+        <v>129602185</v>
       </c>
       <c r="B97" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -11080,13 +11065,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>555801</v>
+        <v>555729</v>
       </c>
       <c r="R97" t="n">
-        <v>7045860</v>
+        <v>7045984</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11113,14 +11098,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11135,22 +11125,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129600756</v>
+        <v>129602416</v>
       </c>
       <c r="B98" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11158,34 +11148,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>555626</v>
+        <v>555801</v>
       </c>
       <c r="R98" t="n">
-        <v>7046163</v>
+        <v>7045860</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -11218,6 +11213,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11244,10 +11244,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129600129</v>
+        <v>129600791</v>
       </c>
       <c r="B99" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11255,42 +11255,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>555483</v>
+        <v>555670</v>
       </c>
       <c r="R99" t="n">
-        <v>7046117</v>
+        <v>7046158</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11317,24 +11312,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11349,22 +11329,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129601948</v>
+        <v>129602252</v>
       </c>
       <c r="B100" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11372,39 +11352,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>555736</v>
+        <v>555848</v>
       </c>
       <c r="R100" t="n">
-        <v>7046059</v>
+        <v>7045879</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11436,7 +11411,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11446,12 +11421,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11466,22 +11436,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129602252</v>
+        <v>129601948</v>
       </c>
       <c r="B101" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11489,34 +11459,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>555848</v>
+        <v>555736</v>
       </c>
       <c r="R101" t="n">
-        <v>7045879</v>
+        <v>7046059</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11548,7 +11523,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11558,7 +11533,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11573,22 +11553,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129600791</v>
+        <v>129600129</v>
       </c>
       <c r="B102" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11596,37 +11576,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>555670</v>
+        <v>555483</v>
       </c>
       <c r="R102" t="n">
-        <v>7046158</v>
+        <v>7046117</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11653,9 +11638,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11670,49 +11670,50 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129600807</v>
+        <v>129602456</v>
       </c>
       <c r="B103" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11721,13 +11722,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>555633</v>
+        <v>555809</v>
       </c>
       <c r="R103" t="n">
-        <v>7046097</v>
+        <v>7045823</v>
       </c>
       <c r="S103" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11756,7 +11757,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11766,7 +11767,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11781,22 +11782,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129600723</v>
+        <v>129601709</v>
       </c>
       <c r="B104" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11804,37 +11805,42 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>555572</v>
+        <v>555739</v>
       </c>
       <c r="R104" t="n">
-        <v>7046171</v>
+        <v>7046139</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11861,9 +11867,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11878,60 +11899,60 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129600507</v>
+        <v>129601828</v>
       </c>
       <c r="B105" t="n">
-        <v>80149</v>
+        <v>91517</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>555608</v>
+        <v>555724</v>
       </c>
       <c r="R105" t="n">
-        <v>7046222</v>
+        <v>7046097</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11958,19 +11979,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11985,57 +11996,57 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129601828</v>
+        <v>129600723</v>
       </c>
       <c r="B106" t="n">
-        <v>91517</v>
+        <v>80149</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>555724</v>
+        <v>555572</v>
       </c>
       <c r="R106" t="n">
-        <v>7046097</v>
+        <v>7046171</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -12094,10 +12105,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129601607</v>
+        <v>129600507</v>
       </c>
       <c r="B107" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12105,37 +12116,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>555709</v>
+        <v>555608</v>
       </c>
       <c r="R107" t="n">
-        <v>7046133</v>
+        <v>7046222</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12162,9 +12173,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12179,22 +12200,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129601709</v>
+        <v>129601607</v>
       </c>
       <c r="B108" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12202,42 +12223,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>555739</v>
+        <v>555709</v>
       </c>
       <c r="R108" t="n">
-        <v>7046139</v>
+        <v>7046133</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12264,24 +12280,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12296,12 +12297,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -12424,38 +12425,37 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129602456</v>
+        <v>129600807</v>
       </c>
       <c r="B110" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -12464,13 +12464,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>555809</v>
+        <v>555633</v>
       </c>
       <c r="R110" t="n">
-        <v>7045823</v>
+        <v>7046097</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12524,12 +12524,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -12652,49 +12652,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129600022</v>
+        <v>129601528</v>
       </c>
       <c r="B112" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>555560</v>
+        <v>555698</v>
       </c>
       <c r="R112" t="n">
-        <v>7046091</v>
+        <v>7046140</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -12753,45 +12749,49 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129601528</v>
+        <v>129600022</v>
       </c>
       <c r="B113" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>555698</v>
+        <v>555560</v>
       </c>
       <c r="R113" t="n">
-        <v>7046140</v>
+        <v>7046091</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -13058,52 +13058,48 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129602025</v>
+        <v>129602472</v>
       </c>
       <c r="B116" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>555739</v>
+        <v>555806</v>
       </c>
       <c r="R116" t="n">
-        <v>7046093</v>
+        <v>7045826</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13130,9 +13126,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13147,60 +13153,64 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129602472</v>
+        <v>129602025</v>
       </c>
       <c r="B117" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>555806</v>
+        <v>555739</v>
       </c>
       <c r="R117" t="n">
-        <v>7045826</v>
+        <v>7046093</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13227,19 +13237,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13254,12 +13254,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -13460,10 +13460,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129602598</v>
+        <v>129600175</v>
       </c>
       <c r="B120" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13471,37 +13471,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>555768</v>
+        <v>555493</v>
       </c>
       <c r="R120" t="n">
-        <v>7045841</v>
+        <v>7046125</v>
       </c>
       <c r="S120" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13530,7 +13535,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13540,7 +13545,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13555,19 +13565,19 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129600978</v>
+        <v>129600621</v>
       </c>
       <c r="B121" t="n">
         <v>57727</v>
@@ -13598,22 +13608,22 @@
       <c r="I121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>555668</v>
+        <v>555635</v>
       </c>
       <c r="R121" t="n">
-        <v>7046211</v>
+        <v>7046219</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13640,24 +13650,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13672,19 +13672,19 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129600621</v>
+        <v>129600978</v>
       </c>
       <c r="B122" t="n">
         <v>57727</v>
@@ -13715,22 +13715,22 @@
       <c r="I122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>555635</v>
+        <v>555668</v>
       </c>
       <c r="R122" t="n">
-        <v>7046219</v>
+        <v>7046211</v>
       </c>
       <c r="S122" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13757,14 +13757,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringhack, gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13779,12 +13789,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -13898,10 +13908,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129600175</v>
+        <v>129602598</v>
       </c>
       <c r="B124" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13909,42 +13919,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>555493</v>
+        <v>555768</v>
       </c>
       <c r="R124" t="n">
-        <v>7046125</v>
+        <v>7045841</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13973,7 +13978,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13983,12 +13988,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14003,12 +14003,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -4034,37 +4034,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129602260</v>
+        <v>129602543</v>
       </c>
       <c r="B32" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4073,13 +4074,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555747</v>
+        <v>555769</v>
       </c>
       <c r="R32" t="n">
-        <v>7045963</v>
+        <v>7045881</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4106,9 +4107,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4123,19 +4139,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129600015</v>
+        <v>129602260</v>
       </c>
       <c r="B33" t="n">
         <v>98727</v>
@@ -4165,27 +4181,22 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555553</v>
+        <v>555747</v>
       </c>
       <c r="R33" t="n">
-        <v>7046074</v>
+        <v>7045963</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4212,19 +4223,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4239,65 +4240,69 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129602543</v>
+        <v>129600015</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555769</v>
+        <v>555553</v>
       </c>
       <c r="R34" t="n">
-        <v>7045881</v>
+        <v>7046074</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4326,7 +4331,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4336,12 +4341,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4356,22 +4356,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129601775</v>
+        <v>129602488</v>
       </c>
       <c r="B35" t="n">
-        <v>98727</v>
+        <v>92006</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4379,41 +4379,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555746</v>
+        <v>555837</v>
       </c>
       <c r="R35" t="n">
-        <v>7046137</v>
+        <v>7045886</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4440,19 +4436,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4467,19 +4453,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129602548</v>
+        <v>129601775</v>
       </c>
       <c r="B36" t="n">
         <v>98727</v>
@@ -4509,12 +4495,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4523,13 +4504,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555770</v>
+        <v>555746</v>
       </c>
       <c r="R36" t="n">
-        <v>7045888</v>
+        <v>7046137</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4558,7 +4539,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4568,7 +4549,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4583,22 +4564,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129602488</v>
+        <v>129602548</v>
       </c>
       <c r="B37" t="n">
-        <v>92006</v>
+        <v>98727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4606,37 +4587,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555837</v>
+        <v>555770</v>
       </c>
       <c r="R37" t="n">
-        <v>7045886</v>
+        <v>7045888</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4663,9 +4653,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4680,22 +4680,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129601909</v>
+        <v>129601980</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4703,42 +4703,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555726</v>
+        <v>555724</v>
       </c>
       <c r="R38" t="n">
-        <v>7046072</v>
+        <v>7046089</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4765,24 +4760,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4797,44 +4777,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129601485</v>
+        <v>129602638</v>
       </c>
       <c r="B39" t="n">
-        <v>80178</v>
+        <v>91851</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4844,10 +4824,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555696</v>
+        <v>555826</v>
       </c>
       <c r="R39" t="n">
-        <v>7046160</v>
+        <v>7045880</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4906,32 +4886,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129602219</v>
+        <v>129601485</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4941,10 +4921,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555697</v>
+        <v>555696</v>
       </c>
       <c r="R40" t="n">
-        <v>7045963</v>
+        <v>7046160</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5003,10 +4983,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129602638</v>
+        <v>129602219</v>
       </c>
       <c r="B41" t="n">
-        <v>91851</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5014,21 +4994,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5038,10 +5018,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555826</v>
+        <v>555697</v>
       </c>
       <c r="R41" t="n">
-        <v>7045880</v>
+        <v>7045963</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5100,10 +5080,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129601980</v>
+        <v>129602085</v>
       </c>
       <c r="B42" t="n">
-        <v>91553</v>
+        <v>57887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5111,37 +5091,51 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>555724</v>
+        <v>555725</v>
       </c>
       <c r="R42" t="n">
-        <v>7046089</v>
+        <v>7046023</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5168,9 +5162,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5185,22 +5189,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129602085</v>
+        <v>129601909</v>
       </c>
       <c r="B43" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5208,36 +5212,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5246,10 +5241,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>555725</v>
+        <v>555726</v>
       </c>
       <c r="R43" t="n">
-        <v>7046023</v>
+        <v>7046072</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5281,7 +5276,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5291,7 +5286,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6078,10 +6078,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129602579</v>
+        <v>129600512</v>
       </c>
       <c r="B51" t="n">
-        <v>78801</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6089,37 +6089,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555842</v>
+        <v>555592</v>
       </c>
       <c r="R51" t="n">
-        <v>7045881</v>
+        <v>7046249</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6146,9 +6151,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6163,65 +6183,69 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129600512</v>
+        <v>129601611</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555592</v>
+        <v>555687</v>
       </c>
       <c r="R52" t="n">
-        <v>7046249</v>
+        <v>7046167</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6250,7 +6274,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6260,12 +6284,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6280,69 +6299,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129601611</v>
+        <v>129602579</v>
       </c>
       <c r="B53" t="n">
-        <v>98727</v>
+        <v>78801</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555687</v>
+        <v>555842</v>
       </c>
       <c r="R53" t="n">
-        <v>7046167</v>
+        <v>7045881</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6369,19 +6379,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>13:41</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6396,60 +6396,64 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129600139</v>
+        <v>129600692</v>
       </c>
       <c r="B54" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555553</v>
+        <v>555611</v>
       </c>
       <c r="R54" t="n">
-        <v>7046074</v>
+        <v>7046241</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6476,19 +6480,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6503,64 +6497,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129600692</v>
+        <v>129600139</v>
       </c>
       <c r="B55" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555611</v>
+        <v>555553</v>
       </c>
       <c r="R55" t="n">
-        <v>7046241</v>
+        <v>7046074</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6587,9 +6577,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6604,12 +6604,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6717,48 +6717,52 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129602952</v>
+        <v>129600524</v>
       </c>
       <c r="B57" t="n">
-        <v>91517</v>
+        <v>98727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555778</v>
+        <v>555564</v>
       </c>
       <c r="R57" t="n">
-        <v>7045842</v>
+        <v>7046096</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6785,19 +6789,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:49</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6812,22 +6806,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129601480</v>
+        <v>129600317</v>
       </c>
       <c r="B58" t="n">
-        <v>80149</v>
+        <v>91851</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6835,34 +6829,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555697</v>
+        <v>555575</v>
       </c>
       <c r="R58" t="n">
-        <v>7046157</v>
+        <v>7046182</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6921,7 +6915,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129600865</v>
+        <v>129602023</v>
       </c>
       <c r="B59" t="n">
         <v>91553</v>
@@ -6956,10 +6950,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>555679</v>
+        <v>555819</v>
       </c>
       <c r="R59" t="n">
-        <v>7046243</v>
+        <v>7045946</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6991,7 +6985,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7001,7 +6995,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7028,32 +7022,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129601061</v>
+        <v>129600865</v>
       </c>
       <c r="B60" t="n">
-        <v>80178</v>
+        <v>91553</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7063,10 +7057,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>555707</v>
+        <v>555679</v>
       </c>
       <c r="R60" t="n">
-        <v>7046194</v>
+        <v>7046243</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7098,7 +7092,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7108,7 +7102,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7123,19 +7117,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129602023</v>
+        <v>129602459</v>
       </c>
       <c r="B61" t="n">
         <v>91553</v>
@@ -7170,13 +7164,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555819</v>
+        <v>555835</v>
       </c>
       <c r="R61" t="n">
-        <v>7045946</v>
+        <v>7045881</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7203,19 +7197,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7230,60 +7214,60 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129600317</v>
+        <v>129602952</v>
       </c>
       <c r="B62" t="n">
-        <v>91851</v>
+        <v>91517</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555575</v>
+        <v>555778</v>
       </c>
       <c r="R62" t="n">
-        <v>7046182</v>
+        <v>7045842</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7310,9 +7294,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7327,22 +7321,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129602459</v>
+        <v>129601480</v>
       </c>
       <c r="B63" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7350,21 +7344,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7374,10 +7368,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555835</v>
+        <v>555697</v>
       </c>
       <c r="R63" t="n">
-        <v>7045881</v>
+        <v>7046157</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7436,52 +7430,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129600524</v>
+        <v>129601061</v>
       </c>
       <c r="B64" t="n">
-        <v>98727</v>
+        <v>80178</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>555564</v>
+        <v>555707</v>
       </c>
       <c r="R64" t="n">
-        <v>7046096</v>
+        <v>7046194</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7508,9 +7498,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7525,22 +7525,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129601936</v>
+        <v>129601012</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7548,21 +7548,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7572,13 +7572,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>555804</v>
+        <v>555680</v>
       </c>
       <c r="R65" t="n">
-        <v>7046004</v>
+        <v>7046211</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7605,19 +7605,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7632,22 +7622,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129600977</v>
+        <v>129601936</v>
       </c>
       <c r="B66" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7655,21 +7645,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7679,10 +7669,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>555704</v>
+        <v>555804</v>
       </c>
       <c r="R66" t="n">
-        <v>7046202</v>
+        <v>7046004</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7714,7 +7704,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7724,7 +7714,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7739,22 +7729,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129601012</v>
+        <v>129600977</v>
       </c>
       <c r="B67" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7762,21 +7752,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7786,13 +7776,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>555680</v>
+        <v>555704</v>
       </c>
       <c r="R67" t="n">
-        <v>7046211</v>
+        <v>7046202</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7819,9 +7809,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7836,19 +7836,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129601541</v>
+        <v>129602371</v>
       </c>
       <c r="B68" t="n">
         <v>57727</v>
@@ -7879,7 +7879,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7888,13 +7888,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>555702</v>
+        <v>555825</v>
       </c>
       <c r="R68" t="n">
-        <v>7046142</v>
+        <v>7045806</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7921,14 +7921,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack, gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7943,19 +7953,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129602371</v>
+        <v>129601541</v>
       </c>
       <c r="B69" t="n">
         <v>57727</v>
@@ -7986,7 +7996,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -7995,13 +8005,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>555825</v>
+        <v>555702</v>
       </c>
       <c r="R69" t="n">
-        <v>7045806</v>
+        <v>7046142</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8028,24 +8038,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8060,12 +8060,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8286,48 +8286,52 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129602553</v>
+        <v>129602304</v>
       </c>
       <c r="B72" t="n">
-        <v>91851</v>
+        <v>98727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>555844</v>
+        <v>555857</v>
       </c>
       <c r="R72" t="n">
-        <v>7045852</v>
+        <v>7045866</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8354,9 +8358,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8371,69 +8385,60 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129600733</v>
+        <v>129602553</v>
       </c>
       <c r="B73" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>555649</v>
+        <v>555844</v>
       </c>
       <c r="R73" t="n">
-        <v>7046243</v>
+        <v>7045852</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8460,19 +8465,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8487,19 +8482,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129602304</v>
+        <v>129600733</v>
       </c>
       <c r="B74" t="n">
         <v>98727</v>
@@ -8529,19 +8524,24 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>555857</v>
+        <v>555649</v>
       </c>
       <c r="R74" t="n">
-        <v>7045866</v>
+        <v>7046243</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8598,12 +8598,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8721,38 +8721,37 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129601872</v>
+        <v>129602094</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8761,10 +8760,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>555721</v>
+        <v>555852</v>
       </c>
       <c r="R76" t="n">
-        <v>7046072</v>
+        <v>7045941</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8796,7 +8795,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8806,12 +8805,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8826,64 +8820,60 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129602094</v>
+        <v>129602315</v>
       </c>
       <c r="B77" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>555852</v>
+        <v>555729</v>
       </c>
       <c r="R77" t="n">
-        <v>7045941</v>
+        <v>7045970</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8912,7 +8902,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8922,7 +8912,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8937,22 +8927,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129602315</v>
+        <v>129601872</v>
       </c>
       <c r="B78" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8960,37 +8950,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>555729</v>
+        <v>555721</v>
       </c>
       <c r="R78" t="n">
-        <v>7045970</v>
+        <v>7046072</v>
       </c>
       <c r="S78" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9019,7 +9014,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9029,7 +9024,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9044,12 +9044,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9173,48 +9173,52 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129600219</v>
+        <v>129602172</v>
       </c>
       <c r="B80" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555572</v>
+        <v>555855</v>
       </c>
       <c r="R80" t="n">
-        <v>7046181</v>
+        <v>7045892</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9241,9 +9245,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9258,60 +9272,69 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129601548</v>
+        <v>129601945</v>
       </c>
       <c r="B81" t="n">
-        <v>80177</v>
+        <v>98727</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555707</v>
+        <v>555730</v>
       </c>
       <c r="R81" t="n">
-        <v>7046135</v>
+        <v>7046151</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9338,9 +9361,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9355,22 +9388,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129600975</v>
+        <v>129600219</v>
       </c>
       <c r="B82" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9378,37 +9411,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555633</v>
+        <v>555572</v>
       </c>
       <c r="R82" t="n">
-        <v>7046096</v>
+        <v>7046181</v>
       </c>
       <c r="S82" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9435,19 +9468,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>13:13</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9462,44 +9485,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129601421</v>
+        <v>129601548</v>
       </c>
       <c r="B83" t="n">
-        <v>80149</v>
+        <v>80177</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9509,13 +9532,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555653</v>
+        <v>555707</v>
       </c>
       <c r="R83" t="n">
-        <v>7046187</v>
+        <v>7046135</v>
       </c>
       <c r="S83" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9542,19 +9565,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9569,19 +9582,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129601148</v>
+        <v>129600975</v>
       </c>
       <c r="B84" t="n">
         <v>80149</v>
@@ -9616,13 +9629,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555654</v>
+        <v>555633</v>
       </c>
       <c r="R84" t="n">
-        <v>7046170</v>
+        <v>7046096</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9651,7 +9664,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9661,7 +9674,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9688,52 +9701,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129602172</v>
+        <v>129601421</v>
       </c>
       <c r="B85" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555855</v>
+        <v>555653</v>
       </c>
       <c r="R85" t="n">
-        <v>7045892</v>
+        <v>7046187</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9762,7 +9771,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9772,7 +9781,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9787,69 +9796,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129601945</v>
+        <v>129601148</v>
       </c>
       <c r="B86" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>555730</v>
+        <v>555654</v>
       </c>
       <c r="R86" t="n">
-        <v>7046151</v>
+        <v>7046170</v>
       </c>
       <c r="S86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9915,10 +9915,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129600090</v>
+        <v>129602154</v>
       </c>
       <c r="B87" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9926,42 +9926,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>555491</v>
+        <v>555676</v>
       </c>
       <c r="R87" t="n">
-        <v>7046111</v>
+        <v>7045998</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9988,24 +9983,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10020,19 +10000,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129602108</v>
+        <v>129600090</v>
       </c>
       <c r="B88" t="n">
         <v>57727</v>
@@ -10068,14 +10048,14 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>555854</v>
+        <v>555491</v>
       </c>
       <c r="R88" t="n">
-        <v>7045940</v>
+        <v>7046111</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10107,7 +10087,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10117,12 +10097,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10137,54 +10117,50 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129602716</v>
+        <v>129602108</v>
       </c>
       <c r="B89" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10193,13 +10169,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>555762</v>
+        <v>555854</v>
       </c>
       <c r="R89" t="n">
-        <v>7045845</v>
+        <v>7045940</v>
       </c>
       <c r="S89" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10228,7 +10204,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10238,7 +10214,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10253,19 +10234,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129601612</v>
+        <v>129602716</v>
       </c>
       <c r="B90" t="n">
         <v>98727</v>
@@ -10295,7 +10276,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10309,13 +10290,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>555675</v>
+        <v>555762</v>
       </c>
       <c r="R90" t="n">
-        <v>7046143</v>
+        <v>7045845</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10344,7 +10325,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10354,7 +10335,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10369,19 +10350,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129603549</v>
+        <v>129601612</v>
       </c>
       <c r="B91" t="n">
         <v>98727</v>
@@ -10411,7 +10392,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10425,10 +10406,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>555865</v>
+        <v>555675</v>
       </c>
       <c r="R91" t="n">
-        <v>7045842</v>
+        <v>7046143</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10460,7 +10441,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10470,7 +10451,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10497,7 +10478,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129601760</v>
+        <v>129603549</v>
       </c>
       <c r="B92" t="n">
         <v>98727</v>
@@ -10527,7 +10508,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -10541,13 +10522,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>555694</v>
+        <v>555865</v>
       </c>
       <c r="R92" t="n">
-        <v>7046166</v>
+        <v>7045842</v>
       </c>
       <c r="S92" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10576,7 +10557,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10586,7 +10567,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10601,60 +10582,69 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129602154</v>
+        <v>129601760</v>
       </c>
       <c r="B93" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>555676</v>
+        <v>555694</v>
       </c>
       <c r="R93" t="n">
-        <v>7045998</v>
+        <v>7046166</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10681,9 +10671,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10698,22 +10698,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129600756</v>
+        <v>129602416</v>
       </c>
       <c r="B94" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10721,34 +10721,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>555626</v>
+        <v>555801</v>
       </c>
       <c r="R94" t="n">
-        <v>7046163</v>
+        <v>7045860</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10781,6 +10786,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10807,48 +10817,57 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129602047</v>
+        <v>129602185</v>
       </c>
       <c r="B95" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>555722</v>
+        <v>555729</v>
       </c>
       <c r="R95" t="n">
-        <v>7046017</v>
+        <v>7045984</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10877,7 +10896,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10887,7 +10906,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10902,19 +10921,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129600095</v>
+        <v>129602047</v>
       </c>
       <c r="B96" t="n">
         <v>79044</v>
@@ -10945,14 +10964,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>555473</v>
+        <v>555722</v>
       </c>
       <c r="R96" t="n">
-        <v>7046098</v>
+        <v>7046017</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10984,7 +11003,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10994,7 +11013,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11009,69 +11028,60 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129602185</v>
+        <v>129600756</v>
       </c>
       <c r="B97" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>555729</v>
+        <v>555626</v>
       </c>
       <c r="R97" t="n">
-        <v>7045984</v>
+        <v>7046163</v>
       </c>
       <c r="S97" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11098,19 +11108,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>14:07</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11125,22 +11125,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129602416</v>
+        <v>129600095</v>
       </c>
       <c r="B98" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11148,42 +11148,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>555801</v>
+        <v>555473</v>
       </c>
       <c r="R98" t="n">
-        <v>7045860</v>
+        <v>7046098</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11210,14 +11205,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11232,22 +11232,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129600791</v>
+        <v>129600129</v>
       </c>
       <c r="B99" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11255,37 +11255,42 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>555670</v>
+        <v>555483</v>
       </c>
       <c r="R99" t="n">
-        <v>7046158</v>
+        <v>7046117</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11312,9 +11317,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11329,22 +11349,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129602252</v>
+        <v>129601948</v>
       </c>
       <c r="B100" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11352,34 +11372,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>555848</v>
+        <v>555736</v>
       </c>
       <c r="R100" t="n">
-        <v>7045879</v>
+        <v>7046059</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11411,7 +11436,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11421,7 +11446,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11436,22 +11466,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129601948</v>
+        <v>129602252</v>
       </c>
       <c r="B101" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11459,39 +11489,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>555736</v>
+        <v>555848</v>
       </c>
       <c r="R101" t="n">
-        <v>7046059</v>
+        <v>7045879</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11523,7 +11548,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11533,12 +11558,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11553,22 +11573,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129600129</v>
+        <v>129600791</v>
       </c>
       <c r="B102" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11576,42 +11596,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>555483</v>
+        <v>555670</v>
       </c>
       <c r="R102" t="n">
-        <v>7046117</v>
+        <v>7046158</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11638,24 +11653,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11670,50 +11670,54 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129602456</v>
+        <v>129602437</v>
       </c>
       <c r="B103" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11722,13 +11726,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>555809</v>
+        <v>555757</v>
       </c>
       <c r="R103" t="n">
-        <v>7045823</v>
+        <v>7045907</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11757,7 +11761,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11767,7 +11771,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11782,50 +11786,49 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129601709</v>
+        <v>129600807</v>
       </c>
       <c r="B104" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -11834,13 +11837,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>555739</v>
+        <v>555633</v>
       </c>
       <c r="R104" t="n">
-        <v>7046139</v>
+        <v>7046097</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11869,7 +11872,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11879,12 +11882,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11899,12 +11897,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -12309,42 +12307,38 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129602437</v>
+        <v>129602456</v>
       </c>
       <c r="B109" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -12353,13 +12347,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>555757</v>
+        <v>555809</v>
       </c>
       <c r="R109" t="n">
-        <v>7045907</v>
+        <v>7045823</v>
       </c>
       <c r="S109" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12388,7 +12382,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12398,7 +12392,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12413,49 +12407,50 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129600807</v>
+        <v>129601709</v>
       </c>
       <c r="B110" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -12464,13 +12459,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>555633</v>
+        <v>555739</v>
       </c>
       <c r="R110" t="n">
-        <v>7046097</v>
+        <v>7046139</v>
       </c>
       <c r="S110" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12499,7 +12494,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12509,7 +12504,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12524,19 +12524,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129600513</v>
+        <v>129600022</v>
       </c>
       <c r="B111" t="n">
         <v>98727</v>
@@ -12569,24 +12569,19 @@
           <t>50</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>555590</v>
+        <v>555560</v>
       </c>
       <c r="R111" t="n">
-        <v>7046134</v>
+        <v>7046091</v>
       </c>
       <c r="S111" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12613,19 +12608,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12640,60 +12625,64 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129601528</v>
+        <v>129601553</v>
       </c>
       <c r="B112" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>555698</v>
+        <v>555704</v>
       </c>
       <c r="R112" t="n">
-        <v>7046140</v>
+        <v>7046148</v>
       </c>
       <c r="S112" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12720,9 +12709,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12737,19 +12736,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129600022</v>
+        <v>129600513</v>
       </c>
       <c r="B113" t="n">
         <v>98727</v>
@@ -12782,19 +12781,24 @@
           <t>50</t>
         </is>
       </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>555560</v>
+        <v>555590</v>
       </c>
       <c r="R113" t="n">
-        <v>7046091</v>
+        <v>7046134</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12821,9 +12825,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12838,64 +12852,60 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129601553</v>
+        <v>129601528</v>
       </c>
       <c r="B114" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>555704</v>
+        <v>555698</v>
       </c>
       <c r="R114" t="n">
-        <v>7046148</v>
+        <v>7046140</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12922,19 +12932,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12949,12 +12949,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -13165,49 +13165,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129602025</v>
+        <v>129600727</v>
       </c>
       <c r="B117" t="n">
-        <v>98727</v>
+        <v>80178</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>555739</v>
+        <v>555605</v>
       </c>
       <c r="R117" t="n">
-        <v>7046093</v>
+        <v>7046222</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13266,45 +13262,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129600727</v>
+        <v>129600845</v>
       </c>
       <c r="B118" t="n">
-        <v>80178</v>
+        <v>80149</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>555605</v>
+        <v>555681</v>
       </c>
       <c r="R118" t="n">
-        <v>7046222</v>
+        <v>7046162</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13363,45 +13359,49 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129600845</v>
+        <v>129602025</v>
       </c>
       <c r="B119" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>555681</v>
+        <v>555739</v>
       </c>
       <c r="R119" t="n">
-        <v>7046162</v>
+        <v>7046093</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -13460,10 +13460,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129600175</v>
+        <v>129602058</v>
       </c>
       <c r="B120" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13471,39 +13471,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>555493</v>
+        <v>555829</v>
       </c>
       <c r="R120" t="n">
-        <v>7046125</v>
+        <v>7045930</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13535,7 +13530,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13545,12 +13540,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13565,22 +13555,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129600621</v>
+        <v>129602598</v>
       </c>
       <c r="B121" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13588,42 +13578,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>555635</v>
+        <v>555768</v>
       </c>
       <c r="R121" t="n">
-        <v>7046219</v>
+        <v>7045841</v>
       </c>
       <c r="S121" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13650,14 +13635,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13672,12 +13662,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -13801,10 +13791,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129602058</v>
+        <v>129600621</v>
       </c>
       <c r="B123" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13812,37 +13802,42 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>555829</v>
+        <v>555635</v>
       </c>
       <c r="R123" t="n">
-        <v>7045930</v>
+        <v>7046219</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13869,19 +13864,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>14:04</t>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13896,22 +13886,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129602598</v>
+        <v>129600175</v>
       </c>
       <c r="B124" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13919,37 +13909,42 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>555768</v>
+        <v>555493</v>
       </c>
       <c r="R124" t="n">
-        <v>7045841</v>
+        <v>7046125</v>
       </c>
       <c r="S124" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13978,7 +13973,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13988,7 +13983,12 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14003,12 +14003,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY124"/>
+  <dimension ref="A1:AY125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3616,10 +3616,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298285</v>
+        <v>129298204</v>
       </c>
       <c r="B28" t="n">
-        <v>91851</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3627,21 +3627,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555760</v>
+        <v>555763</v>
       </c>
       <c r="R28" t="n">
-        <v>7045817</v>
+        <v>7045835</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3723,10 +3723,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298204</v>
+        <v>129298285</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>91851</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3734,21 +3734,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555763</v>
+        <v>555760</v>
       </c>
       <c r="R29" t="n">
-        <v>7045835</v>
+        <v>7045817</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3830,45 +3830,49 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129601128</v>
+        <v>129602260</v>
       </c>
       <c r="B30" t="n">
-        <v>80178</v>
+        <v>98727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555698</v>
+        <v>555747</v>
       </c>
       <c r="R30" t="n">
-        <v>7046187</v>
+        <v>7045963</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3927,48 +3931,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129602332</v>
+        <v>129600015</v>
       </c>
       <c r="B31" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555835</v>
+        <v>555553</v>
       </c>
       <c r="R31" t="n">
-        <v>7045850</v>
+        <v>7046074</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3997,7 +4010,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4007,7 +4020,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4022,22 +4035,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129602543</v>
+        <v>129602332</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4045,39 +4058,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555769</v>
+        <v>555835</v>
       </c>
       <c r="R32" t="n">
-        <v>7045881</v>
+        <v>7045850</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4109,7 +4117,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4119,12 +4127,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4139,61 +4142,57 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129602260</v>
+        <v>129601128</v>
       </c>
       <c r="B33" t="n">
-        <v>98727</v>
+        <v>80178</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555747</v>
+        <v>555698</v>
       </c>
       <c r="R33" t="n">
-        <v>7045963</v>
+        <v>7046187</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4252,57 +4251,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129600015</v>
+        <v>129602543</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555553</v>
+        <v>555769</v>
       </c>
       <c r="R34" t="n">
-        <v>7046074</v>
+        <v>7045881</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4331,7 +4326,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4341,7 +4336,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4356,22 +4356,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129602488</v>
+        <v>129601775</v>
       </c>
       <c r="B35" t="n">
-        <v>92006</v>
+        <v>98727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4379,37 +4379,41 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555837</v>
+        <v>555746</v>
       </c>
       <c r="R35" t="n">
-        <v>7045886</v>
+        <v>7046137</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4436,9 +4440,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4453,19 +4467,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129601775</v>
+        <v>129602548</v>
       </c>
       <c r="B36" t="n">
         <v>98727</v>
@@ -4495,7 +4509,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4504,13 +4523,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555746</v>
+        <v>555770</v>
       </c>
       <c r="R36" t="n">
-        <v>7046137</v>
+        <v>7045888</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4539,7 +4558,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4549,7 +4568,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4564,22 +4583,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129602548</v>
+        <v>129602488</v>
       </c>
       <c r="B37" t="n">
-        <v>98727</v>
+        <v>92006</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4587,46 +4606,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555770</v>
+        <v>555837</v>
       </c>
       <c r="R37" t="n">
-        <v>7045888</v>
+        <v>7045886</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4653,19 +4663,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4680,22 +4680,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129601980</v>
+        <v>129602219</v>
       </c>
       <c r="B38" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4703,21 +4703,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555724</v>
+        <v>555697</v>
       </c>
       <c r="R38" t="n">
-        <v>7046089</v>
+        <v>7045963</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4886,32 +4886,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129601485</v>
+        <v>129601980</v>
       </c>
       <c r="B40" t="n">
-        <v>80178</v>
+        <v>91553</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555696</v>
+        <v>555724</v>
       </c>
       <c r="R40" t="n">
-        <v>7046160</v>
+        <v>7046089</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4983,10 +4983,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129602219</v>
+        <v>129601909</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4994,37 +4994,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555697</v>
+        <v>555726</v>
       </c>
       <c r="R41" t="n">
-        <v>7045963</v>
+        <v>7046072</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5051,9 +5056,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5068,12 +5088,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5201,53 +5221,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129601909</v>
+        <v>129601485</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>555726</v>
+        <v>555696</v>
       </c>
       <c r="R43" t="n">
-        <v>7046072</v>
+        <v>7046160</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5274,24 +5289,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5306,12 +5306,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5545,10 +5545,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129600640</v>
+        <v>129601971</v>
       </c>
       <c r="B46" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5556,21 +5556,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5580,13 +5580,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555615</v>
+        <v>555791</v>
       </c>
       <c r="R46" t="n">
-        <v>7046128</v>
+        <v>7045965</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5640,22 +5640,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129601971</v>
+        <v>129600640</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5663,21 +5663,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5687,13 +5687,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555791</v>
+        <v>555615</v>
       </c>
       <c r="R47" t="n">
-        <v>7045965</v>
+        <v>7046128</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5747,12 +5747,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6078,10 +6078,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129600512</v>
+        <v>129602579</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>78801</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6089,42 +6089,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555592</v>
+        <v>555842</v>
       </c>
       <c r="R51" t="n">
-        <v>7046249</v>
+        <v>7045881</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6151,24 +6146,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6183,69 +6163,65 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129601611</v>
+        <v>129600512</v>
       </c>
       <c r="B52" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555687</v>
+        <v>555592</v>
       </c>
       <c r="R52" t="n">
-        <v>7046167</v>
+        <v>7046249</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6274,7 +6250,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6284,7 +6260,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6299,60 +6280,69 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129602579</v>
+        <v>129601611</v>
       </c>
       <c r="B53" t="n">
-        <v>78801</v>
+        <v>98727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555842</v>
+        <v>555687</v>
       </c>
       <c r="R53" t="n">
-        <v>7045881</v>
+        <v>7046167</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6379,9 +6369,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6396,12 +6396,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6616,10 +6616,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129602004</v>
+        <v>129602952</v>
       </c>
       <c r="B56" t="n">
-        <v>58097</v>
+        <v>91517</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6627,41 +6627,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555738</v>
+        <v>555778</v>
       </c>
       <c r="R56" t="n">
-        <v>7046093</v>
+        <v>7045842</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6688,9 +6684,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6705,64 +6711,60 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129600524</v>
+        <v>129600865</v>
       </c>
       <c r="B57" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555564</v>
+        <v>555679</v>
       </c>
       <c r="R57" t="n">
-        <v>7046096</v>
+        <v>7046243</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6789,9 +6791,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6806,22 +6818,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129600317</v>
+        <v>129602023</v>
       </c>
       <c r="B58" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6829,37 +6841,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555575</v>
+        <v>555819</v>
       </c>
       <c r="R58" t="n">
-        <v>7046182</v>
+        <v>7045946</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6886,9 +6898,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6903,22 +6925,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129602023</v>
+        <v>129600317</v>
       </c>
       <c r="B59" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6926,37 +6948,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>555819</v>
+        <v>555575</v>
       </c>
       <c r="R59" t="n">
-        <v>7045946</v>
+        <v>7046182</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6983,19 +7005,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7010,19 +7022,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129600865</v>
+        <v>129602459</v>
       </c>
       <c r="B60" t="n">
         <v>91553</v>
@@ -7057,13 +7069,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>555679</v>
+        <v>555835</v>
       </c>
       <c r="R60" t="n">
-        <v>7046243</v>
+        <v>7045881</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7090,19 +7102,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7117,57 +7119,61 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129602459</v>
+        <v>129602004</v>
       </c>
       <c r="B61" t="n">
-        <v>91553</v>
+        <v>58097</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555835</v>
+        <v>555738</v>
       </c>
       <c r="R61" t="n">
-        <v>7045881</v>
+        <v>7046093</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7226,48 +7232,52 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129602952</v>
+        <v>129600524</v>
       </c>
       <c r="B62" t="n">
-        <v>91517</v>
+        <v>98727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555778</v>
+        <v>555564</v>
       </c>
       <c r="R62" t="n">
-        <v>7045842</v>
+        <v>7046096</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7294,19 +7304,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>14:49</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7321,12 +7321,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7848,7 +7848,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129602371</v>
+        <v>129601541</v>
       </c>
       <c r="B68" t="n">
         <v>57727</v>
@@ -7879,7 +7879,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7888,13 +7888,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>555825</v>
+        <v>555702</v>
       </c>
       <c r="R68" t="n">
-        <v>7045806</v>
+        <v>7046142</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7921,24 +7921,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7953,19 +7943,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129601541</v>
+        <v>129602371</v>
       </c>
       <c r="B69" t="n">
         <v>57727</v>
@@ -7996,7 +7986,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8005,13 +7995,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>555702</v>
+        <v>555825</v>
       </c>
       <c r="R69" t="n">
-        <v>7046142</v>
+        <v>7045806</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8038,14 +8028,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack, gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8060,57 +8060,66 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129601748</v>
+        <v>129600733</v>
       </c>
       <c r="B70" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>555703</v>
+        <v>555649</v>
       </c>
       <c r="R70" t="n">
-        <v>7046100</v>
+        <v>7046243</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8142,7 +8151,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8152,7 +8161,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8179,45 +8188,49 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129601725</v>
+        <v>129602304</v>
       </c>
       <c r="B71" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>555750</v>
+        <v>555857</v>
       </c>
       <c r="R71" t="n">
-        <v>7046140</v>
+        <v>7045866</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8249,7 +8262,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8259,7 +8272,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8286,49 +8299,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129602304</v>
+        <v>129601748</v>
       </c>
       <c r="B72" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>555857</v>
+        <v>555703</v>
       </c>
       <c r="R72" t="n">
-        <v>7045866</v>
+        <v>7046100</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8360,7 +8369,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8370,7 +8379,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8385,22 +8394,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129602553</v>
+        <v>129601725</v>
       </c>
       <c r="B73" t="n">
-        <v>91851</v>
+        <v>80149</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8408,21 +8417,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8432,13 +8441,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>555844</v>
+        <v>555750</v>
       </c>
       <c r="R73" t="n">
-        <v>7045852</v>
+        <v>7046140</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8465,9 +8474,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8482,69 +8501,60 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129600733</v>
+        <v>129602553</v>
       </c>
       <c r="B74" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>555649</v>
+        <v>555844</v>
       </c>
       <c r="R74" t="n">
-        <v>7046243</v>
+        <v>7045852</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8571,19 +8581,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8598,12 +8598,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8721,52 +8721,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129602094</v>
+        <v>129602315</v>
       </c>
       <c r="B76" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>555852</v>
+        <v>555729</v>
       </c>
       <c r="R76" t="n">
-        <v>7045941</v>
+        <v>7045970</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8795,7 +8791,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8805,7 +8801,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8820,22 +8816,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129602315</v>
+        <v>129601872</v>
       </c>
       <c r="B77" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8843,37 +8839,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>555729</v>
+        <v>555721</v>
       </c>
       <c r="R77" t="n">
-        <v>7045970</v>
+        <v>7046072</v>
       </c>
       <c r="S77" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8902,7 +8903,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8912,7 +8913,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8927,50 +8933,49 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129601872</v>
+        <v>129602094</v>
       </c>
       <c r="B78" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8979,10 +8984,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>555721</v>
+        <v>555852</v>
       </c>
       <c r="R78" t="n">
-        <v>7046072</v>
+        <v>7045941</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9014,7 +9019,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9024,12 +9029,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9044,65 +9044,60 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129603240</v>
+        <v>129601548</v>
       </c>
       <c r="B79" t="n">
-        <v>57727</v>
+        <v>80177</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>555865</v>
+        <v>555707</v>
       </c>
       <c r="R79" t="n">
-        <v>7045842</v>
+        <v>7046135</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9129,24 +9124,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9161,64 +9141,60 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129602172</v>
+        <v>129600975</v>
       </c>
       <c r="B80" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555855</v>
+        <v>555633</v>
       </c>
       <c r="R80" t="n">
-        <v>7045892</v>
+        <v>7046096</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9247,7 +9223,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9257,7 +9233,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9272,66 +9248,57 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129601945</v>
+        <v>129601421</v>
       </c>
       <c r="B81" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555730</v>
+        <v>555653</v>
       </c>
       <c r="R81" t="n">
-        <v>7046151</v>
+        <v>7046187</v>
       </c>
       <c r="S81" t="n">
         <v>3</v>
@@ -9363,7 +9330,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9373,7 +9340,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9400,10 +9367,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129600219</v>
+        <v>129601148</v>
       </c>
       <c r="B82" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9411,37 +9378,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555572</v>
+        <v>555654</v>
       </c>
       <c r="R82" t="n">
-        <v>7046181</v>
+        <v>7046170</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9468,9 +9435,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9485,57 +9462,57 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129601548</v>
+        <v>129600219</v>
       </c>
       <c r="B83" t="n">
-        <v>80177</v>
+        <v>91553</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6461</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555707</v>
+        <v>555572</v>
       </c>
       <c r="R83" t="n">
-        <v>7046135</v>
+        <v>7046181</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9594,45 +9571,54 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129600975</v>
+        <v>129601945</v>
       </c>
       <c r="B84" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555633</v>
+        <v>555730</v>
       </c>
       <c r="R84" t="n">
-        <v>7046096</v>
+        <v>7046151</v>
       </c>
       <c r="S84" t="n">
         <v>3</v>
@@ -9664,7 +9650,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9674,7 +9660,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9701,10 +9687,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129601421</v>
+        <v>129603240</v>
       </c>
       <c r="B85" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9712,37 +9698,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555653</v>
+        <v>555865</v>
       </c>
       <c r="R85" t="n">
-        <v>7046187</v>
+        <v>7045842</v>
       </c>
       <c r="S85" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9771,7 +9762,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9781,7 +9772,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9796,60 +9792,64 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129601148</v>
+        <v>129602172</v>
       </c>
       <c r="B86" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>555654</v>
+        <v>555855</v>
       </c>
       <c r="R86" t="n">
-        <v>7046170</v>
+        <v>7045892</v>
       </c>
       <c r="S86" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9903,22 +9903,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129602154</v>
+        <v>129600090</v>
       </c>
       <c r="B87" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9926,37 +9926,42 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>555676</v>
+        <v>555491</v>
       </c>
       <c r="R87" t="n">
-        <v>7045998</v>
+        <v>7046111</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9983,9 +9988,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10000,19 +10020,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129600090</v>
+        <v>129602108</v>
       </c>
       <c r="B88" t="n">
         <v>57727</v>
@@ -10048,14 +10068,14 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>555491</v>
+        <v>555854</v>
       </c>
       <c r="R88" t="n">
-        <v>7046111</v>
+        <v>7045940</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10087,7 +10107,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10097,12 +10117,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10117,22 +10137,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129602108</v>
+        <v>129602154</v>
       </c>
       <c r="B89" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10140,42 +10160,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>555854</v>
+        <v>555676</v>
       </c>
       <c r="R89" t="n">
-        <v>7045940</v>
+        <v>7045998</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10202,24 +10217,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10234,12 +10234,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -10710,38 +10710,42 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129602416</v>
+        <v>129602185</v>
       </c>
       <c r="B94" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -10750,13 +10754,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>555801</v>
+        <v>555729</v>
       </c>
       <c r="R94" t="n">
-        <v>7045860</v>
+        <v>7045984</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10783,14 +10787,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10805,54 +10814,50 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129602185</v>
+        <v>129602416</v>
       </c>
       <c r="B95" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -10861,13 +10866,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>555729</v>
+        <v>555801</v>
       </c>
       <c r="R95" t="n">
-        <v>7045984</v>
+        <v>7045860</v>
       </c>
       <c r="S95" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10894,19 +10899,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>14:07</t>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10921,22 +10921,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129602047</v>
+        <v>129600756</v>
       </c>
       <c r="B96" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10944,21 +10944,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10968,13 +10968,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>555722</v>
+        <v>555626</v>
       </c>
       <c r="R96" t="n">
-        <v>7046017</v>
+        <v>7046163</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11001,19 +11001,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11028,22 +11018,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129600756</v>
+        <v>129602047</v>
       </c>
       <c r="B97" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11051,21 +11041,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11075,13 +11065,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>555626</v>
+        <v>555722</v>
       </c>
       <c r="R97" t="n">
-        <v>7046163</v>
+        <v>7046017</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11108,9 +11098,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11125,12 +11125,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -11244,10 +11244,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129600129</v>
+        <v>129600791</v>
       </c>
       <c r="B99" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11255,42 +11255,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>555483</v>
+        <v>555670</v>
       </c>
       <c r="R99" t="n">
-        <v>7046117</v>
+        <v>7046158</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11317,24 +11312,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11349,22 +11329,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129601948</v>
+        <v>129602252</v>
       </c>
       <c r="B100" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11372,39 +11352,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>555736</v>
+        <v>555848</v>
       </c>
       <c r="R100" t="n">
-        <v>7046059</v>
+        <v>7045879</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11436,7 +11411,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11446,12 +11421,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11466,22 +11436,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129602252</v>
+        <v>129601948</v>
       </c>
       <c r="B101" t="n">
-        <v>91553</v>
+        <v>57727</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11489,34 +11459,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>555848</v>
+        <v>555736</v>
       </c>
       <c r="R101" t="n">
-        <v>7045879</v>
+        <v>7046059</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11548,7 +11523,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11558,7 +11533,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11573,22 +11553,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129600791</v>
+        <v>129600129</v>
       </c>
       <c r="B102" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11596,37 +11576,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>555670</v>
+        <v>555483</v>
       </c>
       <c r="R102" t="n">
-        <v>7046158</v>
+        <v>7046117</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11653,9 +11638,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11670,69 +11670,60 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129602437</v>
+        <v>129601828</v>
       </c>
       <c r="B103" t="n">
-        <v>98727</v>
+        <v>91517</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>555757</v>
+        <v>555724</v>
       </c>
       <c r="R103" t="n">
-        <v>7045907</v>
+        <v>7046097</v>
       </c>
       <c r="S103" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11759,19 +11750,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11786,64 +11767,60 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129600807</v>
+        <v>129601607</v>
       </c>
       <c r="B104" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>555633</v>
+        <v>555709</v>
       </c>
       <c r="R104" t="n">
-        <v>7046097</v>
+        <v>7046133</v>
       </c>
       <c r="S104" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11870,19 +11847,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11897,57 +11864,57 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129601828</v>
+        <v>129600723</v>
       </c>
       <c r="B105" t="n">
-        <v>91517</v>
+        <v>80149</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>555724</v>
+        <v>555572</v>
       </c>
       <c r="R105" t="n">
-        <v>7046097</v>
+        <v>7046171</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -12006,7 +11973,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129600723</v>
+        <v>129600507</v>
       </c>
       <c r="B106" t="n">
         <v>80149</v>
@@ -12041,13 +12008,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>555572</v>
+        <v>555608</v>
       </c>
       <c r="R106" t="n">
-        <v>7046171</v>
+        <v>7046222</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12074,9 +12041,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12091,22 +12068,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129600507</v>
+        <v>129602456</v>
       </c>
       <c r="B107" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12114,34 +12091,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>555608</v>
+        <v>555809</v>
       </c>
       <c r="R107" t="n">
-        <v>7046222</v>
+        <v>7045823</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12173,7 +12155,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12183,7 +12165,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12210,10 +12192,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129601607</v>
+        <v>129601709</v>
       </c>
       <c r="B108" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12221,37 +12203,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>555709</v>
+        <v>555739</v>
       </c>
       <c r="R108" t="n">
-        <v>7046133</v>
+        <v>7046139</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12278,9 +12265,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12295,50 +12297,54 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129602456</v>
+        <v>129602437</v>
       </c>
       <c r="B109" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -12347,13 +12353,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>555809</v>
+        <v>555757</v>
       </c>
       <c r="R109" t="n">
-        <v>7045823</v>
+        <v>7045907</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12382,7 +12388,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12392,7 +12398,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12407,50 +12413,49 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129601709</v>
+        <v>129600807</v>
       </c>
       <c r="B110" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -12459,13 +12464,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>555739</v>
+        <v>555633</v>
       </c>
       <c r="R110" t="n">
-        <v>7046139</v>
+        <v>7046097</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12494,7 +12499,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12504,12 +12509,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12524,61 +12524,57 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129600022</v>
+        <v>129601521</v>
       </c>
       <c r="B111" t="n">
-        <v>98727</v>
+        <v>97598</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>555560</v>
+        <v>555695</v>
       </c>
       <c r="R111" t="n">
-        <v>7046091</v>
+        <v>7046136</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -12637,52 +12633,48 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129601553</v>
+        <v>129601528</v>
       </c>
       <c r="B112" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>555704</v>
+        <v>555698</v>
       </c>
       <c r="R112" t="n">
-        <v>7046148</v>
+        <v>7046140</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12709,19 +12701,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12736,12 +12718,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -12864,45 +12846,49 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129601528</v>
+        <v>129600022</v>
       </c>
       <c r="B114" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>555698</v>
+        <v>555560</v>
       </c>
       <c r="R114" t="n">
-        <v>7046140</v>
+        <v>7046091</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12961,48 +12947,52 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129601521</v>
+        <v>129601553</v>
       </c>
       <c r="B115" t="n">
-        <v>97598</v>
+        <v>98727</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>555695</v>
+        <v>555704</v>
       </c>
       <c r="R115" t="n">
-        <v>7046136</v>
+        <v>7046148</v>
       </c>
       <c r="S115" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13029,9 +13019,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13046,12 +13046,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
@@ -13674,7 +13674,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129600978</v>
+        <v>129600175</v>
       </c>
       <c r="B122" t="n">
         <v>57727</v>
@@ -13710,14 +13710,14 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>555668</v>
+        <v>555493</v>
       </c>
       <c r="R122" t="n">
-        <v>7046211</v>
+        <v>7046125</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13749,7 +13749,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
@@ -13779,12 +13779,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -13898,7 +13898,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129600175</v>
+        <v>129600978</v>
       </c>
       <c r="B124" t="n">
         <v>57727</v>
@@ -13934,14 +13934,14 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>555493</v>
+        <v>555668</v>
       </c>
       <c r="R124" t="n">
-        <v>7046125</v>
+        <v>7046211</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
@@ -14003,15 +14003,112 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>129601920</v>
+      </c>
+      <c r="B125" t="n">
+        <v>92036</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>5467</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Kådvaxskinn</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Phlebia serialis</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>555741</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7046110</v>
+      </c>
+      <c r="S125" t="n">
+        <v>15</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3616,10 +3616,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298204</v>
+        <v>129298285</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>91851</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3627,21 +3627,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555763</v>
+        <v>555760</v>
       </c>
       <c r="R28" t="n">
-        <v>7045835</v>
+        <v>7045817</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3723,10 +3723,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298285</v>
+        <v>129298204</v>
       </c>
       <c r="B29" t="n">
-        <v>91851</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3734,21 +3734,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555760</v>
+        <v>555763</v>
       </c>
       <c r="R29" t="n">
-        <v>7045817</v>
+        <v>7045835</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3830,52 +3830,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129602260</v>
+        <v>129602332</v>
       </c>
       <c r="B30" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555747</v>
+        <v>555835</v>
       </c>
       <c r="R30" t="n">
-        <v>7045963</v>
+        <v>7045850</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3902,9 +3898,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3919,19 +3925,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129600015</v>
+        <v>129602260</v>
       </c>
       <c r="B31" t="n">
         <v>98727</v>
@@ -3961,27 +3967,22 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555553</v>
+        <v>555747</v>
       </c>
       <c r="R31" t="n">
-        <v>7046074</v>
+        <v>7045963</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4008,19 +4009,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,60 +4026,69 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129602332</v>
+        <v>129600015</v>
       </c>
       <c r="B32" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555835</v>
+        <v>555553</v>
       </c>
       <c r="R32" t="n">
-        <v>7045850</v>
+        <v>7046074</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4142,12 +4142,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4368,10 +4368,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129601775</v>
+        <v>129602488</v>
       </c>
       <c r="B35" t="n">
-        <v>98727</v>
+        <v>92006</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4379,41 +4379,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555746</v>
+        <v>555837</v>
       </c>
       <c r="R35" t="n">
-        <v>7046137</v>
+        <v>7045886</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4440,19 +4436,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4467,12 +4453,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4595,10 +4581,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129602488</v>
+        <v>129601775</v>
       </c>
       <c r="B37" t="n">
-        <v>92006</v>
+        <v>98727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4606,37 +4592,41 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555837</v>
+        <v>555746</v>
       </c>
       <c r="R37" t="n">
-        <v>7045886</v>
+        <v>7046137</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4663,9 +4653,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4680,12 +4680,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129602638</v>
+        <v>129602085</v>
       </c>
       <c r="B39" t="n">
-        <v>91851</v>
+        <v>57887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4800,37 +4800,51 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555826</v>
+        <v>555725</v>
       </c>
       <c r="R39" t="n">
-        <v>7045880</v>
+        <v>7046023</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4857,9 +4871,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4874,22 +4898,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129601980</v>
+        <v>129602638</v>
       </c>
       <c r="B40" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4897,21 +4921,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4921,10 +4945,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555724</v>
+        <v>555826</v>
       </c>
       <c r="R40" t="n">
-        <v>7046089</v>
+        <v>7045880</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4983,10 +5007,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129601909</v>
+        <v>129601980</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>91553</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4994,42 +5018,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555726</v>
+        <v>555724</v>
       </c>
       <c r="R41" t="n">
-        <v>7046072</v>
+        <v>7046089</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5056,24 +5075,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5088,74 +5092,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129602085</v>
+        <v>129601485</v>
       </c>
       <c r="B42" t="n">
-        <v>57887</v>
+        <v>80178</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>555725</v>
+        <v>555696</v>
       </c>
       <c r="R42" t="n">
-        <v>7046023</v>
+        <v>7046160</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5182,19 +5172,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5209,60 +5189,65 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129601485</v>
+        <v>129601909</v>
       </c>
       <c r="B43" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>555696</v>
+        <v>555726</v>
       </c>
       <c r="R43" t="n">
-        <v>7046160</v>
+        <v>7046072</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5289,9 +5274,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5306,12 +5306,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5545,45 +5545,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129601971</v>
+        <v>129603244</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555791</v>
+        <v>555877</v>
       </c>
       <c r="R46" t="n">
-        <v>7045965</v>
+        <v>7045808</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5615,7 +5619,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5625,7 +5629,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5759,10 +5763,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129601113</v>
+        <v>129601971</v>
       </c>
       <c r="B48" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5770,21 +5774,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5794,13 +5798,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>555677</v>
+        <v>555791</v>
       </c>
       <c r="R48" t="n">
-        <v>7046225</v>
+        <v>7045965</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5827,9 +5831,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5844,64 +5858,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129603244</v>
+        <v>129601113</v>
       </c>
       <c r="B49" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>555877</v>
+        <v>555677</v>
       </c>
       <c r="R49" t="n">
-        <v>7045808</v>
+        <v>7046225</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5928,19 +5938,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5955,12 +5955,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6078,10 +6078,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129602579</v>
+        <v>129600512</v>
       </c>
       <c r="B51" t="n">
-        <v>78801</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6089,37 +6089,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555842</v>
+        <v>555592</v>
       </c>
       <c r="R51" t="n">
-        <v>7045881</v>
+        <v>7046249</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6146,9 +6151,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6163,65 +6183,69 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129600512</v>
+        <v>129601611</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555592</v>
+        <v>555687</v>
       </c>
       <c r="R52" t="n">
-        <v>7046249</v>
+        <v>7046167</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6250,7 +6274,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6260,12 +6284,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6280,69 +6299,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129601611</v>
+        <v>129602579</v>
       </c>
       <c r="B53" t="n">
-        <v>98727</v>
+        <v>78801</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555687</v>
+        <v>555842</v>
       </c>
       <c r="R53" t="n">
-        <v>7046167</v>
+        <v>7045881</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6369,19 +6379,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>13:41</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6396,64 +6396,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129600692</v>
+        <v>129600139</v>
       </c>
       <c r="B54" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555611</v>
+        <v>555553</v>
       </c>
       <c r="R54" t="n">
-        <v>7046241</v>
+        <v>7046074</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6480,9 +6476,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6497,60 +6503,64 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129600139</v>
+        <v>129600692</v>
       </c>
       <c r="B55" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555553</v>
+        <v>555611</v>
       </c>
       <c r="R55" t="n">
-        <v>7046074</v>
+        <v>7046241</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6577,19 +6587,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6604,44 +6604,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129602952</v>
+        <v>129600865</v>
       </c>
       <c r="B56" t="n">
-        <v>91517</v>
+        <v>91553</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555778</v>
+        <v>555679</v>
       </c>
       <c r="R56" t="n">
-        <v>7045842</v>
+        <v>7046243</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6723,7 +6723,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129600865</v>
+        <v>129602023</v>
       </c>
       <c r="B57" t="n">
         <v>91553</v>
@@ -6758,10 +6758,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555679</v>
+        <v>555819</v>
       </c>
       <c r="R57" t="n">
-        <v>7046243</v>
+        <v>7045946</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6830,10 +6830,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129602023</v>
+        <v>129600317</v>
       </c>
       <c r="B58" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6841,37 +6841,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555819</v>
+        <v>555575</v>
       </c>
       <c r="R58" t="n">
-        <v>7045946</v>
+        <v>7046182</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6898,19 +6898,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6925,22 +6915,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129600317</v>
+        <v>129602459</v>
       </c>
       <c r="B59" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6948,34 +6938,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>555575</v>
+        <v>555835</v>
       </c>
       <c r="R59" t="n">
-        <v>7046182</v>
+        <v>7045881</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7034,10 +7024,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129602459</v>
+        <v>129601480</v>
       </c>
       <c r="B60" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7045,21 +7035,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7069,10 +7059,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>555835</v>
+        <v>555697</v>
       </c>
       <c r="R60" t="n">
-        <v>7045881</v>
+        <v>7046157</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7131,10 +7121,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129602004</v>
+        <v>129602952</v>
       </c>
       <c r="B61" t="n">
-        <v>58097</v>
+        <v>91517</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7142,41 +7132,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555738</v>
+        <v>555778</v>
       </c>
       <c r="R61" t="n">
-        <v>7046093</v>
+        <v>7045842</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7203,9 +7189,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7220,64 +7216,60 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129600524</v>
+        <v>129601061</v>
       </c>
       <c r="B62" t="n">
-        <v>98727</v>
+        <v>80178</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555564</v>
+        <v>555707</v>
       </c>
       <c r="R62" t="n">
-        <v>7046096</v>
+        <v>7046194</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7304,9 +7296,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7321,57 +7323,61 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129601480</v>
+        <v>129602004</v>
       </c>
       <c r="B63" t="n">
-        <v>80149</v>
+        <v>58097</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555697</v>
+        <v>555738</v>
       </c>
       <c r="R63" t="n">
-        <v>7046157</v>
+        <v>7046093</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7430,48 +7436,52 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129601061</v>
+        <v>129600524</v>
       </c>
       <c r="B64" t="n">
-        <v>80178</v>
+        <v>98727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>555707</v>
+        <v>555564</v>
       </c>
       <c r="R64" t="n">
-        <v>7046194</v>
+        <v>7046096</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7498,19 +7508,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7525,22 +7525,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129601012</v>
+        <v>129601936</v>
       </c>
       <c r="B65" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7548,21 +7548,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7572,13 +7572,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>555680</v>
+        <v>555804</v>
       </c>
       <c r="R65" t="n">
-        <v>7046211</v>
+        <v>7046004</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7605,9 +7605,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7622,22 +7632,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129601936</v>
+        <v>129600977</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7645,21 +7655,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7669,10 +7679,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>555804</v>
+        <v>555704</v>
       </c>
       <c r="R66" t="n">
-        <v>7046004</v>
+        <v>7046202</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7704,7 +7714,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7714,7 +7724,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7729,22 +7739,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129600977</v>
+        <v>129601012</v>
       </c>
       <c r="B67" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7752,21 +7762,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7776,13 +7786,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>555704</v>
+        <v>555680</v>
       </c>
       <c r="R67" t="n">
-        <v>7046202</v>
+        <v>7046211</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7809,19 +7819,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:13</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7836,12 +7836,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8072,57 +8072,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129600733</v>
+        <v>129602553</v>
       </c>
       <c r="B70" t="n">
-        <v>98727</v>
+        <v>91851</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>555649</v>
+        <v>555844</v>
       </c>
       <c r="R70" t="n">
-        <v>7046243</v>
+        <v>7045852</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8149,19 +8140,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>13:04</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8176,19 +8157,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129602304</v>
+        <v>129600733</v>
       </c>
       <c r="B71" t="n">
         <v>98727</v>
@@ -8218,19 +8199,24 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>555857</v>
+        <v>555649</v>
       </c>
       <c r="R71" t="n">
-        <v>7045866</v>
+        <v>7046243</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8262,7 +8248,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8272,7 +8258,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8287,57 +8273,61 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129601748</v>
+        <v>129602304</v>
       </c>
       <c r="B72" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>555703</v>
+        <v>555857</v>
       </c>
       <c r="R72" t="n">
-        <v>7046100</v>
+        <v>7045866</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8369,7 +8359,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8379,7 +8369,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8394,12 +8384,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8513,10 +8503,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129602553</v>
+        <v>129601748</v>
       </c>
       <c r="B74" t="n">
-        <v>91851</v>
+        <v>80149</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8524,21 +8514,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8548,13 +8538,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>555844</v>
+        <v>555703</v>
       </c>
       <c r="R74" t="n">
-        <v>7045852</v>
+        <v>7046100</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8581,9 +8571,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8598,12 +8598,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9056,32 +9056,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129601548</v>
+        <v>129600975</v>
       </c>
       <c r="B79" t="n">
-        <v>80177</v>
+        <v>80149</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9091,13 +9091,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>555707</v>
+        <v>555633</v>
       </c>
       <c r="R79" t="n">
-        <v>7046135</v>
+        <v>7046096</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9124,9 +9124,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9141,19 +9151,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129600975</v>
+        <v>129601421</v>
       </c>
       <c r="B80" t="n">
         <v>80149</v>
@@ -9188,10 +9198,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555633</v>
+        <v>555653</v>
       </c>
       <c r="R80" t="n">
-        <v>7046096</v>
+        <v>7046187</v>
       </c>
       <c r="S80" t="n">
         <v>3</v>
@@ -9223,7 +9233,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9233,7 +9243,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9260,7 +9270,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129601421</v>
+        <v>129601148</v>
       </c>
       <c r="B81" t="n">
         <v>80149</v>
@@ -9295,13 +9305,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555653</v>
+        <v>555654</v>
       </c>
       <c r="R81" t="n">
-        <v>7046187</v>
+        <v>7046170</v>
       </c>
       <c r="S81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9330,7 +9340,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9340,7 +9350,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9367,10 +9377,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129601148</v>
+        <v>129603240</v>
       </c>
       <c r="B82" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9378,37 +9388,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555654</v>
+        <v>555865</v>
       </c>
       <c r="R82" t="n">
-        <v>7046170</v>
+        <v>7045842</v>
       </c>
       <c r="S82" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9437,7 +9452,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9447,7 +9462,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9462,60 +9482,64 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129600219</v>
+        <v>129602172</v>
       </c>
       <c r="B83" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555572</v>
+        <v>555855</v>
       </c>
       <c r="R83" t="n">
-        <v>7046181</v>
+        <v>7045892</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9542,9 +9566,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9559,69 +9593,60 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129601945</v>
+        <v>129600219</v>
       </c>
       <c r="B84" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555730</v>
+        <v>555572</v>
       </c>
       <c r="R84" t="n">
-        <v>7046151</v>
+        <v>7046181</v>
       </c>
       <c r="S84" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9648,19 +9673,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>13:53</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9675,65 +9690,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129603240</v>
+        <v>129601548</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>80177</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555865</v>
+        <v>555707</v>
       </c>
       <c r="R85" t="n">
-        <v>7045842</v>
+        <v>7046135</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9760,24 +9770,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9792,19 +9787,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129602172</v>
+        <v>129601945</v>
       </c>
       <c r="B86" t="n">
         <v>98727</v>
@@ -9834,7 +9829,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9843,13 +9843,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>555855</v>
+        <v>555730</v>
       </c>
       <c r="R86" t="n">
-        <v>7045892</v>
+        <v>7046151</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9903,65 +9903,69 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129600090</v>
+        <v>129602716</v>
       </c>
       <c r="B87" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>555491</v>
+        <v>555762</v>
       </c>
       <c r="R87" t="n">
-        <v>7046111</v>
+        <v>7045845</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9990,7 +9994,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10000,12 +10004,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10020,50 +10019,54 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129602108</v>
+        <v>129601760</v>
       </c>
       <c r="B88" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -10072,13 +10075,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>555854</v>
+        <v>555694</v>
       </c>
       <c r="R88" t="n">
-        <v>7045940</v>
+        <v>7046166</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10107,7 +10110,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10117,12 +10120,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10137,12 +10135,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10246,57 +10244,53 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129602716</v>
+        <v>129600090</v>
       </c>
       <c r="B90" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>555762</v>
+        <v>555491</v>
       </c>
       <c r="R90" t="n">
-        <v>7045845</v>
+        <v>7046111</v>
       </c>
       <c r="S90" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10325,7 +10319,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10335,7 +10329,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10350,54 +10349,50 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129601612</v>
+        <v>129602108</v>
       </c>
       <c r="B91" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -10406,10 +10401,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>555675</v>
+        <v>555854</v>
       </c>
       <c r="R91" t="n">
-        <v>7046143</v>
+        <v>7045940</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10441,7 +10436,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10451,7 +10446,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10466,19 +10466,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129603549</v>
+        <v>129601612</v>
       </c>
       <c r="B92" t="n">
         <v>98727</v>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -10522,10 +10522,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>555865</v>
+        <v>555675</v>
       </c>
       <c r="R92" t="n">
-        <v>7045842</v>
+        <v>7046143</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10594,7 +10594,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129601760</v>
+        <v>129603549</v>
       </c>
       <c r="B93" t="n">
         <v>98727</v>
@@ -10624,7 +10624,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -10638,13 +10638,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>555694</v>
+        <v>555865</v>
       </c>
       <c r="R93" t="n">
-        <v>7046166</v>
+        <v>7045842</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10698,69 +10698,60 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129602185</v>
+        <v>129600756</v>
       </c>
       <c r="B94" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>555729</v>
+        <v>555626</v>
       </c>
       <c r="R94" t="n">
-        <v>7045984</v>
+        <v>7046163</v>
       </c>
       <c r="S94" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10787,19 +10778,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>14:07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10814,22 +10795,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129602416</v>
+        <v>129600095</v>
       </c>
       <c r="B95" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10837,42 +10818,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>555801</v>
+        <v>555473</v>
       </c>
       <c r="R95" t="n">
-        <v>7045860</v>
+        <v>7046098</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10899,14 +10875,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10921,22 +10902,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129600756</v>
+        <v>129602416</v>
       </c>
       <c r="B96" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10944,34 +10925,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>555626</v>
+        <v>555801</v>
       </c>
       <c r="R96" t="n">
-        <v>7046163</v>
+        <v>7045860</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -11004,6 +10990,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11137,48 +11128,57 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129600095</v>
+        <v>129602185</v>
       </c>
       <c r="B98" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>555473</v>
+        <v>555729</v>
       </c>
       <c r="R98" t="n">
-        <v>7046098</v>
+        <v>7045984</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11232,22 +11232,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129600791</v>
+        <v>129602252</v>
       </c>
       <c r="B99" t="n">
-        <v>80149</v>
+        <v>91553</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11255,21 +11255,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11279,13 +11279,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>555670</v>
+        <v>555848</v>
       </c>
       <c r="R99" t="n">
-        <v>7046158</v>
+        <v>7045879</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11312,9 +11312,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11329,22 +11339,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129602252</v>
+        <v>129600791</v>
       </c>
       <c r="B100" t="n">
-        <v>91553</v>
+        <v>80149</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11352,21 +11362,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11376,13 +11386,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>555848</v>
+        <v>555670</v>
       </c>
       <c r="R100" t="n">
-        <v>7045879</v>
+        <v>7046158</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11409,19 +11419,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11436,12 +11436,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11682,45 +11682,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129601828</v>
+        <v>129600723</v>
       </c>
       <c r="B103" t="n">
-        <v>91517</v>
+        <v>80149</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>555724</v>
+        <v>555572</v>
       </c>
       <c r="R103" t="n">
-        <v>7046097</v>
+        <v>7046171</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -11779,10 +11779,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129601607</v>
+        <v>129600507</v>
       </c>
       <c r="B104" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11790,37 +11790,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>555709</v>
+        <v>555608</v>
       </c>
       <c r="R104" t="n">
-        <v>7046133</v>
+        <v>7046222</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11847,9 +11847,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11864,22 +11874,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129600723</v>
+        <v>129601607</v>
       </c>
       <c r="B105" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11887,34 +11897,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>555572</v>
+        <v>555709</v>
       </c>
       <c r="R105" t="n">
-        <v>7046171</v>
+        <v>7046133</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11973,48 +11983,48 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129600507</v>
+        <v>129601828</v>
       </c>
       <c r="B106" t="n">
-        <v>80149</v>
+        <v>91517</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>555608</v>
+        <v>555724</v>
       </c>
       <c r="R106" t="n">
-        <v>7046222</v>
+        <v>7046097</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12041,19 +12051,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12068,50 +12068,49 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129602456</v>
+        <v>129600807</v>
       </c>
       <c r="B107" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -12120,13 +12119,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>555809</v>
+        <v>555633</v>
       </c>
       <c r="R107" t="n">
-        <v>7045823</v>
+        <v>7046097</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12155,7 +12154,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12165,7 +12164,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12180,50 +12179,54 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129601709</v>
+        <v>129602437</v>
       </c>
       <c r="B108" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -12232,13 +12235,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>555739</v>
+        <v>555757</v>
       </c>
       <c r="R108" t="n">
-        <v>7046139</v>
+        <v>7045907</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12267,7 +12270,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12277,12 +12280,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12297,54 +12295,50 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129602437</v>
+        <v>129602456</v>
       </c>
       <c r="B109" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -12353,13 +12347,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>555757</v>
+        <v>555809</v>
       </c>
       <c r="R109" t="n">
-        <v>7045907</v>
+        <v>7045823</v>
       </c>
       <c r="S109" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12388,7 +12382,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12398,7 +12392,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12413,49 +12407,50 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129600807</v>
+        <v>129601709</v>
       </c>
       <c r="B110" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -12464,13 +12459,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>555633</v>
+        <v>555739</v>
       </c>
       <c r="R110" t="n">
-        <v>7046097</v>
+        <v>7046139</v>
       </c>
       <c r="S110" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12499,7 +12494,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12509,7 +12504,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12524,12 +12524,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -12730,7 +12730,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129600513</v>
+        <v>129600022</v>
       </c>
       <c r="B113" t="n">
         <v>98727</v>
@@ -12763,24 +12763,19 @@
           <t>50</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>555590</v>
+        <v>555560</v>
       </c>
       <c r="R113" t="n">
-        <v>7046134</v>
+        <v>7046091</v>
       </c>
       <c r="S113" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12807,19 +12802,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12834,19 +12819,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129600022</v>
+        <v>129601553</v>
       </c>
       <c r="B114" t="n">
         <v>98727</v>
@@ -12876,22 +12861,22 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>555560</v>
+        <v>555704</v>
       </c>
       <c r="R114" t="n">
-        <v>7046091</v>
+        <v>7046148</v>
       </c>
       <c r="S114" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12918,9 +12903,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12935,19 +12930,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129601553</v>
+        <v>129600513</v>
       </c>
       <c r="B115" t="n">
         <v>98727</v>
@@ -12977,22 +12972,27 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>555704</v>
+        <v>555590</v>
       </c>
       <c r="R115" t="n">
-        <v>7046148</v>
+        <v>7046134</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13031,7 +13031,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13046,12 +13046,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
@@ -13165,45 +13165,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129600727</v>
+        <v>129600845</v>
       </c>
       <c r="B117" t="n">
-        <v>80178</v>
+        <v>80149</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>555605</v>
+        <v>555681</v>
       </c>
       <c r="R117" t="n">
-        <v>7046222</v>
+        <v>7046162</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13262,45 +13262,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129600845</v>
+        <v>129600727</v>
       </c>
       <c r="B118" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>555681</v>
+        <v>555605</v>
       </c>
       <c r="R118" t="n">
-        <v>7046162</v>
+        <v>7046222</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3056,7 +3056,7 @@
         <v>129298314</v>
       </c>
       <c r="B23" t="n">
-        <v>80150</v>
+        <v>80176</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>129298193</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129298243</v>
       </c>
       <c r="B25" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>129298267</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>129298152</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3616,10 +3616,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298285</v>
+        <v>129298204</v>
       </c>
       <c r="B28" t="n">
-        <v>91851</v>
+        <v>79070</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3627,21 +3627,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555760</v>
+        <v>555763</v>
       </c>
       <c r="R28" t="n">
-        <v>7045817</v>
+        <v>7045835</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3723,10 +3723,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298204</v>
+        <v>129298285</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>91879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3734,21 +3734,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555763</v>
+        <v>555760</v>
       </c>
       <c r="R29" t="n">
-        <v>7045835</v>
+        <v>7045817</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3830,48 +3830,52 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129602332</v>
+        <v>129602260</v>
       </c>
       <c r="B30" t="n">
-        <v>80149</v>
+        <v>98756</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555835</v>
+        <v>555747</v>
       </c>
       <c r="R30" t="n">
-        <v>7045850</v>
+        <v>7045963</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3898,19 +3902,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3925,22 +3919,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129602260</v>
+        <v>129600015</v>
       </c>
       <c r="B31" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3967,22 +3961,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555747</v>
+        <v>555553</v>
       </c>
       <c r="R31" t="n">
-        <v>7045963</v>
+        <v>7046074</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4009,9 +4008,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4026,69 +4035,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129600015</v>
+        <v>129602332</v>
       </c>
       <c r="B32" t="n">
-        <v>98727</v>
+        <v>80175</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555553</v>
+        <v>555835</v>
       </c>
       <c r="R32" t="n">
-        <v>7046074</v>
+        <v>7045850</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4142,12 +4142,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4157,7 +4157,7 @@
         <v>129601128</v>
       </c>
       <c r="B33" t="n">
-        <v>80178</v>
+        <v>80204</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>129602543</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>129602488</v>
       </c>
       <c r="B35" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4465,10 +4465,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129602548</v>
+        <v>129601775</v>
       </c>
       <c r="B36" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4495,12 +4495,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4509,13 +4504,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555770</v>
+        <v>555746</v>
       </c>
       <c r="R36" t="n">
-        <v>7045888</v>
+        <v>7046137</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4544,7 +4539,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4554,7 +4549,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4569,22 +4564,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129601775</v>
+        <v>129602548</v>
       </c>
       <c r="B37" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4611,7 +4606,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4620,13 +4620,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555746</v>
+        <v>555770</v>
       </c>
       <c r="R37" t="n">
-        <v>7046137</v>
+        <v>7045888</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4680,22 +4680,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129602219</v>
+        <v>129602638</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>91879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4703,21 +4703,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555697</v>
+        <v>555826</v>
       </c>
       <c r="R38" t="n">
-        <v>7045963</v>
+        <v>7045880</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129602085</v>
+        <v>129601980</v>
       </c>
       <c r="B39" t="n">
-        <v>57887</v>
+        <v>91581</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4800,51 +4800,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555725</v>
+        <v>555724</v>
       </c>
       <c r="R39" t="n">
-        <v>7046023</v>
+        <v>7046089</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4871,19 +4857,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4898,44 +4874,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129602638</v>
+        <v>129601485</v>
       </c>
       <c r="B40" t="n">
-        <v>91851</v>
+        <v>80204</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4945,10 +4921,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555826</v>
+        <v>555696</v>
       </c>
       <c r="R40" t="n">
-        <v>7045880</v>
+        <v>7046160</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5007,10 +4983,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129601980</v>
+        <v>129602219</v>
       </c>
       <c r="B41" t="n">
-        <v>91553</v>
+        <v>79070</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5018,21 +4994,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5042,10 +5018,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555724</v>
+        <v>555697</v>
       </c>
       <c r="R41" t="n">
-        <v>7046089</v>
+        <v>7045963</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5104,48 +5080,53 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129601485</v>
+        <v>129601909</v>
       </c>
       <c r="B42" t="n">
-        <v>80178</v>
+        <v>57730</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>555696</v>
+        <v>555726</v>
       </c>
       <c r="R42" t="n">
-        <v>7046160</v>
+        <v>7046072</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5172,9 +5153,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5189,22 +5185,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129601909</v>
+        <v>129602085</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>57890</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5212,27 +5208,36 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5241,10 +5246,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>555726</v>
+        <v>555725</v>
       </c>
       <c r="R43" t="n">
-        <v>7046072</v>
+        <v>7046023</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5276,7 +5281,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5286,12 +5291,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5321,7 +5321,7 @@
         <v>129600463</v>
       </c>
       <c r="B44" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>129602321</v>
       </c>
       <c r="B45" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5545,52 +5545,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129603244</v>
+        <v>129600640</v>
       </c>
       <c r="B46" t="n">
-        <v>98727</v>
+        <v>80175</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555877</v>
+        <v>555615</v>
       </c>
       <c r="R46" t="n">
-        <v>7045808</v>
+        <v>7046128</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5619,7 +5615,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5629,7 +5625,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5644,22 +5640,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129600640</v>
+        <v>129601113</v>
       </c>
       <c r="B47" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5691,13 +5687,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555615</v>
+        <v>555677</v>
       </c>
       <c r="R47" t="n">
-        <v>7046128</v>
+        <v>7046225</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5724,19 +5720,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5751,12 +5737,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5766,7 +5752,7 @@
         <v>129601971</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5870,48 +5856,52 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129601113</v>
+        <v>129603244</v>
       </c>
       <c r="B49" t="n">
-        <v>80149</v>
+        <v>98756</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>555677</v>
+        <v>555877</v>
       </c>
       <c r="R49" t="n">
-        <v>7046225</v>
+        <v>7045808</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5938,9 +5928,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5955,12 +5955,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5970,7 +5970,7 @@
         <v>129602134</v>
       </c>
       <c r="B50" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6078,10 +6078,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129600512</v>
+        <v>129602579</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>78827</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6089,42 +6089,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555592</v>
+        <v>555842</v>
       </c>
       <c r="R51" t="n">
-        <v>7046249</v>
+        <v>7045881</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6151,24 +6146,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6183,69 +6163,65 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129601611</v>
+        <v>129600512</v>
       </c>
       <c r="B52" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555687</v>
+        <v>555592</v>
       </c>
       <c r="R52" t="n">
-        <v>7046167</v>
+        <v>7046249</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6274,7 +6250,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6284,7 +6260,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6299,60 +6280,69 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129602579</v>
+        <v>129601611</v>
       </c>
       <c r="B53" t="n">
-        <v>78801</v>
+        <v>98756</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555842</v>
+        <v>555687</v>
       </c>
       <c r="R53" t="n">
-        <v>7045881</v>
+        <v>7046167</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6379,9 +6369,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6396,60 +6396,64 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129600139</v>
+        <v>129600692</v>
       </c>
       <c r="B54" t="n">
-        <v>80149</v>
+        <v>98756</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555553</v>
+        <v>555611</v>
       </c>
       <c r="R54" t="n">
-        <v>7046074</v>
+        <v>7046241</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6476,19 +6480,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6503,64 +6497,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129600692</v>
+        <v>129600139</v>
       </c>
       <c r="B55" t="n">
-        <v>98727</v>
+        <v>80175</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555611</v>
+        <v>555553</v>
       </c>
       <c r="R55" t="n">
-        <v>7046241</v>
+        <v>7046074</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6587,9 +6577,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6604,12 +6604,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6619,7 +6619,7 @@
         <v>129600865</v>
       </c>
       <c r="B56" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>129602023</v>
       </c>
       <c r="B57" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
         <v>129600317</v>
       </c>
       <c r="B58" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>129602459</v>
       </c>
       <c r="B59" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7024,32 +7024,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129601480</v>
+        <v>129601061</v>
       </c>
       <c r="B60" t="n">
-        <v>80149</v>
+        <v>80204</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7059,13 +7059,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>555697</v>
+        <v>555707</v>
       </c>
       <c r="R60" t="n">
-        <v>7046157</v>
+        <v>7046194</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7092,9 +7092,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7109,44 +7119,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129602952</v>
+        <v>129601480</v>
       </c>
       <c r="B61" t="n">
-        <v>91517</v>
+        <v>80175</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7156,13 +7166,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555778</v>
+        <v>555697</v>
       </c>
       <c r="R61" t="n">
-        <v>7045842</v>
+        <v>7046157</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7189,19 +7199,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>14:49</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7216,22 +7216,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129601061</v>
+        <v>129602952</v>
       </c>
       <c r="B62" t="n">
-        <v>80178</v>
+        <v>91545</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7239,21 +7239,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7263,10 +7263,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555707</v>
+        <v>555778</v>
       </c>
       <c r="R62" t="n">
-        <v>7046194</v>
+        <v>7045842</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7323,12 +7323,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7338,7 +7338,7 @@
         <v>129602004</v>
       </c>
       <c r="B63" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>129600524</v>
       </c>
       <c r="B64" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7537,10 +7537,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129601936</v>
+        <v>129601541</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7548,37 +7548,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>555804</v>
+        <v>555702</v>
       </c>
       <c r="R65" t="n">
-        <v>7046004</v>
+        <v>7046142</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7605,19 +7610,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:57</t>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7632,22 +7632,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129600977</v>
+        <v>129602371</v>
       </c>
       <c r="B66" t="n">
-        <v>80149</v>
+        <v>57730</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7655,34 +7655,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>555704</v>
+        <v>555825</v>
       </c>
       <c r="R66" t="n">
-        <v>7046202</v>
+        <v>7045806</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7714,7 +7719,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7724,7 +7729,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7739,12 +7749,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7754,7 +7764,7 @@
         <v>129601012</v>
       </c>
       <c r="B67" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7848,10 +7858,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129601541</v>
+        <v>129600977</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7859,42 +7869,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>555702</v>
+        <v>555704</v>
       </c>
       <c r="R68" t="n">
-        <v>7046142</v>
+        <v>7046202</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7921,14 +7926,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7943,22 +7953,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129602371</v>
+        <v>129601936</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7966,39 +7976,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>555825</v>
+        <v>555804</v>
       </c>
       <c r="R69" t="n">
-        <v>7045806</v>
+        <v>7046004</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8030,7 +8035,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8040,12 +8045,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8075,7 +8075,7 @@
         <v>129602553</v>
       </c>
       <c r="B70" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8169,54 +8169,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129600733</v>
+        <v>129601748</v>
       </c>
       <c r="B71" t="n">
-        <v>98727</v>
+        <v>80175</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>555649</v>
+        <v>555703</v>
       </c>
       <c r="R71" t="n">
-        <v>7046243</v>
+        <v>7046100</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8248,7 +8239,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8258,7 +8249,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8285,49 +8276,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129602304</v>
+        <v>129601725</v>
       </c>
       <c r="B72" t="n">
-        <v>98727</v>
+        <v>80175</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>555857</v>
+        <v>555750</v>
       </c>
       <c r="R72" t="n">
-        <v>7045866</v>
+        <v>7046140</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8359,7 +8346,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8369,7 +8356,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8396,45 +8383,49 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129601725</v>
+        <v>129602304</v>
       </c>
       <c r="B73" t="n">
-        <v>80149</v>
+        <v>98756</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>555750</v>
+        <v>555857</v>
       </c>
       <c r="R73" t="n">
-        <v>7046140</v>
+        <v>7045866</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8466,7 +8457,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8476,7 +8467,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8503,45 +8494,54 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129601748</v>
+        <v>129600733</v>
       </c>
       <c r="B74" t="n">
-        <v>80149</v>
+        <v>98756</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>555703</v>
+        <v>555649</v>
       </c>
       <c r="R74" t="n">
-        <v>7046100</v>
+        <v>7046243</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8613,7 +8613,7 @@
         <v>129600581</v>
       </c>
       <c r="B75" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>129602315</v>
       </c>
       <c r="B76" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>129601872</v>
       </c>
       <c r="B77" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>129602094</v>
       </c>
       <c r="B78" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9056,10 +9056,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129600975</v>
+        <v>129600219</v>
       </c>
       <c r="B79" t="n">
-        <v>80149</v>
+        <v>91581</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9067,37 +9067,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>555633</v>
+        <v>555572</v>
       </c>
       <c r="R79" t="n">
-        <v>7046096</v>
+        <v>7046181</v>
       </c>
       <c r="S79" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9124,19 +9124,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:13</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9151,22 +9141,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129601421</v>
+        <v>129600975</v>
       </c>
       <c r="B80" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9198,10 +9188,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555653</v>
+        <v>555633</v>
       </c>
       <c r="R80" t="n">
-        <v>7046187</v>
+        <v>7046096</v>
       </c>
       <c r="S80" t="n">
         <v>3</v>
@@ -9233,7 +9223,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9243,7 +9233,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9273,7 +9263,7 @@
         <v>129601148</v>
       </c>
       <c r="B81" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9377,10 +9367,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129603240</v>
+        <v>129601421</v>
       </c>
       <c r="B82" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9388,42 +9378,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555865</v>
+        <v>555653</v>
       </c>
       <c r="R82" t="n">
-        <v>7045842</v>
+        <v>7046187</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9452,7 +9437,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9462,12 +9447,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9482,64 +9462,60 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129602172</v>
+        <v>129601548</v>
       </c>
       <c r="B83" t="n">
-        <v>98727</v>
+        <v>80203</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555855</v>
+        <v>555707</v>
       </c>
       <c r="R83" t="n">
-        <v>7045892</v>
+        <v>7046135</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9566,19 +9542,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9593,22 +9559,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129600219</v>
+        <v>129603240</v>
       </c>
       <c r="B84" t="n">
-        <v>91553</v>
+        <v>57730</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9616,37 +9582,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555572</v>
+        <v>555865</v>
       </c>
       <c r="R84" t="n">
-        <v>7046181</v>
+        <v>7045842</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9673,9 +9644,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9690,60 +9676,64 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129601548</v>
+        <v>129602172</v>
       </c>
       <c r="B85" t="n">
-        <v>80177</v>
+        <v>98756</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555707</v>
+        <v>555855</v>
       </c>
       <c r="R85" t="n">
-        <v>7046135</v>
+        <v>7045892</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9770,9 +9760,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9787,12 +9787,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9802,7 +9802,7 @@
         <v>129601945</v>
       </c>
       <c r="B86" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9915,57 +9915,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129602716</v>
+        <v>129602154</v>
       </c>
       <c r="B87" t="n">
-        <v>98727</v>
+        <v>91581</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>555762</v>
+        <v>555676</v>
       </c>
       <c r="R87" t="n">
-        <v>7045845</v>
+        <v>7045998</v>
       </c>
       <c r="S87" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9992,19 +9983,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10019,22 +10000,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129601760</v>
+        <v>129602716</v>
       </c>
       <c r="B88" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10061,7 +10042,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10075,13 +10056,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>555694</v>
+        <v>555762</v>
       </c>
       <c r="R88" t="n">
-        <v>7046166</v>
+        <v>7045845</v>
       </c>
       <c r="S88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10110,7 +10091,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10120,7 +10101,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10147,48 +10128,57 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129602154</v>
+        <v>129601612</v>
       </c>
       <c r="B89" t="n">
-        <v>91553</v>
+        <v>98756</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>555676</v>
+        <v>555675</v>
       </c>
       <c r="R89" t="n">
-        <v>7045998</v>
+        <v>7046143</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10215,9 +10205,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10232,62 +10232,66 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129600090</v>
+        <v>129603549</v>
       </c>
       <c r="B90" t="n">
-        <v>57727</v>
+        <v>98756</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>555491</v>
+        <v>555865</v>
       </c>
       <c r="R90" t="n">
-        <v>7046111</v>
+        <v>7045842</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10319,7 +10323,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10329,12 +10333,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10361,38 +10360,42 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129602108</v>
+        <v>129601760</v>
       </c>
       <c r="B91" t="n">
-        <v>57727</v>
+        <v>98756</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -10401,13 +10404,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>555854</v>
+        <v>555694</v>
       </c>
       <c r="R91" t="n">
-        <v>7045940</v>
+        <v>7046166</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10436,7 +10439,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10446,12 +10449,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10466,66 +10464,62 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129601612</v>
+        <v>129600090</v>
       </c>
       <c r="B92" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>555675</v>
+        <v>555491</v>
       </c>
       <c r="R92" t="n">
-        <v>7046143</v>
+        <v>7046111</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10557,7 +10551,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10567,7 +10561,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10594,42 +10593,38 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129603549</v>
+        <v>129602108</v>
       </c>
       <c r="B93" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10638,10 +10633,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>555865</v>
+        <v>555854</v>
       </c>
       <c r="R93" t="n">
-        <v>7045842</v>
+        <v>7045940</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10673,7 +10668,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10683,7 +10678,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10698,22 +10698,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129600756</v>
+        <v>129602416</v>
       </c>
       <c r="B94" t="n">
-        <v>80149</v>
+        <v>57730</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10721,34 +10721,39 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>555626</v>
+        <v>555801</v>
       </c>
       <c r="R94" t="n">
-        <v>7046163</v>
+        <v>7045860</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10781,6 +10786,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10807,10 +10817,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129600095</v>
+        <v>129602047</v>
       </c>
       <c r="B95" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10838,14 +10848,14 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>555473</v>
+        <v>555722</v>
       </c>
       <c r="R95" t="n">
-        <v>7046098</v>
+        <v>7046017</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10877,7 +10887,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10887,7 +10897,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10902,22 +10912,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129602416</v>
+        <v>129600756</v>
       </c>
       <c r="B96" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10925,39 +10935,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>555801</v>
+        <v>555626</v>
       </c>
       <c r="R96" t="n">
-        <v>7045860</v>
+        <v>7046163</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10990,11 +10995,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11021,10 +11021,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129602047</v>
+        <v>129600095</v>
       </c>
       <c r="B97" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11052,14 +11052,14 @@
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>555722</v>
+        <v>555473</v>
       </c>
       <c r="R97" t="n">
-        <v>7046017</v>
+        <v>7046098</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11116,12 +11116,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -11131,7 +11131,7 @@
         <v>129602185</v>
       </c>
       <c r="B98" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11244,10 +11244,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129602252</v>
+        <v>129600791</v>
       </c>
       <c r="B99" t="n">
-        <v>91553</v>
+        <v>80175</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11255,21 +11255,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11279,13 +11279,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>555848</v>
+        <v>555670</v>
       </c>
       <c r="R99" t="n">
-        <v>7045879</v>
+        <v>7046158</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11312,19 +11312,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11339,22 +11329,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129600791</v>
+        <v>129602252</v>
       </c>
       <c r="B100" t="n">
-        <v>80149</v>
+        <v>91581</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11362,21 +11352,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11386,13 +11376,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>555670</v>
+        <v>555848</v>
       </c>
       <c r="R100" t="n">
-        <v>7046158</v>
+        <v>7045879</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11419,9 +11409,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11436,12 +11436,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11451,7 +11451,7 @@
         <v>129601948</v>
       </c>
       <c r="B101" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>129600129</v>
       </c>
       <c r="B102" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>129600723</v>
       </c>
       <c r="B103" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>129600507</v>
       </c>
       <c r="B104" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11886,32 +11886,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129601607</v>
+        <v>129601828</v>
       </c>
       <c r="B105" t="n">
-        <v>79044</v>
+        <v>91545</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11921,10 +11921,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>555709</v>
+        <v>555724</v>
       </c>
       <c r="R105" t="n">
-        <v>7046133</v>
+        <v>7046097</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11983,32 +11983,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129601828</v>
+        <v>129601607</v>
       </c>
       <c r="B106" t="n">
-        <v>91517</v>
+        <v>79070</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12018,10 +12018,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>555724</v>
+        <v>555709</v>
       </c>
       <c r="R106" t="n">
-        <v>7046097</v>
+        <v>7046133</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -12080,37 +12080,38 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129600807</v>
+        <v>129601709</v>
       </c>
       <c r="B107" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -12119,13 +12120,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>555633</v>
+        <v>555739</v>
       </c>
       <c r="R107" t="n">
-        <v>7046097</v>
+        <v>7046139</v>
       </c>
       <c r="S107" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12154,7 +12155,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12164,7 +12165,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12179,12 +12185,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -12194,7 +12200,7 @@
         <v>129602437</v>
       </c>
       <c r="B108" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12307,38 +12313,37 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129602456</v>
+        <v>129600807</v>
       </c>
       <c r="B109" t="n">
-        <v>57724</v>
+        <v>98756</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -12347,13 +12352,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>555809</v>
+        <v>555633</v>
       </c>
       <c r="R109" t="n">
-        <v>7045823</v>
+        <v>7046097</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12382,7 +12387,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12392,7 +12397,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12407,19 +12412,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129601709</v>
+        <v>129602456</v>
       </c>
       <c r="B110" t="n">
         <v>57727</v>
@@ -12430,16 +12435,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -12450,7 +12455,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -12459,10 +12464,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>555739</v>
+        <v>555809</v>
       </c>
       <c r="R110" t="n">
-        <v>7046139</v>
+        <v>7045823</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12494,7 +12499,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12504,12 +12509,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12539,7 +12539,7 @@
         <v>129601521</v>
       </c>
       <c r="B111" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
         <v>129601528</v>
       </c>
       <c r="B112" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>129600022</v>
       </c>
       <c r="B113" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>129601553</v>
       </c>
       <c r="B114" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>129600513</v>
       </c>
       <c r="B115" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>129602472</v>
       </c>
       <c r="B116" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13165,45 +13165,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129600845</v>
+        <v>129600727</v>
       </c>
       <c r="B117" t="n">
-        <v>80149</v>
+        <v>80204</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>555681</v>
+        <v>555605</v>
       </c>
       <c r="R117" t="n">
-        <v>7046162</v>
+        <v>7046222</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13262,45 +13262,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129600727</v>
+        <v>129600845</v>
       </c>
       <c r="B118" t="n">
-        <v>80178</v>
+        <v>80175</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>555605</v>
+        <v>555681</v>
       </c>
       <c r="R118" t="n">
-        <v>7046222</v>
+        <v>7046162</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13362,7 +13362,7 @@
         <v>129602025</v>
       </c>
       <c r="B119" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>129602058</v>
       </c>
       <c r="B120" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13567,10 +13567,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129602598</v>
+        <v>129600175</v>
       </c>
       <c r="B121" t="n">
-        <v>80149</v>
+        <v>57730</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13578,37 +13578,42 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>555768</v>
+        <v>555493</v>
       </c>
       <c r="R121" t="n">
-        <v>7045841</v>
+        <v>7046125</v>
       </c>
       <c r="S121" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13637,7 +13642,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13647,7 +13652,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13662,22 +13672,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129600175</v>
+        <v>129600621</v>
       </c>
       <c r="B122" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13705,7 +13715,7 @@
       <c r="I122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -13714,13 +13724,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>555493</v>
+        <v>555635</v>
       </c>
       <c r="R122" t="n">
-        <v>7046125</v>
+        <v>7046219</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13747,24 +13757,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13779,22 +13779,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129600621</v>
+        <v>129600978</v>
       </c>
       <c r="B123" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13822,22 +13822,22 @@
       <c r="I123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>555635</v>
+        <v>555668</v>
       </c>
       <c r="R123" t="n">
-        <v>7046219</v>
+        <v>7046211</v>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13864,14 +13864,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack, gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13886,22 +13896,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129600978</v>
+        <v>129602598</v>
       </c>
       <c r="B124" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13909,42 +13919,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>555668</v>
+        <v>555768</v>
       </c>
       <c r="R124" t="n">
-        <v>7046211</v>
+        <v>7045841</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13973,7 +13978,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13983,12 +13988,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14003,12 +14003,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -14018,7 +14018,7 @@
         <v>129601920</v>
       </c>
       <c r="B125" t="n">
-        <v>92036</v>
+        <v>92064</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3830,52 +3830,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129602260</v>
+        <v>129602332</v>
       </c>
       <c r="B30" t="n">
-        <v>98756</v>
+        <v>80175</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555747</v>
+        <v>555835</v>
       </c>
       <c r="R30" t="n">
-        <v>7045963</v>
+        <v>7045850</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3902,9 +3898,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3919,69 +3925,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129600015</v>
+        <v>129601128</v>
       </c>
       <c r="B31" t="n">
-        <v>98756</v>
+        <v>80204</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555553</v>
+        <v>555698</v>
       </c>
       <c r="R31" t="n">
-        <v>7046074</v>
+        <v>7046187</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4008,19 +4005,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,22 +4022,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129602332</v>
+        <v>129602543</v>
       </c>
       <c r="B32" t="n">
-        <v>80175</v>
+        <v>57730</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4058,34 +4045,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555835</v>
+        <v>555769</v>
       </c>
       <c r="R32" t="n">
-        <v>7045850</v>
+        <v>7045881</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4117,7 +4109,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4127,7 +4119,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4142,57 +4139,61 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129601128</v>
+        <v>129602260</v>
       </c>
       <c r="B33" t="n">
-        <v>80204</v>
+        <v>98756</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555698</v>
+        <v>555747</v>
       </c>
       <c r="R33" t="n">
-        <v>7046187</v>
+        <v>7045963</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4251,53 +4252,57 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129602543</v>
+        <v>129600015</v>
       </c>
       <c r="B34" t="n">
-        <v>57730</v>
+        <v>98756</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555769</v>
+        <v>555553</v>
       </c>
       <c r="R34" t="n">
-        <v>7045881</v>
+        <v>7046074</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4326,7 +4331,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4336,12 +4341,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4356,12 +4356,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -6078,48 +6078,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129602579</v>
+        <v>129601611</v>
       </c>
       <c r="B51" t="n">
-        <v>78827</v>
+        <v>98756</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555842</v>
+        <v>555687</v>
       </c>
       <c r="R51" t="n">
-        <v>7045881</v>
+        <v>7046167</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6146,9 +6155,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6163,22 +6182,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129600512</v>
+        <v>129602579</v>
       </c>
       <c r="B52" t="n">
-        <v>57730</v>
+        <v>78827</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6186,42 +6205,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555592</v>
+        <v>555842</v>
       </c>
       <c r="R52" t="n">
-        <v>7046249</v>
+        <v>7045881</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6248,24 +6262,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6280,69 +6279,65 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129601611</v>
+        <v>129600512</v>
       </c>
       <c r="B53" t="n">
-        <v>98756</v>
+        <v>57730</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555687</v>
+        <v>555592</v>
       </c>
       <c r="R53" t="n">
-        <v>7046167</v>
+        <v>7046249</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6371,7 +6366,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6381,7 +6376,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6396,64 +6396,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129600692</v>
+        <v>129600139</v>
       </c>
       <c r="B54" t="n">
-        <v>98756</v>
+        <v>80175</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555611</v>
+        <v>555553</v>
       </c>
       <c r="R54" t="n">
-        <v>7046241</v>
+        <v>7046074</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6480,9 +6476,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6497,60 +6503,64 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129600139</v>
+        <v>129600692</v>
       </c>
       <c r="B55" t="n">
-        <v>80175</v>
+        <v>98756</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555553</v>
+        <v>555611</v>
       </c>
       <c r="R55" t="n">
-        <v>7046074</v>
+        <v>7046241</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6577,19 +6587,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6604,12 +6604,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7537,10 +7537,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129601541</v>
+        <v>129601012</v>
       </c>
       <c r="B65" t="n">
-        <v>57730</v>
+        <v>91581</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7548,39 +7548,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>555702</v>
+        <v>555680</v>
       </c>
       <c r="R65" t="n">
-        <v>7046142</v>
+        <v>7046211</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7613,11 +7608,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7644,10 +7634,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129602371</v>
+        <v>129600977</v>
       </c>
       <c r="B66" t="n">
-        <v>57730</v>
+        <v>80175</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7655,39 +7645,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>555825</v>
+        <v>555704</v>
       </c>
       <c r="R66" t="n">
-        <v>7045806</v>
+        <v>7046202</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7719,7 +7704,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7729,12 +7714,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7749,22 +7729,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129601012</v>
+        <v>129601936</v>
       </c>
       <c r="B67" t="n">
-        <v>91581</v>
+        <v>79070</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7772,21 +7752,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7796,13 +7776,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>555680</v>
+        <v>555804</v>
       </c>
       <c r="R67" t="n">
-        <v>7046211</v>
+        <v>7046004</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7829,9 +7809,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7846,22 +7836,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129600977</v>
+        <v>129601541</v>
       </c>
       <c r="B68" t="n">
-        <v>80175</v>
+        <v>57730</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7869,37 +7859,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>555704</v>
+        <v>555702</v>
       </c>
       <c r="R68" t="n">
-        <v>7046202</v>
+        <v>7046142</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7926,19 +7921,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>13:13</t>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7953,22 +7943,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129601936</v>
+        <v>129602371</v>
       </c>
       <c r="B69" t="n">
-        <v>79070</v>
+        <v>57730</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7976,34 +7966,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>555804</v>
+        <v>555825</v>
       </c>
       <c r="R69" t="n">
-        <v>7046004</v>
+        <v>7045806</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8035,7 +8030,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8045,7 +8040,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8721,10 +8721,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129602315</v>
+        <v>129601872</v>
       </c>
       <c r="B76" t="n">
-        <v>79070</v>
+        <v>57730</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8732,37 +8732,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>555729</v>
+        <v>555721</v>
       </c>
       <c r="R76" t="n">
-        <v>7045970</v>
+        <v>7046072</v>
       </c>
       <c r="S76" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8791,7 +8796,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8801,7 +8806,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8816,22 +8826,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129601872</v>
+        <v>129602315</v>
       </c>
       <c r="B77" t="n">
-        <v>57730</v>
+        <v>79070</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8839,42 +8849,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>555721</v>
+        <v>555729</v>
       </c>
       <c r="R77" t="n">
-        <v>7046072</v>
+        <v>7045970</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8903,7 +8908,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8913,12 +8918,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8933,12 +8933,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9056,10 +9056,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129600219</v>
+        <v>129603240</v>
       </c>
       <c r="B79" t="n">
-        <v>91581</v>
+        <v>57730</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9067,37 +9067,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>555572</v>
+        <v>555865</v>
       </c>
       <c r="R79" t="n">
-        <v>7046181</v>
+        <v>7045842</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9124,9 +9129,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9141,60 +9161,64 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129600975</v>
+        <v>129602172</v>
       </c>
       <c r="B80" t="n">
-        <v>80175</v>
+        <v>98756</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555633</v>
+        <v>555855</v>
       </c>
       <c r="R80" t="n">
-        <v>7046096</v>
+        <v>7045892</v>
       </c>
       <c r="S80" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9223,7 +9247,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9233,7 +9257,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9248,60 +9272,69 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129601148</v>
+        <v>129601945</v>
       </c>
       <c r="B81" t="n">
-        <v>80175</v>
+        <v>98756</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555654</v>
+        <v>555730</v>
       </c>
       <c r="R81" t="n">
-        <v>7046170</v>
+        <v>7046151</v>
       </c>
       <c r="S81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9330,7 +9363,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9340,7 +9373,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9367,10 +9400,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129601421</v>
+        <v>129600219</v>
       </c>
       <c r="B82" t="n">
-        <v>80175</v>
+        <v>91581</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9378,37 +9411,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555653</v>
+        <v>555572</v>
       </c>
       <c r="R82" t="n">
-        <v>7046187</v>
+        <v>7046181</v>
       </c>
       <c r="S82" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9435,19 +9468,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9462,44 +9485,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129601548</v>
+        <v>129600975</v>
       </c>
       <c r="B83" t="n">
-        <v>80203</v>
+        <v>80175</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9509,13 +9532,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555707</v>
+        <v>555633</v>
       </c>
       <c r="R83" t="n">
-        <v>7046135</v>
+        <v>7046096</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9542,9 +9565,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9559,22 +9592,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129603240</v>
+        <v>129601148</v>
       </c>
       <c r="B84" t="n">
-        <v>57730</v>
+        <v>80175</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9582,42 +9615,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555865</v>
+        <v>555654</v>
       </c>
       <c r="R84" t="n">
-        <v>7045842</v>
+        <v>7046170</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9646,7 +9674,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9656,12 +9684,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9676,64 +9699,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129602172</v>
+        <v>129601421</v>
       </c>
       <c r="B85" t="n">
-        <v>98756</v>
+        <v>80175</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555855</v>
+        <v>555653</v>
       </c>
       <c r="R85" t="n">
-        <v>7045892</v>
+        <v>7046187</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9762,7 +9781,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9772,7 +9791,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9787,69 +9806,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129601945</v>
+        <v>129601548</v>
       </c>
       <c r="B86" t="n">
-        <v>98756</v>
+        <v>80203</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>555730</v>
+        <v>555707</v>
       </c>
       <c r="R86" t="n">
-        <v>7046151</v>
+        <v>7046135</v>
       </c>
       <c r="S86" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9876,19 +9886,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>13:53</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9903,12 +9903,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -10710,10 +10710,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129602416</v>
+        <v>129602047</v>
       </c>
       <c r="B94" t="n">
-        <v>57730</v>
+        <v>79070</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10721,42 +10721,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>555801</v>
+        <v>555722</v>
       </c>
       <c r="R94" t="n">
-        <v>7045860</v>
+        <v>7046017</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10783,14 +10778,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10805,22 +10805,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129602047</v>
+        <v>129600756</v>
       </c>
       <c r="B95" t="n">
-        <v>79070</v>
+        <v>80175</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10828,21 +10828,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10852,13 +10852,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>555722</v>
+        <v>555626</v>
       </c>
       <c r="R95" t="n">
-        <v>7046017</v>
+        <v>7046163</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10885,19 +10885,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10912,60 +10902,69 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129600756</v>
+        <v>129602185</v>
       </c>
       <c r="B96" t="n">
-        <v>80175</v>
+        <v>98756</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>555626</v>
+        <v>555729</v>
       </c>
       <c r="R96" t="n">
-        <v>7046163</v>
+        <v>7045984</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10992,9 +10991,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11009,12 +11018,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -11128,42 +11137,38 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129602185</v>
+        <v>129602416</v>
       </c>
       <c r="B98" t="n">
-        <v>98756</v>
+        <v>57730</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -11172,13 +11177,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>555729</v>
+        <v>555801</v>
       </c>
       <c r="R98" t="n">
-        <v>7045984</v>
+        <v>7045860</v>
       </c>
       <c r="S98" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11205,19 +11210,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>14:07</t>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11232,12 +11232,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3056,7 +3056,7 @@
         <v>129298314</v>
       </c>
       <c r="B23" t="n">
-        <v>80176</v>
+        <v>80181</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>129298193</v>
       </c>
       <c r="B24" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129298243</v>
       </c>
       <c r="B25" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>129298267</v>
       </c>
       <c r="B26" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>129298152</v>
       </c>
       <c r="B27" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3616,10 +3616,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129298204</v>
+        <v>129298285</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>91885</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3627,21 +3627,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>555763</v>
+        <v>555760</v>
       </c>
       <c r="R28" t="n">
-        <v>7045835</v>
+        <v>7045817</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3723,10 +3723,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129298285</v>
+        <v>129298204</v>
       </c>
       <c r="B29" t="n">
-        <v>91879</v>
+        <v>79075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3734,21 +3734,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>555760</v>
+        <v>555763</v>
       </c>
       <c r="R29" t="n">
-        <v>7045817</v>
+        <v>7045835</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3830,48 +3830,52 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129602332</v>
+        <v>129602260</v>
       </c>
       <c r="B30" t="n">
-        <v>80175</v>
+        <v>98768</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555835</v>
+        <v>555747</v>
       </c>
       <c r="R30" t="n">
-        <v>7045850</v>
+        <v>7045963</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3898,19 +3902,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3925,60 +3919,69 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129601128</v>
+        <v>129600015</v>
       </c>
       <c r="B31" t="n">
-        <v>80204</v>
+        <v>98768</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555698</v>
+        <v>555553</v>
       </c>
       <c r="R31" t="n">
-        <v>7046187</v>
+        <v>7046074</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4005,9 +4008,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4022,22 +4035,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129602543</v>
+        <v>129602332</v>
       </c>
       <c r="B32" t="n">
-        <v>57730</v>
+        <v>80180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4045,39 +4058,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555769</v>
+        <v>555835</v>
       </c>
       <c r="R32" t="n">
-        <v>7045881</v>
+        <v>7045850</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4109,7 +4117,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4119,12 +4127,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4139,61 +4142,57 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129602260</v>
+        <v>129601128</v>
       </c>
       <c r="B33" t="n">
-        <v>98756</v>
+        <v>80209</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555747</v>
+        <v>555698</v>
       </c>
       <c r="R33" t="n">
-        <v>7045963</v>
+        <v>7046187</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4252,57 +4251,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129600015</v>
+        <v>129602543</v>
       </c>
       <c r="B34" t="n">
-        <v>98756</v>
+        <v>57735</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555553</v>
+        <v>555769</v>
       </c>
       <c r="R34" t="n">
-        <v>7046074</v>
+        <v>7045881</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4331,7 +4326,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4341,7 +4336,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4356,22 +4356,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129602488</v>
+        <v>129601775</v>
       </c>
       <c r="B35" t="n">
-        <v>92034</v>
+        <v>98768</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4379,37 +4379,41 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555837</v>
+        <v>555746</v>
       </c>
       <c r="R35" t="n">
-        <v>7045886</v>
+        <v>7046137</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4436,9 +4440,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4453,22 +4467,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129601775</v>
+        <v>129602548</v>
       </c>
       <c r="B36" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4495,7 +4509,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4504,13 +4523,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555746</v>
+        <v>555770</v>
       </c>
       <c r="R36" t="n">
-        <v>7046137</v>
+        <v>7045888</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4539,7 +4558,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4549,7 +4568,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4564,22 +4583,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129602548</v>
+        <v>129602488</v>
       </c>
       <c r="B37" t="n">
-        <v>98756</v>
+        <v>92040</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4587,46 +4606,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555770</v>
+        <v>555837</v>
       </c>
       <c r="R37" t="n">
-        <v>7045888</v>
+        <v>7045886</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4653,19 +4663,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4680,22 +4680,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129602638</v>
+        <v>129601980</v>
       </c>
       <c r="B38" t="n">
-        <v>91879</v>
+        <v>91587</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4703,21 +4703,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555826</v>
+        <v>555724</v>
       </c>
       <c r="R38" t="n">
-        <v>7045880</v>
+        <v>7046089</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129601980</v>
+        <v>129602638</v>
       </c>
       <c r="B39" t="n">
-        <v>91581</v>
+        <v>91885</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4800,21 +4800,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555724</v>
+        <v>555826</v>
       </c>
       <c r="R39" t="n">
-        <v>7046089</v>
+        <v>7045880</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4889,7 +4889,7 @@
         <v>129601485</v>
       </c>
       <c r="B40" t="n">
-        <v>80204</v>
+        <v>80209</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>129602219</v>
       </c>
       <c r="B41" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>129601909</v>
       </c>
       <c r="B42" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>129602085</v>
       </c>
       <c r="B43" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>129600463</v>
       </c>
       <c r="B44" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>129602321</v>
       </c>
       <c r="B45" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>129600640</v>
       </c>
       <c r="B46" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>129601113</v>
       </c>
       <c r="B47" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>129601971</v>
       </c>
       <c r="B48" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>129603244</v>
       </c>
       <c r="B49" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>129602134</v>
       </c>
       <c r="B50" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>129601611</v>
       </c>
       <c r="B51" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
         <v>129602579</v>
       </c>
       <c r="B52" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>129600512</v>
       </c>
       <c r="B53" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>129600139</v>
       </c>
       <c r="B54" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>129600692</v>
       </c>
       <c r="B55" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6616,48 +6616,52 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129600865</v>
+        <v>129602004</v>
       </c>
       <c r="B56" t="n">
-        <v>91581</v>
+        <v>58105</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555679</v>
+        <v>555738</v>
       </c>
       <c r="R56" t="n">
-        <v>7046243</v>
+        <v>7046093</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6684,19 +6688,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6711,60 +6705,64 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129602023</v>
+        <v>129600524</v>
       </c>
       <c r="B57" t="n">
-        <v>91581</v>
+        <v>98768</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555819</v>
+        <v>555564</v>
       </c>
       <c r="R57" t="n">
-        <v>7045946</v>
+        <v>7046096</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6791,19 +6789,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6818,60 +6806,60 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129600317</v>
+        <v>129601061</v>
       </c>
       <c r="B58" t="n">
-        <v>91879</v>
+        <v>80209</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555575</v>
+        <v>555707</v>
       </c>
       <c r="R58" t="n">
-        <v>7046182</v>
+        <v>7046194</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6898,9 +6886,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6915,22 +6913,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129602459</v>
+        <v>129601480</v>
       </c>
       <c r="B59" t="n">
-        <v>91581</v>
+        <v>80180</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6938,21 +6936,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6962,10 +6960,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>555835</v>
+        <v>555697</v>
       </c>
       <c r="R59" t="n">
-        <v>7045881</v>
+        <v>7046157</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7024,48 +7022,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129601061</v>
+        <v>129600317</v>
       </c>
       <c r="B60" t="n">
-        <v>80204</v>
+        <v>91885</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>555707</v>
+        <v>555575</v>
       </c>
       <c r="R60" t="n">
-        <v>7046194</v>
+        <v>7046182</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7092,19 +7090,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7119,22 +7107,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129601480</v>
+        <v>129600865</v>
       </c>
       <c r="B61" t="n">
-        <v>80175</v>
+        <v>91587</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7142,21 +7130,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7166,13 +7154,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555697</v>
+        <v>555679</v>
       </c>
       <c r="R61" t="n">
-        <v>7046157</v>
+        <v>7046243</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7199,9 +7187,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7216,44 +7214,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129602952</v>
+        <v>129602023</v>
       </c>
       <c r="B62" t="n">
-        <v>91545</v>
+        <v>91587</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7263,10 +7261,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555778</v>
+        <v>555819</v>
       </c>
       <c r="R62" t="n">
-        <v>7045842</v>
+        <v>7045946</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7298,7 +7296,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7308,7 +7306,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7335,49 +7333,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129602004</v>
+        <v>129602459</v>
       </c>
       <c r="B63" t="n">
-        <v>58100</v>
+        <v>91587</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555738</v>
+        <v>555835</v>
       </c>
       <c r="R63" t="n">
-        <v>7046093</v>
+        <v>7045881</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7436,52 +7430,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129600524</v>
+        <v>129602952</v>
       </c>
       <c r="B64" t="n">
-        <v>98756</v>
+        <v>91551</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>555564</v>
+        <v>555778</v>
       </c>
       <c r="R64" t="n">
-        <v>7046096</v>
+        <v>7045842</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7508,9 +7498,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7525,22 +7525,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129601012</v>
+        <v>129601936</v>
       </c>
       <c r="B65" t="n">
-        <v>91581</v>
+        <v>79075</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7548,21 +7548,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7572,13 +7572,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>555680</v>
+        <v>555804</v>
       </c>
       <c r="R65" t="n">
-        <v>7046211</v>
+        <v>7046004</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7605,9 +7605,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7622,22 +7632,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129600977</v>
+        <v>129601012</v>
       </c>
       <c r="B66" t="n">
-        <v>80175</v>
+        <v>91587</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7645,21 +7655,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7669,13 +7679,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>555704</v>
+        <v>555680</v>
       </c>
       <c r="R66" t="n">
-        <v>7046202</v>
+        <v>7046211</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7702,19 +7712,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:13</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7729,22 +7729,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129601936</v>
+        <v>129600977</v>
       </c>
       <c r="B67" t="n">
-        <v>79070</v>
+        <v>80180</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7752,21 +7752,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>555804</v>
+        <v>555704</v>
       </c>
       <c r="R67" t="n">
-        <v>7046004</v>
+        <v>7046202</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7836,22 +7836,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129601541</v>
+        <v>129602371</v>
       </c>
       <c r="B68" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7888,13 +7888,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>555702</v>
+        <v>555825</v>
       </c>
       <c r="R68" t="n">
-        <v>7046142</v>
+        <v>7045806</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7921,14 +7921,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack, gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7943,22 +7953,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129602371</v>
+        <v>129601541</v>
       </c>
       <c r="B69" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7986,7 +7996,7 @@
       <c r="I69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -7995,13 +8005,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>555825</v>
+        <v>555702</v>
       </c>
       <c r="R69" t="n">
-        <v>7045806</v>
+        <v>7046142</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8028,24 +8038,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8060,12 +8060,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8075,7 +8075,7 @@
         <v>129602553</v>
       </c>
       <c r="B70" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>129601748</v>
       </c>
       <c r="B71" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>129601725</v>
       </c>
       <c r="B72" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8383,10 +8383,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129602304</v>
+        <v>129600733</v>
       </c>
       <c r="B73" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8413,19 +8413,24 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>555857</v>
+        <v>555649</v>
       </c>
       <c r="R73" t="n">
-        <v>7045866</v>
+        <v>7046243</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8457,7 +8462,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8467,7 +8472,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8482,22 +8487,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129600733</v>
+        <v>129602304</v>
       </c>
       <c r="B74" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8524,24 +8529,19 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>555649</v>
+        <v>555857</v>
       </c>
       <c r="R74" t="n">
-        <v>7046243</v>
+        <v>7045866</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8598,12 +8598,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8613,7 +8613,7 @@
         <v>129600581</v>
       </c>
       <c r="B75" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8721,38 +8721,37 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129601872</v>
+        <v>129602094</v>
       </c>
       <c r="B76" t="n">
-        <v>57730</v>
+        <v>98768</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8761,10 +8760,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>555721</v>
+        <v>555852</v>
       </c>
       <c r="R76" t="n">
-        <v>7046072</v>
+        <v>7045941</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8796,7 +8795,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8806,12 +8805,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8826,12 +8820,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8841,7 +8835,7 @@
         <v>129602315</v>
       </c>
       <c r="B77" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8945,37 +8939,38 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129602094</v>
+        <v>129601872</v>
       </c>
       <c r="B78" t="n">
-        <v>98756</v>
+        <v>57735</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8984,10 +8979,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>555852</v>
+        <v>555721</v>
       </c>
       <c r="R78" t="n">
-        <v>7045941</v>
+        <v>7046072</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9019,7 +9014,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9029,7 +9024,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9044,22 +9044,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129603240</v>
+        <v>129600975</v>
       </c>
       <c r="B79" t="n">
-        <v>57730</v>
+        <v>80180</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9067,42 +9067,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>555865</v>
+        <v>555633</v>
       </c>
       <c r="R79" t="n">
-        <v>7045842</v>
+        <v>7046096</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9131,7 +9126,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9141,12 +9136,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9161,64 +9151,60 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129602172</v>
+        <v>129601148</v>
       </c>
       <c r="B80" t="n">
-        <v>98756</v>
+        <v>80180</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555855</v>
+        <v>555654</v>
       </c>
       <c r="R80" t="n">
-        <v>7045892</v>
+        <v>7046170</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9247,7 +9233,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9257,7 +9243,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9272,66 +9258,57 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129601945</v>
+        <v>129601421</v>
       </c>
       <c r="B81" t="n">
-        <v>98756</v>
+        <v>80180</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555730</v>
+        <v>555653</v>
       </c>
       <c r="R81" t="n">
-        <v>7046151</v>
+        <v>7046187</v>
       </c>
       <c r="S81" t="n">
         <v>3</v>
@@ -9363,7 +9340,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9373,7 +9350,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9400,45 +9377,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129600219</v>
+        <v>129601548</v>
       </c>
       <c r="B82" t="n">
-        <v>91581</v>
+        <v>80208</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555572</v>
+        <v>555707</v>
       </c>
       <c r="R82" t="n">
-        <v>7046181</v>
+        <v>7046135</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9497,48 +9474,52 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129600975</v>
+        <v>129602172</v>
       </c>
       <c r="B83" t="n">
-        <v>80175</v>
+        <v>98768</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555633</v>
+        <v>555855</v>
       </c>
       <c r="R83" t="n">
-        <v>7046096</v>
+        <v>7045892</v>
       </c>
       <c r="S83" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9567,7 +9548,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9577,7 +9558,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9592,60 +9573,69 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129601148</v>
+        <v>129601945</v>
       </c>
       <c r="B84" t="n">
-        <v>80175</v>
+        <v>98768</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555654</v>
+        <v>555730</v>
       </c>
       <c r="R84" t="n">
-        <v>7046170</v>
+        <v>7046151</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9674,7 +9664,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9684,7 +9674,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9711,10 +9701,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129601421</v>
+        <v>129600219</v>
       </c>
       <c r="B85" t="n">
-        <v>80175</v>
+        <v>91587</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9722,37 +9712,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555653</v>
+        <v>555572</v>
       </c>
       <c r="R85" t="n">
-        <v>7046187</v>
+        <v>7046181</v>
       </c>
       <c r="S85" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9779,19 +9769,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:31</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9806,60 +9786,65 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129601548</v>
+        <v>129603240</v>
       </c>
       <c r="B86" t="n">
-        <v>80203</v>
+        <v>57735</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>555707</v>
+        <v>555865</v>
       </c>
       <c r="R86" t="n">
-        <v>7046135</v>
+        <v>7045842</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9886,9 +9871,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9903,12 +9903,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9918,7 +9918,7 @@
         <v>129602154</v>
       </c>
       <c r="B87" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10012,57 +10012,53 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129602716</v>
+        <v>129600090</v>
       </c>
       <c r="B88" t="n">
-        <v>98756</v>
+        <v>57735</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>555762</v>
+        <v>555491</v>
       </c>
       <c r="R88" t="n">
-        <v>7045845</v>
+        <v>7046111</v>
       </c>
       <c r="S88" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10091,7 +10087,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10101,7 +10097,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10116,54 +10117,50 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129601612</v>
+        <v>129602108</v>
       </c>
       <c r="B89" t="n">
-        <v>98756</v>
+        <v>57735</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10172,10 +10169,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>555675</v>
+        <v>555854</v>
       </c>
       <c r="R89" t="n">
-        <v>7046143</v>
+        <v>7045940</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10207,7 +10204,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10217,7 +10214,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10232,22 +10234,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129603549</v>
+        <v>129602716</v>
       </c>
       <c r="B90" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10274,7 +10276,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10288,13 +10290,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>555865</v>
+        <v>555762</v>
       </c>
       <c r="R90" t="n">
-        <v>7045842</v>
+        <v>7045845</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10323,7 +10325,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10333,7 +10335,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10348,22 +10350,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129601760</v>
+        <v>129601612</v>
       </c>
       <c r="B91" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10390,7 +10392,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10404,13 +10406,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>555694</v>
+        <v>555675</v>
       </c>
       <c r="R91" t="n">
-        <v>7046166</v>
+        <v>7046143</v>
       </c>
       <c r="S91" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10439,7 +10441,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10449,7 +10451,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10464,62 +10466,66 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129600090</v>
+        <v>129603549</v>
       </c>
       <c r="B92" t="n">
-        <v>57730</v>
+        <v>98768</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>555491</v>
+        <v>555865</v>
       </c>
       <c r="R92" t="n">
-        <v>7046111</v>
+        <v>7045842</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10551,7 +10557,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10561,12 +10567,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10593,38 +10594,42 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129602108</v>
+        <v>129601760</v>
       </c>
       <c r="B93" t="n">
-        <v>57730</v>
+        <v>98768</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10633,13 +10638,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>555854</v>
+        <v>555694</v>
       </c>
       <c r="R93" t="n">
-        <v>7045940</v>
+        <v>7046166</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10668,7 +10673,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10678,12 +10683,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10698,60 +10698,69 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129602047</v>
+        <v>129602185</v>
       </c>
       <c r="B94" t="n">
-        <v>79070</v>
+        <v>98768</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>555722</v>
+        <v>555729</v>
       </c>
       <c r="R94" t="n">
-        <v>7046017</v>
+        <v>7045984</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10780,7 +10789,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10790,7 +10799,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10805,22 +10814,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129600756</v>
+        <v>129602047</v>
       </c>
       <c r="B95" t="n">
-        <v>80175</v>
+        <v>79075</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10828,21 +10837,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10852,13 +10861,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>555626</v>
+        <v>555722</v>
       </c>
       <c r="R95" t="n">
-        <v>7046163</v>
+        <v>7046017</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10885,9 +10894,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10902,69 +10921,60 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129602185</v>
+        <v>129600756</v>
       </c>
       <c r="B96" t="n">
-        <v>98756</v>
+        <v>80180</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>555729</v>
+        <v>555626</v>
       </c>
       <c r="R96" t="n">
-        <v>7045984</v>
+        <v>7046163</v>
       </c>
       <c r="S96" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10991,19 +11001,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>14:07</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11018,12 +11018,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -11033,7 +11033,7 @@
         <v>129600095</v>
       </c>
       <c r="B97" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>129602416</v>
       </c>
       <c r="B98" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11244,10 +11244,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129600791</v>
+        <v>129602252</v>
       </c>
       <c r="B99" t="n">
-        <v>80175</v>
+        <v>91587</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11255,21 +11255,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11279,13 +11279,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>555670</v>
+        <v>555848</v>
       </c>
       <c r="R99" t="n">
-        <v>7046158</v>
+        <v>7045879</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11312,9 +11312,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11329,22 +11339,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129602252</v>
+        <v>129600791</v>
       </c>
       <c r="B100" t="n">
-        <v>91581</v>
+        <v>80180</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11352,21 +11362,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11376,13 +11386,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>555848</v>
+        <v>555670</v>
       </c>
       <c r="R100" t="n">
-        <v>7045879</v>
+        <v>7046158</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11409,19 +11419,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11436,22 +11436,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129601948</v>
+        <v>129600129</v>
       </c>
       <c r="B101" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11484,14 +11484,14 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>555736</v>
+        <v>555483</v>
       </c>
       <c r="R101" t="n">
-        <v>7046059</v>
+        <v>7046117</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11523,7 +11523,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
@@ -11565,10 +11565,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129600129</v>
+        <v>129601948</v>
       </c>
       <c r="B102" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11601,14 +11601,14 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>555483</v>
+        <v>555736</v>
       </c>
       <c r="R102" t="n">
-        <v>7046117</v>
+        <v>7046059</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11640,7 +11640,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
@@ -11682,45 +11682,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129600723</v>
+        <v>129601828</v>
       </c>
       <c r="B103" t="n">
-        <v>80175</v>
+        <v>91551</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>555572</v>
+        <v>555724</v>
       </c>
       <c r="R103" t="n">
-        <v>7046171</v>
+        <v>7046097</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -11779,10 +11779,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129600507</v>
+        <v>129600723</v>
       </c>
       <c r="B104" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11814,13 +11814,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>555608</v>
+        <v>555572</v>
       </c>
       <c r="R104" t="n">
-        <v>7046222</v>
+        <v>7046171</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11847,19 +11847,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11874,60 +11864,60 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129601828</v>
+        <v>129600507</v>
       </c>
       <c r="B105" t="n">
-        <v>91545</v>
+        <v>80180</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>555724</v>
+        <v>555608</v>
       </c>
       <c r="R105" t="n">
-        <v>7046097</v>
+        <v>7046222</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11954,9 +11944,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11971,12 +11971,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11986,7 +11986,7 @@
         <v>129601607</v>
       </c>
       <c r="B106" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12080,10 +12080,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129601709</v>
+        <v>129602456</v>
       </c>
       <c r="B107" t="n">
-        <v>57730</v>
+        <v>57732</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12091,16 +12091,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -12111,7 +12111,7 @@
       <c r="I107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -12120,10 +12120,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>555739</v>
+        <v>555809</v>
       </c>
       <c r="R107" t="n">
-        <v>7046139</v>
+        <v>7045823</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12155,7 +12155,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12165,12 +12165,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12197,42 +12192,38 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129602437</v>
+        <v>129601709</v>
       </c>
       <c r="B108" t="n">
-        <v>98756</v>
+        <v>57735</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -12241,13 +12232,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>555757</v>
+        <v>555739</v>
       </c>
       <c r="R108" t="n">
-        <v>7045907</v>
+        <v>7046139</v>
       </c>
       <c r="S108" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12276,7 +12267,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12286,7 +12277,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12301,22 +12297,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129600807</v>
+        <v>129602437</v>
       </c>
       <c r="B109" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12343,7 +12339,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -12352,10 +12353,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>555633</v>
+        <v>555757</v>
       </c>
       <c r="R109" t="n">
-        <v>7046097</v>
+        <v>7045907</v>
       </c>
       <c r="S109" t="n">
         <v>4</v>
@@ -12387,7 +12388,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12397,7 +12398,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12424,38 +12425,37 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129602456</v>
+        <v>129600807</v>
       </c>
       <c r="B110" t="n">
-        <v>57727</v>
+        <v>98768</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -12464,13 +12464,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>555809</v>
+        <v>555633</v>
       </c>
       <c r="R110" t="n">
-        <v>7045823</v>
+        <v>7046097</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12524,44 +12524,44 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129601521</v>
+        <v>129601528</v>
       </c>
       <c r="B111" t="n">
-        <v>97627</v>
+        <v>91587</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12571,10 +12571,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>555695</v>
+        <v>555698</v>
       </c>
       <c r="R111" t="n">
-        <v>7046136</v>
+        <v>7046140</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -12633,45 +12633,49 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129601528</v>
+        <v>129600022</v>
       </c>
       <c r="B112" t="n">
-        <v>91581</v>
+        <v>98768</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>555698</v>
+        <v>555560</v>
       </c>
       <c r="R112" t="n">
-        <v>7046140</v>
+        <v>7046091</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -12730,10 +12734,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129600022</v>
+        <v>129601553</v>
       </c>
       <c r="B113" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12760,22 +12764,22 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>555560</v>
+        <v>555704</v>
       </c>
       <c r="R113" t="n">
-        <v>7046091</v>
+        <v>7046148</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12802,9 +12806,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12819,22 +12833,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129601553</v>
+        <v>129600513</v>
       </c>
       <c r="B114" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12861,22 +12875,27 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>555704</v>
+        <v>555590</v>
       </c>
       <c r="R114" t="n">
-        <v>7046148</v>
+        <v>7046134</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12905,7 +12924,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12915,7 +12934,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12930,69 +12949,60 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129600513</v>
+        <v>129601521</v>
       </c>
       <c r="B115" t="n">
-        <v>98756</v>
+        <v>97639</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>555590</v>
+        <v>555695</v>
       </c>
       <c r="R115" t="n">
-        <v>7046134</v>
+        <v>7046136</v>
       </c>
       <c r="S115" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13019,19 +13029,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13046,60 +13046,60 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129602472</v>
+        <v>129600727</v>
       </c>
       <c r="B116" t="n">
-        <v>79070</v>
+        <v>80209</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>555806</v>
+        <v>555605</v>
       </c>
       <c r="R116" t="n">
-        <v>7045826</v>
+        <v>7046222</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13126,19 +13126,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13153,57 +13143,57 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129600727</v>
+        <v>129600845</v>
       </c>
       <c r="B117" t="n">
-        <v>80204</v>
+        <v>80180</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>555605</v>
+        <v>555681</v>
       </c>
       <c r="R117" t="n">
-        <v>7046222</v>
+        <v>7046162</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13262,10 +13252,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129600845</v>
+        <v>129602472</v>
       </c>
       <c r="B118" t="n">
-        <v>80175</v>
+        <v>79075</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13273,21 +13263,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13297,13 +13287,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>555681</v>
+        <v>555806</v>
       </c>
       <c r="R118" t="n">
-        <v>7046162</v>
+        <v>7045826</v>
       </c>
       <c r="S118" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13330,9 +13320,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13347,12 +13347,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -13362,7 +13362,7 @@
         <v>129602025</v>
       </c>
       <c r="B119" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13460,10 +13460,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129602058</v>
+        <v>129602598</v>
       </c>
       <c r="B120" t="n">
-        <v>79070</v>
+        <v>80180</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13471,21 +13471,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13495,13 +13495,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>555829</v>
+        <v>555768</v>
       </c>
       <c r="R120" t="n">
-        <v>7045930</v>
+        <v>7045841</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13540,7 +13540,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13555,22 +13555,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129600175</v>
+        <v>129600621</v>
       </c>
       <c r="B121" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
       <c r="I121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13607,13 +13607,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>555493</v>
+        <v>555635</v>
       </c>
       <c r="R121" t="n">
-        <v>7046125</v>
+        <v>7046219</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13640,24 +13640,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13672,22 +13662,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129600621</v>
+        <v>129600175</v>
       </c>
       <c r="B122" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13715,7 +13705,7 @@
       <c r="I122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -13724,13 +13714,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>555635</v>
+        <v>555493</v>
       </c>
       <c r="R122" t="n">
-        <v>7046219</v>
+        <v>7046125</v>
       </c>
       <c r="S122" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13757,14 +13747,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Ringhack, gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13779,12 +13779,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -13794,7 +13794,7 @@
         <v>129600978</v>
       </c>
       <c r="B123" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129602598</v>
+        <v>129602058</v>
       </c>
       <c r="B124" t="n">
-        <v>80175</v>
+        <v>79075</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13919,21 +13919,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13943,13 +13943,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>555768</v>
+        <v>555829</v>
       </c>
       <c r="R124" t="n">
-        <v>7045841</v>
+        <v>7045930</v>
       </c>
       <c r="S124" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13988,7 +13988,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14003,12 +14003,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -14018,7 +14018,7 @@
         <v>129601920</v>
       </c>
       <c r="B125" t="n">
-        <v>92064</v>
+        <v>92070</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3056,7 +3056,7 @@
         <v>129298314</v>
       </c>
       <c r="B23" t="n">
-        <v>80181</v>
+        <v>80182</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>129298193</v>
       </c>
       <c r="B24" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>129298243</v>
       </c>
       <c r="B25" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>129298267</v>
       </c>
       <c r="B26" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>129298152</v>
       </c>
       <c r="B27" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>129298285</v>
       </c>
       <c r="B28" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>129298204</v>
       </c>
       <c r="B29" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>129602260</v>
       </c>
       <c r="B30" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>129600015</v>
       </c>
       <c r="B31" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4047,32 +4047,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129602332</v>
+        <v>129601128</v>
       </c>
       <c r="B32" t="n">
-        <v>80180</v>
+        <v>80210</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4082,13 +4082,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555835</v>
+        <v>555698</v>
       </c>
       <c r="R32" t="n">
-        <v>7045850</v>
+        <v>7046187</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4115,19 +4115,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4142,44 +4132,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129601128</v>
+        <v>129602332</v>
       </c>
       <c r="B33" t="n">
-        <v>80209</v>
+        <v>80181</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4189,13 +4179,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555698</v>
+        <v>555835</v>
       </c>
       <c r="R33" t="n">
-        <v>7046187</v>
+        <v>7045850</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4222,9 +4212,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4239,12 +4239,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4254,7 +4254,7 @@
         <v>129602543</v>
       </c>
       <c r="B34" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129601775</v>
+        <v>129602488</v>
       </c>
       <c r="B35" t="n">
-        <v>98768</v>
+        <v>92041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4379,41 +4379,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>555746</v>
+        <v>555837</v>
       </c>
       <c r="R35" t="n">
-        <v>7046137</v>
+        <v>7045886</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4440,19 +4436,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4467,22 +4453,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129602548</v>
+        <v>129601775</v>
       </c>
       <c r="B36" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4509,12 +4495,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4523,13 +4504,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555770</v>
+        <v>555746</v>
       </c>
       <c r="R36" t="n">
-        <v>7045888</v>
+        <v>7046137</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4558,7 +4539,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4568,7 +4549,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4583,22 +4564,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129602488</v>
+        <v>129602548</v>
       </c>
       <c r="B37" t="n">
-        <v>92040</v>
+        <v>98769</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4606,37 +4587,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555837</v>
+        <v>555770</v>
       </c>
       <c r="R37" t="n">
-        <v>7045886</v>
+        <v>7045888</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4663,9 +4653,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4680,22 +4680,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129601980</v>
+        <v>129602085</v>
       </c>
       <c r="B38" t="n">
-        <v>91587</v>
+        <v>57896</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4703,37 +4703,51 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555724</v>
+        <v>555725</v>
       </c>
       <c r="R38" t="n">
-        <v>7046089</v>
+        <v>7046023</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4760,9 +4774,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4777,22 +4801,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129602638</v>
+        <v>129602219</v>
       </c>
       <c r="B39" t="n">
-        <v>91885</v>
+        <v>79076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4800,21 +4824,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4824,10 +4848,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555826</v>
+        <v>555697</v>
       </c>
       <c r="R39" t="n">
-        <v>7045880</v>
+        <v>7045963</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4889,7 +4913,7 @@
         <v>129601485</v>
       </c>
       <c r="B40" t="n">
-        <v>80209</v>
+        <v>80210</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4983,10 +5007,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129602219</v>
+        <v>129602638</v>
       </c>
       <c r="B41" t="n">
-        <v>79075</v>
+        <v>91886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4994,21 +5018,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5018,10 +5042,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555697</v>
+        <v>555826</v>
       </c>
       <c r="R41" t="n">
-        <v>7045963</v>
+        <v>7045880</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5080,10 +5104,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129601909</v>
+        <v>129601980</v>
       </c>
       <c r="B42" t="n">
-        <v>57735</v>
+        <v>91588</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5091,42 +5115,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>555726</v>
+        <v>555724</v>
       </c>
       <c r="R42" t="n">
-        <v>7046072</v>
+        <v>7046089</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5153,24 +5172,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5185,22 +5189,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129602085</v>
+        <v>129601909</v>
       </c>
       <c r="B43" t="n">
-        <v>57895</v>
+        <v>57736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5208,36 +5212,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5246,10 +5241,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>555725</v>
+        <v>555726</v>
       </c>
       <c r="R43" t="n">
-        <v>7046023</v>
+        <v>7046072</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5281,7 +5276,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5291,7 +5286,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5321,7 +5321,7 @@
         <v>129600463</v>
       </c>
       <c r="B44" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>129602321</v>
       </c>
       <c r="B45" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5545,48 +5545,52 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129600640</v>
+        <v>129603244</v>
       </c>
       <c r="B46" t="n">
-        <v>80180</v>
+        <v>98769</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555615</v>
+        <v>555877</v>
       </c>
       <c r="R46" t="n">
-        <v>7046128</v>
+        <v>7045808</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5615,7 +5619,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5625,7 +5629,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5640,60 +5644,64 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129601113</v>
+        <v>129602134</v>
       </c>
       <c r="B47" t="n">
-        <v>80180</v>
+        <v>98769</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555677</v>
+        <v>555825</v>
       </c>
       <c r="R47" t="n">
-        <v>7046225</v>
+        <v>7045910</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5720,9 +5728,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5737,22 +5755,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129601971</v>
+        <v>129600640</v>
       </c>
       <c r="B48" t="n">
-        <v>79075</v>
+        <v>80181</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5760,21 +5778,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5784,13 +5802,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>555791</v>
+        <v>555615</v>
       </c>
       <c r="R48" t="n">
-        <v>7045965</v>
+        <v>7046128</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5819,7 +5837,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5829,7 +5847,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5844,61 +5862,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129603244</v>
+        <v>129601971</v>
       </c>
       <c r="B49" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>555877</v>
+        <v>555791</v>
       </c>
       <c r="R49" t="n">
-        <v>7045808</v>
+        <v>7045965</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5930,7 +5944,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5940,7 +5954,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5967,52 +5981,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129602134</v>
+        <v>129601113</v>
       </c>
       <c r="B50" t="n">
-        <v>98768</v>
+        <v>80181</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555825</v>
+        <v>555677</v>
       </c>
       <c r="R50" t="n">
-        <v>7045910</v>
+        <v>7046225</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6039,19 +6049,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6066,69 +6066,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129601611</v>
+        <v>129602579</v>
       </c>
       <c r="B51" t="n">
-        <v>98768</v>
+        <v>78833</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555687</v>
+        <v>555842</v>
       </c>
       <c r="R51" t="n">
-        <v>7046167</v>
+        <v>7045881</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6155,19 +6146,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>13:41</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6182,22 +6163,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129602579</v>
+        <v>129600512</v>
       </c>
       <c r="B52" t="n">
-        <v>78832</v>
+        <v>57736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6205,37 +6186,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555842</v>
+        <v>555592</v>
       </c>
       <c r="R52" t="n">
-        <v>7045881</v>
+        <v>7046249</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6262,9 +6248,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6279,65 +6280,69 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129600512</v>
+        <v>129601611</v>
       </c>
       <c r="B53" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555592</v>
+        <v>555687</v>
       </c>
       <c r="R53" t="n">
-        <v>7046249</v>
+        <v>7046167</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6366,7 +6371,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6376,12 +6381,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6396,60 +6396,64 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129600139</v>
+        <v>129600692</v>
       </c>
       <c r="B54" t="n">
-        <v>80180</v>
+        <v>98769</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555553</v>
+        <v>555611</v>
       </c>
       <c r="R54" t="n">
-        <v>7046074</v>
+        <v>7046241</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6476,19 +6480,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6503,64 +6497,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129600692</v>
+        <v>129600139</v>
       </c>
       <c r="B55" t="n">
-        <v>98768</v>
+        <v>80181</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555611</v>
+        <v>555553</v>
       </c>
       <c r="R55" t="n">
-        <v>7046241</v>
+        <v>7046074</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6587,9 +6577,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6604,12 +6604,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6619,7 +6619,7 @@
         <v>129602004</v>
       </c>
       <c r="B56" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6717,52 +6717,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129600524</v>
+        <v>129602952</v>
       </c>
       <c r="B57" t="n">
-        <v>98768</v>
+        <v>91552</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555564</v>
+        <v>555778</v>
       </c>
       <c r="R57" t="n">
-        <v>7046096</v>
+        <v>7045842</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6789,9 +6785,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6806,44 +6812,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129601061</v>
+        <v>129600865</v>
       </c>
       <c r="B58" t="n">
-        <v>80209</v>
+        <v>91588</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6853,10 +6859,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555707</v>
+        <v>555679</v>
       </c>
       <c r="R58" t="n">
-        <v>7046194</v>
+        <v>7046243</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6888,7 +6894,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6898,7 +6904,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6913,22 +6919,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129601480</v>
+        <v>129602023</v>
       </c>
       <c r="B59" t="n">
-        <v>80180</v>
+        <v>91588</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6936,21 +6942,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6960,13 +6966,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>555697</v>
+        <v>555819</v>
       </c>
       <c r="R59" t="n">
-        <v>7046157</v>
+        <v>7045946</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6993,9 +6999,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7010,12 +7026,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7025,7 +7041,7 @@
         <v>129600317</v>
       </c>
       <c r="B60" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7119,10 +7135,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129600865</v>
+        <v>129602459</v>
       </c>
       <c r="B61" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7154,13 +7170,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555679</v>
+        <v>555835</v>
       </c>
       <c r="R61" t="n">
-        <v>7046243</v>
+        <v>7045881</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7187,19 +7203,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7214,44 +7220,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129602023</v>
+        <v>129601061</v>
       </c>
       <c r="B62" t="n">
-        <v>91587</v>
+        <v>80210</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7261,10 +7267,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555819</v>
+        <v>555707</v>
       </c>
       <c r="R62" t="n">
-        <v>7045946</v>
+        <v>7046194</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7296,7 +7302,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7306,7 +7312,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7321,22 +7327,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129602459</v>
+        <v>129601480</v>
       </c>
       <c r="B63" t="n">
-        <v>91587</v>
+        <v>80181</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7344,21 +7350,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7368,10 +7374,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555835</v>
+        <v>555697</v>
       </c>
       <c r="R63" t="n">
-        <v>7045881</v>
+        <v>7046157</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7430,48 +7436,52 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129602952</v>
+        <v>129600524</v>
       </c>
       <c r="B64" t="n">
-        <v>91551</v>
+        <v>98769</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>555778</v>
+        <v>555564</v>
       </c>
       <c r="R64" t="n">
-        <v>7045842</v>
+        <v>7046096</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7498,19 +7508,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:49</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7525,12 +7525,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7540,7 +7540,7 @@
         <v>129601936</v>
       </c>
       <c r="B65" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7644,10 +7644,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129601012</v>
+        <v>129600977</v>
       </c>
       <c r="B66" t="n">
-        <v>91587</v>
+        <v>80181</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7655,21 +7655,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7679,13 +7679,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>555680</v>
+        <v>555704</v>
       </c>
       <c r="R66" t="n">
-        <v>7046211</v>
+        <v>7046202</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7712,9 +7712,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7729,22 +7739,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129600977</v>
+        <v>129601012</v>
       </c>
       <c r="B67" t="n">
-        <v>80180</v>
+        <v>91588</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7752,21 +7762,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7776,13 +7786,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>555704</v>
+        <v>555680</v>
       </c>
       <c r="R67" t="n">
-        <v>7046202</v>
+        <v>7046211</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7809,19 +7819,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:13</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7836,12 +7836,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7851,7 +7851,7 @@
         <v>129602371</v>
       </c>
       <c r="B68" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>129601541</v>
       </c>
       <c r="B69" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>129602553</v>
       </c>
       <c r="B70" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8169,10 +8169,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129601748</v>
+        <v>129601725</v>
       </c>
       <c r="B71" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8204,10 +8204,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>555703</v>
+        <v>555750</v>
       </c>
       <c r="R71" t="n">
-        <v>7046100</v>
+        <v>7046140</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8264,57 +8264,66 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129601725</v>
+        <v>129600733</v>
       </c>
       <c r="B72" t="n">
-        <v>80180</v>
+        <v>98769</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>555750</v>
+        <v>555649</v>
       </c>
       <c r="R72" t="n">
-        <v>7046140</v>
+        <v>7046243</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8346,7 +8355,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8356,7 +8365,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8371,22 +8380,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129600733</v>
+        <v>129602304</v>
       </c>
       <c r="B73" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8413,24 +8422,19 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>555649</v>
+        <v>555857</v>
       </c>
       <c r="R73" t="n">
-        <v>7046243</v>
+        <v>7045866</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8462,7 +8466,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8472,7 +8476,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8487,61 +8491,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129602304</v>
+        <v>129601748</v>
       </c>
       <c r="B74" t="n">
-        <v>98768</v>
+        <v>80181</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>555857</v>
+        <v>555703</v>
       </c>
       <c r="R74" t="n">
-        <v>7045866</v>
+        <v>7046100</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8598,12 +8598,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8613,7 +8613,7 @@
         <v>129600581</v>
       </c>
       <c r="B75" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8721,37 +8721,38 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129602094</v>
+        <v>129601872</v>
       </c>
       <c r="B76" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8760,10 +8761,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>555852</v>
+        <v>555721</v>
       </c>
       <c r="R76" t="n">
-        <v>7045941</v>
+        <v>7046072</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8795,7 +8796,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8805,7 +8806,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8820,12 +8826,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8835,7 +8841,7 @@
         <v>129602315</v>
       </c>
       <c r="B77" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8939,38 +8945,37 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129601872</v>
+        <v>129602094</v>
       </c>
       <c r="B78" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8979,10 +8984,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>555721</v>
+        <v>555852</v>
       </c>
       <c r="R78" t="n">
-        <v>7046072</v>
+        <v>7045941</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9014,7 +9019,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9024,12 +9029,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9044,22 +9044,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129600975</v>
+        <v>129600219</v>
       </c>
       <c r="B79" t="n">
-        <v>80180</v>
+        <v>91588</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9067,37 +9067,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>555633</v>
+        <v>555572</v>
       </c>
       <c r="R79" t="n">
-        <v>7046096</v>
+        <v>7046181</v>
       </c>
       <c r="S79" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9124,19 +9124,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:13</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9151,60 +9141,64 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129601148</v>
+        <v>129602172</v>
       </c>
       <c r="B80" t="n">
-        <v>80180</v>
+        <v>98769</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555654</v>
+        <v>555855</v>
       </c>
       <c r="R80" t="n">
-        <v>7046170</v>
+        <v>7045892</v>
       </c>
       <c r="S80" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9233,7 +9227,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9243,7 +9237,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9258,57 +9252,66 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129601421</v>
+        <v>129601945</v>
       </c>
       <c r="B81" t="n">
-        <v>80180</v>
+        <v>98769</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555653</v>
+        <v>555730</v>
       </c>
       <c r="R81" t="n">
-        <v>7046187</v>
+        <v>7046151</v>
       </c>
       <c r="S81" t="n">
         <v>3</v>
@@ -9340,7 +9343,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9350,7 +9353,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9377,32 +9380,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129601548</v>
+        <v>129600975</v>
       </c>
       <c r="B82" t="n">
-        <v>80208</v>
+        <v>80181</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9412,13 +9415,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555707</v>
+        <v>555633</v>
       </c>
       <c r="R82" t="n">
-        <v>7046135</v>
+        <v>7046096</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9445,9 +9448,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9462,64 +9475,60 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129602172</v>
+        <v>129601421</v>
       </c>
       <c r="B83" t="n">
-        <v>98768</v>
+        <v>80181</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555855</v>
+        <v>555653</v>
       </c>
       <c r="R83" t="n">
-        <v>7045892</v>
+        <v>7046187</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9548,7 +9557,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9558,7 +9567,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9573,69 +9582,60 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129601945</v>
+        <v>129601148</v>
       </c>
       <c r="B84" t="n">
-        <v>98768</v>
+        <v>80181</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555730</v>
+        <v>555654</v>
       </c>
       <c r="R84" t="n">
-        <v>7046151</v>
+        <v>7046170</v>
       </c>
       <c r="S84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9701,45 +9701,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129600219</v>
+        <v>129601548</v>
       </c>
       <c r="B85" t="n">
-        <v>91587</v>
+        <v>80209</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555572</v>
+        <v>555707</v>
       </c>
       <c r="R85" t="n">
-        <v>7046181</v>
+        <v>7046135</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9801,7 +9801,7 @@
         <v>129603240</v>
       </c>
       <c r="B86" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>129602154</v>
       </c>
       <c r="B87" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>129600090</v>
       </c>
       <c r="B88" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>129602108</v>
       </c>
       <c r="B89" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>129602716</v>
       </c>
       <c r="B90" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>129601612</v>
       </c>
       <c r="B91" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>129603549</v>
       </c>
       <c r="B92" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>129601760</v>
       </c>
       <c r="B93" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10710,57 +10710,48 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129602185</v>
+        <v>129602047</v>
       </c>
       <c r="B94" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>555729</v>
+        <v>555722</v>
       </c>
       <c r="R94" t="n">
-        <v>7045984</v>
+        <v>7046017</v>
       </c>
       <c r="S94" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10789,7 +10780,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10799,7 +10790,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10814,22 +10805,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129602047</v>
+        <v>129600756</v>
       </c>
       <c r="B95" t="n">
-        <v>79075</v>
+        <v>80181</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10837,21 +10828,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10861,13 +10852,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>555722</v>
+        <v>555626</v>
       </c>
       <c r="R95" t="n">
-        <v>7046017</v>
+        <v>7046163</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10894,19 +10885,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10921,22 +10902,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129600756</v>
+        <v>129600095</v>
       </c>
       <c r="B96" t="n">
-        <v>80180</v>
+        <v>79076</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10944,37 +10925,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>555626</v>
+        <v>555473</v>
       </c>
       <c r="R96" t="n">
-        <v>7046163</v>
+        <v>7046098</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11001,9 +10982,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11018,22 +11009,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129600095</v>
+        <v>129602416</v>
       </c>
       <c r="B97" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11041,37 +11032,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>555473</v>
+        <v>555801</v>
       </c>
       <c r="R97" t="n">
-        <v>7046098</v>
+        <v>7045860</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11098,19 +11094,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>12:36</t>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11125,50 +11116,54 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129602416</v>
+        <v>129602185</v>
       </c>
       <c r="B98" t="n">
-        <v>57735</v>
+        <v>98769</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -11177,13 +11172,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>555801</v>
+        <v>555729</v>
       </c>
       <c r="R98" t="n">
-        <v>7045860</v>
+        <v>7045984</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11210,14 +11205,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11232,22 +11232,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129602252</v>
+        <v>129600791</v>
       </c>
       <c r="B99" t="n">
-        <v>91587</v>
+        <v>80181</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11255,21 +11255,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11279,13 +11279,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>555848</v>
+        <v>555670</v>
       </c>
       <c r="R99" t="n">
-        <v>7045879</v>
+        <v>7046158</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11312,19 +11312,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11339,22 +11329,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129600791</v>
+        <v>129602252</v>
       </c>
       <c r="B100" t="n">
-        <v>80180</v>
+        <v>91588</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11362,21 +11352,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11386,13 +11376,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>555670</v>
+        <v>555848</v>
       </c>
       <c r="R100" t="n">
-        <v>7046158</v>
+        <v>7045879</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11419,9 +11409,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11436,12 +11436,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11451,7 +11451,7 @@
         <v>129600129</v>
       </c>
       <c r="B101" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>129601948</v>
       </c>
       <c r="B102" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11682,48 +11682,48 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129601828</v>
+        <v>129600507</v>
       </c>
       <c r="B103" t="n">
-        <v>91551</v>
+        <v>80181</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>555724</v>
+        <v>555608</v>
       </c>
       <c r="R103" t="n">
-        <v>7046097</v>
+        <v>7046222</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11750,9 +11750,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11767,22 +11777,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129600723</v>
+        <v>129602456</v>
       </c>
       <c r="B104" t="n">
-        <v>80180</v>
+        <v>57733</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11790,37 +11800,42 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>555572</v>
+        <v>555809</v>
       </c>
       <c r="R104" t="n">
-        <v>7046171</v>
+        <v>7045823</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11847,9 +11862,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11864,60 +11889,69 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129600507</v>
+        <v>129602437</v>
       </c>
       <c r="B105" t="n">
-        <v>80180</v>
+        <v>98769</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>555608</v>
+        <v>555757</v>
       </c>
       <c r="R105" t="n">
-        <v>7046222</v>
+        <v>7045907</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11946,7 +11980,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11956,7 +11990,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11971,60 +12005,64 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129601607</v>
+        <v>129600807</v>
       </c>
       <c r="B106" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>555709</v>
+        <v>555633</v>
       </c>
       <c r="R106" t="n">
-        <v>7046133</v>
+        <v>7046097</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12051,9 +12089,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12068,65 +12116,60 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129602456</v>
+        <v>129601828</v>
       </c>
       <c r="B107" t="n">
-        <v>57732</v>
+        <v>91552</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>555809</v>
+        <v>555724</v>
       </c>
       <c r="R107" t="n">
-        <v>7045823</v>
+        <v>7046097</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12153,19 +12196,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>14:28</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12180,22 +12213,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129601709</v>
+        <v>129601607</v>
       </c>
       <c r="B108" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12203,42 +12236,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>555739</v>
+        <v>555709</v>
       </c>
       <c r="R108" t="n">
-        <v>7046139</v>
+        <v>7046133</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12265,24 +12293,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12297,69 +12310,60 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129602437</v>
+        <v>129600723</v>
       </c>
       <c r="B109" t="n">
-        <v>98768</v>
+        <v>80181</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>555757</v>
+        <v>555572</v>
       </c>
       <c r="R109" t="n">
-        <v>7045907</v>
+        <v>7046171</v>
       </c>
       <c r="S109" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12386,19 +12390,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12413,49 +12407,50 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129600807</v>
+        <v>129601709</v>
       </c>
       <c r="B110" t="n">
-        <v>98768</v>
+        <v>57736</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -12464,13 +12459,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>555633</v>
+        <v>555739</v>
       </c>
       <c r="R110" t="n">
-        <v>7046097</v>
+        <v>7046139</v>
       </c>
       <c r="S110" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12499,7 +12494,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12509,7 +12504,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12524,44 +12524,44 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129601528</v>
+        <v>129601521</v>
       </c>
       <c r="B111" t="n">
-        <v>91587</v>
+        <v>97640</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12571,10 +12571,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>555698</v>
+        <v>555695</v>
       </c>
       <c r="R111" t="n">
-        <v>7046140</v>
+        <v>7046136</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -12633,49 +12633,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129600022</v>
+        <v>129601528</v>
       </c>
       <c r="B112" t="n">
-        <v>98768</v>
+        <v>91588</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>555560</v>
+        <v>555698</v>
       </c>
       <c r="R112" t="n">
-        <v>7046091</v>
+        <v>7046140</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -12734,10 +12730,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129601553</v>
+        <v>129600022</v>
       </c>
       <c r="B113" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12764,22 +12760,22 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>555704</v>
+        <v>555560</v>
       </c>
       <c r="R113" t="n">
-        <v>7046148</v>
+        <v>7046091</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12806,19 +12802,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12833,22 +12819,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129600513</v>
+        <v>129601553</v>
       </c>
       <c r="B114" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12875,27 +12861,22 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>555590</v>
+        <v>555704</v>
       </c>
       <c r="R114" t="n">
-        <v>7046134</v>
+        <v>7046148</v>
       </c>
       <c r="S114" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12924,7 +12905,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12934,7 +12915,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12949,60 +12930,69 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129601521</v>
+        <v>129600513</v>
       </c>
       <c r="B115" t="n">
-        <v>97639</v>
+        <v>98769</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>555695</v>
+        <v>555590</v>
       </c>
       <c r="R115" t="n">
-        <v>7046136</v>
+        <v>7046134</v>
       </c>
       <c r="S115" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13029,9 +13019,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13046,12 +13046,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
@@ -13061,7 +13061,7 @@
         <v>129600727</v>
       </c>
       <c r="B116" t="n">
-        <v>80209</v>
+        <v>80210</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13155,10 +13155,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129600845</v>
+        <v>129602472</v>
       </c>
       <c r="B117" t="n">
-        <v>80180</v>
+        <v>79076</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13166,21 +13166,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13190,13 +13190,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>555681</v>
+        <v>555806</v>
       </c>
       <c r="R117" t="n">
-        <v>7046162</v>
+        <v>7045826</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13223,9 +13223,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13240,22 +13250,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129602472</v>
+        <v>129600845</v>
       </c>
       <c r="B118" t="n">
-        <v>79075</v>
+        <v>80181</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13263,21 +13273,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13287,13 +13297,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>555806</v>
+        <v>555681</v>
       </c>
       <c r="R118" t="n">
-        <v>7045826</v>
+        <v>7046162</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13320,19 +13330,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13347,12 +13347,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -13362,7 +13362,7 @@
         <v>129602025</v>
       </c>
       <c r="B119" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13460,10 +13460,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129602598</v>
+        <v>129602058</v>
       </c>
       <c r="B120" t="n">
-        <v>80180</v>
+        <v>79076</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13471,21 +13471,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13495,13 +13495,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>555768</v>
+        <v>555829</v>
       </c>
       <c r="R120" t="n">
-        <v>7045841</v>
+        <v>7045930</v>
       </c>
       <c r="S120" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13540,7 +13540,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13555,22 +13555,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129600621</v>
+        <v>129602598</v>
       </c>
       <c r="B121" t="n">
-        <v>57735</v>
+        <v>80181</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13578,42 +13578,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>555635</v>
+        <v>555768</v>
       </c>
       <c r="R121" t="n">
-        <v>7046219</v>
+        <v>7045841</v>
       </c>
       <c r="S121" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13640,14 +13635,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13662,22 +13662,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129600175</v>
+        <v>129600978</v>
       </c>
       <c r="B122" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13710,14 +13710,14 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>555493</v>
+        <v>555668</v>
       </c>
       <c r="R122" t="n">
-        <v>7046125</v>
+        <v>7046211</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13749,7 +13749,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
@@ -13779,22 +13779,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129600978</v>
+        <v>129600621</v>
       </c>
       <c r="B123" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13822,22 +13822,22 @@
       <c r="I123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>555668</v>
+        <v>555635</v>
       </c>
       <c r="R123" t="n">
-        <v>7046211</v>
+        <v>7046219</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13864,24 +13864,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13896,22 +13886,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129602058</v>
+        <v>129600175</v>
       </c>
       <c r="B124" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13919,34 +13909,39 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>555829</v>
+        <v>555493</v>
       </c>
       <c r="R124" t="n">
-        <v>7045930</v>
+        <v>7046125</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13978,7 +13973,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13988,7 +13983,12 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14003,12 +14003,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -14018,7 +14018,7 @@
         <v>129601920</v>
       </c>
       <c r="B125" t="n">
-        <v>92070</v>
+        <v>92071</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -6616,49 +6616,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129602004</v>
+        <v>129601480</v>
       </c>
       <c r="B56" t="n">
-        <v>58106</v>
+        <v>80181</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555738</v>
+        <v>555697</v>
       </c>
       <c r="R56" t="n">
-        <v>7046093</v>
+        <v>7046157</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -7339,45 +7335,49 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129601480</v>
+        <v>129602004</v>
       </c>
       <c r="B63" t="n">
-        <v>80181</v>
+        <v>58106</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555697</v>
+        <v>555738</v>
       </c>
       <c r="R63" t="n">
-        <v>7046157</v>
+        <v>7046093</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -8072,10 +8072,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129602553</v>
+        <v>129601748</v>
       </c>
       <c r="B70" t="n">
-        <v>91886</v>
+        <v>80181</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8083,21 +8083,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8107,13 +8107,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>555844</v>
+        <v>555703</v>
       </c>
       <c r="R70" t="n">
-        <v>7045852</v>
+        <v>7046100</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8140,9 +8140,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8157,22 +8167,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129601725</v>
+        <v>129602553</v>
       </c>
       <c r="B71" t="n">
-        <v>80181</v>
+        <v>91886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8180,21 +8190,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8204,13 +8214,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>555750</v>
+        <v>555844</v>
       </c>
       <c r="R71" t="n">
-        <v>7046140</v>
+        <v>7045852</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8237,19 +8247,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>13:49</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8264,66 +8264,57 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129600733</v>
+        <v>129601725</v>
       </c>
       <c r="B72" t="n">
-        <v>98769</v>
+        <v>80181</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>555649</v>
+        <v>555750</v>
       </c>
       <c r="R72" t="n">
-        <v>7046243</v>
+        <v>7046140</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8355,7 +8346,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8365,7 +8356,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8380,19 +8371,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129602304</v>
+        <v>129600733</v>
       </c>
       <c r="B73" t="n">
         <v>98769</v>
@@ -8422,19 +8413,24 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>555857</v>
+        <v>555649</v>
       </c>
       <c r="R73" t="n">
-        <v>7045866</v>
+        <v>7046243</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8466,7 +8462,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8476,7 +8472,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8491,57 +8487,61 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129601748</v>
+        <v>129602304</v>
       </c>
       <c r="B74" t="n">
-        <v>80181</v>
+        <v>98769</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>555703</v>
+        <v>555857</v>
       </c>
       <c r="R74" t="n">
-        <v>7046100</v>
+        <v>7045866</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8598,12 +8598,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -13058,48 +13058,48 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129600727</v>
+        <v>129602472</v>
       </c>
       <c r="B116" t="n">
-        <v>80210</v>
+        <v>79076</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>555605</v>
+        <v>555806</v>
       </c>
       <c r="R116" t="n">
-        <v>7046222</v>
+        <v>7045826</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13126,9 +13126,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13143,22 +13153,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129602472</v>
+        <v>129600845</v>
       </c>
       <c r="B117" t="n">
-        <v>79076</v>
+        <v>80181</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13166,21 +13176,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13190,13 +13200,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>555806</v>
+        <v>555681</v>
       </c>
       <c r="R117" t="n">
-        <v>7045826</v>
+        <v>7046162</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13223,19 +13233,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13250,57 +13250,61 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129600845</v>
+        <v>129602025</v>
       </c>
       <c r="B118" t="n">
-        <v>80181</v>
+        <v>98769</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>555681</v>
+        <v>555739</v>
       </c>
       <c r="R118" t="n">
-        <v>7046162</v>
+        <v>7046093</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13359,49 +13363,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129602025</v>
+        <v>129600727</v>
       </c>
       <c r="B119" t="n">
-        <v>98769</v>
+        <v>80210</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>555739</v>
+        <v>555605</v>
       </c>
       <c r="R119" t="n">
-        <v>7046093</v>
+        <v>7046222</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3830,49 +3830,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129602260</v>
+        <v>129601128</v>
       </c>
       <c r="B30" t="n">
-        <v>98769</v>
+        <v>80215</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555747</v>
+        <v>555698</v>
       </c>
       <c r="R30" t="n">
-        <v>7045963</v>
+        <v>7046187</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3931,57 +3927,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129600015</v>
+        <v>129602332</v>
       </c>
       <c r="B31" t="n">
-        <v>98769</v>
+        <v>80186</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555553</v>
+        <v>555835</v>
       </c>
       <c r="R31" t="n">
-        <v>7046074</v>
+        <v>7045850</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4010,7 +3997,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4020,7 +4007,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,60 +4022,65 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129601128</v>
+        <v>129602543</v>
       </c>
       <c r="B32" t="n">
-        <v>80210</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555698</v>
+        <v>555769</v>
       </c>
       <c r="R32" t="n">
-        <v>7046187</v>
+        <v>7045881</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4115,9 +4107,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4132,60 +4139,64 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129602332</v>
+        <v>129602260</v>
       </c>
       <c r="B33" t="n">
-        <v>80181</v>
+        <v>98774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555835</v>
+        <v>555747</v>
       </c>
       <c r="R33" t="n">
-        <v>7045850</v>
+        <v>7045963</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4212,19 +4223,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4239,65 +4240,69 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129602543</v>
+        <v>129600015</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555769</v>
+        <v>555553</v>
       </c>
       <c r="R34" t="n">
-        <v>7045881</v>
+        <v>7046074</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4326,7 +4331,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4336,12 +4341,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4356,12 +4356,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4371,7 +4371,7 @@
         <v>129602488</v>
       </c>
       <c r="B35" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>129601775</v>
       </c>
       <c r="B36" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>129602548</v>
       </c>
       <c r="B37" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4692,62 +4692,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129602085</v>
+        <v>129601485</v>
       </c>
       <c r="B38" t="n">
-        <v>57896</v>
+        <v>80215</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555725</v>
+        <v>555696</v>
       </c>
       <c r="R38" t="n">
-        <v>7046023</v>
+        <v>7046160</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4774,19 +4760,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4801,22 +4777,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129602219</v>
+        <v>129601980</v>
       </c>
       <c r="B39" t="n">
-        <v>79076</v>
+        <v>91593</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4824,21 +4800,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4848,10 +4824,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555697</v>
+        <v>555724</v>
       </c>
       <c r="R39" t="n">
-        <v>7045963</v>
+        <v>7046089</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4910,48 +4886,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129601485</v>
+        <v>129601909</v>
       </c>
       <c r="B40" t="n">
-        <v>80210</v>
+        <v>57736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555696</v>
+        <v>555726</v>
       </c>
       <c r="R40" t="n">
-        <v>7046160</v>
+        <v>7046072</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4978,9 +4959,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4995,12 +4991,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5010,7 +5006,7 @@
         <v>129602638</v>
       </c>
       <c r="B41" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5104,10 +5100,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129601980</v>
+        <v>129602219</v>
       </c>
       <c r="B42" t="n">
-        <v>91588</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5115,21 +5111,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5139,10 +5135,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>555724</v>
+        <v>555697</v>
       </c>
       <c r="R42" t="n">
-        <v>7046089</v>
+        <v>7045963</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5201,10 +5197,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129601909</v>
+        <v>129602085</v>
       </c>
       <c r="B43" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5212,27 +5208,36 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5241,10 +5246,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>555726</v>
+        <v>555725</v>
       </c>
       <c r="R43" t="n">
-        <v>7046072</v>
+        <v>7046023</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5276,7 +5281,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5286,12 +5291,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5321,7 +5321,7 @@
         <v>129600463</v>
       </c>
       <c r="B44" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>129602321</v>
       </c>
       <c r="B45" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5545,49 +5545,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129603244</v>
+        <v>129601971</v>
       </c>
       <c r="B46" t="n">
-        <v>98769</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555877</v>
+        <v>555791</v>
       </c>
       <c r="R46" t="n">
-        <v>7045808</v>
+        <v>7045965</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5619,7 +5615,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5629,7 +5625,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5656,52 +5652,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129602134</v>
+        <v>129600640</v>
       </c>
       <c r="B47" t="n">
-        <v>98769</v>
+        <v>80186</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555825</v>
+        <v>555615</v>
       </c>
       <c r="R47" t="n">
-        <v>7045910</v>
+        <v>7046128</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5730,7 +5722,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5740,7 +5732,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5755,22 +5747,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129600640</v>
+        <v>129601113</v>
       </c>
       <c r="B48" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5802,13 +5794,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>555615</v>
+        <v>555677</v>
       </c>
       <c r="R48" t="n">
-        <v>7046128</v>
+        <v>7046225</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5835,19 +5827,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5862,57 +5844,61 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129601971</v>
+        <v>129603244</v>
       </c>
       <c r="B49" t="n">
-        <v>79076</v>
+        <v>98774</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>555791</v>
+        <v>555877</v>
       </c>
       <c r="R49" t="n">
-        <v>7045965</v>
+        <v>7045808</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5944,7 +5930,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5954,7 +5940,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5981,48 +5967,52 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129601113</v>
+        <v>129602134</v>
       </c>
       <c r="B50" t="n">
-        <v>80181</v>
+        <v>98774</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555677</v>
+        <v>555825</v>
       </c>
       <c r="R50" t="n">
-        <v>7046225</v>
+        <v>7045910</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6049,9 +6039,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6066,22 +6066,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129602579</v>
+        <v>129600512</v>
       </c>
       <c r="B51" t="n">
-        <v>78833</v>
+        <v>57736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6089,37 +6089,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555842</v>
+        <v>555592</v>
       </c>
       <c r="R51" t="n">
-        <v>7045881</v>
+        <v>7046249</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6146,9 +6151,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6163,22 +6183,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129600512</v>
+        <v>129602579</v>
       </c>
       <c r="B52" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6186,42 +6206,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555592</v>
+        <v>555842</v>
       </c>
       <c r="R52" t="n">
-        <v>7046249</v>
+        <v>7045881</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6248,24 +6263,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6280,12 +6280,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6295,7 +6295,7 @@
         <v>129601611</v>
       </c>
       <c r="B53" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6408,52 +6408,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129600692</v>
+        <v>129600139</v>
       </c>
       <c r="B54" t="n">
-        <v>98769</v>
+        <v>80186</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>555611</v>
+        <v>555553</v>
       </c>
       <c r="R54" t="n">
-        <v>7046241</v>
+        <v>7046074</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6480,9 +6476,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6497,60 +6503,64 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129600139</v>
+        <v>129600692</v>
       </c>
       <c r="B55" t="n">
-        <v>80181</v>
+        <v>98774</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>555553</v>
+        <v>555611</v>
       </c>
       <c r="R55" t="n">
-        <v>7046074</v>
+        <v>7046241</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6577,19 +6587,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6604,12 +6604,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6619,7 +6619,7 @@
         <v>129601480</v>
       </c>
       <c r="B56" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6713,10 +6713,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129602952</v>
+        <v>129601061</v>
       </c>
       <c r="B57" t="n">
-        <v>91552</v>
+        <v>80215</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6724,21 +6724,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555778</v>
+        <v>555707</v>
       </c>
       <c r="R57" t="n">
-        <v>7045842</v>
+        <v>7046194</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6808,60 +6808,64 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129600865</v>
+        <v>129602004</v>
       </c>
       <c r="B58" t="n">
-        <v>91588</v>
+        <v>58106</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555679</v>
+        <v>555738</v>
       </c>
       <c r="R58" t="n">
-        <v>7046243</v>
+        <v>7046093</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6888,19 +6892,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6915,60 +6909,64 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129602023</v>
+        <v>129600524</v>
       </c>
       <c r="B59" t="n">
-        <v>91588</v>
+        <v>98774</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>555819</v>
+        <v>555564</v>
       </c>
       <c r="R59" t="n">
-        <v>7045946</v>
+        <v>7046096</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6995,19 +6993,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7022,60 +7010,60 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129600317</v>
+        <v>129602952</v>
       </c>
       <c r="B60" t="n">
-        <v>91886</v>
+        <v>91557</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>555575</v>
+        <v>555778</v>
       </c>
       <c r="R60" t="n">
-        <v>7046182</v>
+        <v>7045842</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7102,9 +7090,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7119,22 +7117,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129602459</v>
+        <v>129600317</v>
       </c>
       <c r="B61" t="n">
-        <v>91588</v>
+        <v>91891</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7142,34 +7140,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555835</v>
+        <v>555575</v>
       </c>
       <c r="R61" t="n">
-        <v>7045881</v>
+        <v>7046182</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7228,32 +7226,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129601061</v>
+        <v>129600865</v>
       </c>
       <c r="B62" t="n">
-        <v>80210</v>
+        <v>91593</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7263,10 +7261,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555707</v>
+        <v>555679</v>
       </c>
       <c r="R62" t="n">
-        <v>7046194</v>
+        <v>7046243</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7298,7 +7296,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7308,7 +7306,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7323,64 +7321,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129602004</v>
+        <v>129602023</v>
       </c>
       <c r="B63" t="n">
-        <v>58106</v>
+        <v>91593</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555738</v>
+        <v>555819</v>
       </c>
       <c r="R63" t="n">
-        <v>7046093</v>
+        <v>7045946</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7407,9 +7401,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7424,61 +7428,57 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129600524</v>
+        <v>129602459</v>
       </c>
       <c r="B64" t="n">
-        <v>98769</v>
+        <v>91593</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>555564</v>
+        <v>555835</v>
       </c>
       <c r="R64" t="n">
-        <v>7046096</v>
+        <v>7045881</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7540,7 +7540,7 @@
         <v>129601936</v>
       </c>
       <c r="B65" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>129600977</v>
       </c>
       <c r="B66" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>129601012</v>
       </c>
       <c r="B67" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8072,10 +8072,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129601748</v>
+        <v>129602553</v>
       </c>
       <c r="B70" t="n">
-        <v>80181</v>
+        <v>91891</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8083,21 +8083,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8107,13 +8107,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>555703</v>
+        <v>555844</v>
       </c>
       <c r="R70" t="n">
-        <v>7046100</v>
+        <v>7045852</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8140,19 +8140,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8167,60 +8157,69 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129602553</v>
+        <v>129600733</v>
       </c>
       <c r="B71" t="n">
-        <v>91886</v>
+        <v>98774</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>555844</v>
+        <v>555649</v>
       </c>
       <c r="R71" t="n">
-        <v>7045852</v>
+        <v>7046243</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8247,9 +8246,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8264,57 +8273,61 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129601725</v>
+        <v>129602304</v>
       </c>
       <c r="B72" t="n">
-        <v>80181</v>
+        <v>98774</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>555750</v>
+        <v>555857</v>
       </c>
       <c r="R72" t="n">
-        <v>7046140</v>
+        <v>7045866</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8346,7 +8359,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8356,7 +8369,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8383,54 +8396,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129600733</v>
+        <v>129601748</v>
       </c>
       <c r="B73" t="n">
-        <v>98769</v>
+        <v>80186</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>555649</v>
+        <v>555703</v>
       </c>
       <c r="R73" t="n">
-        <v>7046243</v>
+        <v>7046100</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8462,7 +8466,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8472,7 +8476,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8499,49 +8503,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129602304</v>
+        <v>129601725</v>
       </c>
       <c r="B74" t="n">
-        <v>98769</v>
+        <v>80186</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>555857</v>
+        <v>555750</v>
       </c>
       <c r="R74" t="n">
-        <v>7045866</v>
+        <v>7046140</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8613,7 +8613,7 @@
         <v>129600581</v>
       </c>
       <c r="B75" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8721,10 +8721,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129601872</v>
+        <v>129602315</v>
       </c>
       <c r="B76" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8732,42 +8732,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>555721</v>
+        <v>555729</v>
       </c>
       <c r="R76" t="n">
-        <v>7046072</v>
+        <v>7045970</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8796,7 +8791,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8806,12 +8801,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8826,60 +8816,64 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129602315</v>
+        <v>129602094</v>
       </c>
       <c r="B77" t="n">
-        <v>79076</v>
+        <v>98774</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>555729</v>
+        <v>555852</v>
       </c>
       <c r="R77" t="n">
-        <v>7045970</v>
+        <v>7045941</v>
       </c>
       <c r="S77" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8908,7 +8902,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8918,7 +8912,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8933,49 +8927,50 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129602094</v>
+        <v>129601872</v>
       </c>
       <c r="B78" t="n">
-        <v>98769</v>
+        <v>57736</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8984,10 +8979,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>555852</v>
+        <v>555721</v>
       </c>
       <c r="R78" t="n">
-        <v>7045941</v>
+        <v>7046072</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9019,7 +9014,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9029,7 +9024,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9044,12 +9044,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9059,7 +9059,7 @@
         <v>129600219</v>
       </c>
       <c r="B79" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>129602172</v>
       </c>
       <c r="B80" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>129601945</v>
       </c>
       <c r="B81" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9380,32 +9380,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129600975</v>
+        <v>129601548</v>
       </c>
       <c r="B82" t="n">
-        <v>80181</v>
+        <v>80214</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9415,13 +9415,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555633</v>
+        <v>555707</v>
       </c>
       <c r="R82" t="n">
-        <v>7046096</v>
+        <v>7046135</v>
       </c>
       <c r="S82" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9448,19 +9448,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>13:13</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9475,22 +9465,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129601421</v>
+        <v>129600975</v>
       </c>
       <c r="B83" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9522,10 +9512,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555653</v>
+        <v>555633</v>
       </c>
       <c r="R83" t="n">
-        <v>7046187</v>
+        <v>7046096</v>
       </c>
       <c r="S83" t="n">
         <v>3</v>
@@ -9557,7 +9547,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9567,7 +9557,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9594,10 +9584,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129601148</v>
+        <v>129601421</v>
       </c>
       <c r="B84" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9629,13 +9619,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555654</v>
+        <v>555653</v>
       </c>
       <c r="R84" t="n">
-        <v>7046170</v>
+        <v>7046187</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9664,7 +9654,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9674,7 +9664,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9701,32 +9691,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129601548</v>
+        <v>129601148</v>
       </c>
       <c r="B85" t="n">
-        <v>80209</v>
+        <v>80186</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9736,13 +9726,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555707</v>
+        <v>555654</v>
       </c>
       <c r="R85" t="n">
-        <v>7046135</v>
+        <v>7046170</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9769,9 +9759,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9786,12 +9786,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9915,10 +9915,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129602154</v>
+        <v>129600090</v>
       </c>
       <c r="B87" t="n">
-        <v>91588</v>
+        <v>57736</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9926,37 +9926,42 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>555676</v>
+        <v>555491</v>
       </c>
       <c r="R87" t="n">
-        <v>7045998</v>
+        <v>7046111</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9983,9 +9988,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10000,19 +10020,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129600090</v>
+        <v>129602108</v>
       </c>
       <c r="B88" t="n">
         <v>57736</v>
@@ -10048,14 +10068,14 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>555491</v>
+        <v>555854</v>
       </c>
       <c r="R88" t="n">
-        <v>7046111</v>
+        <v>7045940</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10087,7 +10107,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10097,12 +10117,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10117,50 +10137,54 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129602108</v>
+        <v>129602716</v>
       </c>
       <c r="B89" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10169,13 +10193,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>555854</v>
+        <v>555762</v>
       </c>
       <c r="R89" t="n">
-        <v>7045940</v>
+        <v>7045845</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10204,7 +10228,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10214,12 +10238,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10234,22 +10253,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129602716</v>
+        <v>129601612</v>
       </c>
       <c r="B90" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10276,7 +10295,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10290,13 +10309,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>555762</v>
+        <v>555675</v>
       </c>
       <c r="R90" t="n">
-        <v>7045845</v>
+        <v>7046143</v>
       </c>
       <c r="S90" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10325,7 +10344,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10335,7 +10354,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10350,22 +10369,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129601612</v>
+        <v>129603549</v>
       </c>
       <c r="B91" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10392,7 +10411,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10406,10 +10425,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>555675</v>
+        <v>555865</v>
       </c>
       <c r="R91" t="n">
-        <v>7046143</v>
+        <v>7045842</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10441,7 +10460,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10451,7 +10470,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10478,10 +10497,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129603549</v>
+        <v>129601760</v>
       </c>
       <c r="B92" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10508,7 +10527,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -10522,13 +10541,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>555865</v>
+        <v>555694</v>
       </c>
       <c r="R92" t="n">
-        <v>7045842</v>
+        <v>7046166</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10557,7 +10576,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10567,7 +10586,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10582,69 +10601,60 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129601760</v>
+        <v>129602154</v>
       </c>
       <c r="B93" t="n">
-        <v>98769</v>
+        <v>91593</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>555694</v>
+        <v>555676</v>
       </c>
       <c r="R93" t="n">
-        <v>7046166</v>
+        <v>7045998</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10671,19 +10681,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>13:45</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10698,12 +10698,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10713,7 +10713,7 @@
         <v>129602047</v>
       </c>
       <c r="B94" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10817,10 +10817,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129600756</v>
+        <v>129600095</v>
       </c>
       <c r="B95" t="n">
-        <v>80181</v>
+        <v>79081</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10828,37 +10828,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>555626</v>
+        <v>555473</v>
       </c>
       <c r="R95" t="n">
-        <v>7046163</v>
+        <v>7046098</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10885,9 +10885,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10902,22 +10912,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129600095</v>
+        <v>129600756</v>
       </c>
       <c r="B96" t="n">
-        <v>79076</v>
+        <v>80186</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10925,37 +10935,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>555473</v>
+        <v>555626</v>
       </c>
       <c r="R96" t="n">
-        <v>7046098</v>
+        <v>7046163</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10982,19 +10992,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>12:36</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11009,12 +11009,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -11131,7 +11131,7 @@
         <v>129602185</v>
       </c>
       <c r="B98" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11244,10 +11244,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129600791</v>
+        <v>129602252</v>
       </c>
       <c r="B99" t="n">
-        <v>80181</v>
+        <v>91593</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11255,21 +11255,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11279,13 +11279,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>555670</v>
+        <v>555848</v>
       </c>
       <c r="R99" t="n">
-        <v>7046158</v>
+        <v>7045879</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11312,9 +11312,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11329,22 +11339,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129602252</v>
+        <v>129600791</v>
       </c>
       <c r="B100" t="n">
-        <v>91588</v>
+        <v>80186</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11352,21 +11362,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11376,13 +11386,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>555848</v>
+        <v>555670</v>
       </c>
       <c r="R100" t="n">
-        <v>7045879</v>
+        <v>7046158</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11409,19 +11419,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11436,12 +11436,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11682,48 +11682,48 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129600507</v>
+        <v>129601828</v>
       </c>
       <c r="B103" t="n">
-        <v>80181</v>
+        <v>91557</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>555608</v>
+        <v>555724</v>
       </c>
       <c r="R103" t="n">
-        <v>7046222</v>
+        <v>7046097</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11750,19 +11750,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11777,22 +11767,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129602456</v>
+        <v>129600723</v>
       </c>
       <c r="B104" t="n">
-        <v>57733</v>
+        <v>80186</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11800,42 +11790,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>555809</v>
+        <v>555572</v>
       </c>
       <c r="R104" t="n">
-        <v>7045823</v>
+        <v>7046171</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11862,19 +11847,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>14:28</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11889,69 +11864,60 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129602437</v>
+        <v>129600507</v>
       </c>
       <c r="B105" t="n">
-        <v>98769</v>
+        <v>80186</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>555757</v>
+        <v>555608</v>
       </c>
       <c r="R105" t="n">
-        <v>7045907</v>
+        <v>7046222</v>
       </c>
       <c r="S105" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11980,7 +11946,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11990,7 +11956,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12005,49 +11971,50 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129600807</v>
+        <v>129602456</v>
       </c>
       <c r="B106" t="n">
-        <v>98769</v>
+        <v>57733</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -12056,13 +12023,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>555633</v>
+        <v>555809</v>
       </c>
       <c r="R106" t="n">
-        <v>7046097</v>
+        <v>7045823</v>
       </c>
       <c r="S106" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12091,7 +12058,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12101,7 +12068,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12116,60 +12083,69 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129601828</v>
+        <v>129602437</v>
       </c>
       <c r="B107" t="n">
-        <v>91552</v>
+        <v>98774</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>555724</v>
+        <v>555757</v>
       </c>
       <c r="R107" t="n">
-        <v>7046097</v>
+        <v>7045907</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12196,9 +12172,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12213,60 +12199,64 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129601607</v>
+        <v>129600807</v>
       </c>
       <c r="B108" t="n">
-        <v>79076</v>
+        <v>98774</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>555709</v>
+        <v>555633</v>
       </c>
       <c r="R108" t="n">
-        <v>7046133</v>
+        <v>7046097</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12293,9 +12283,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12310,22 +12310,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129600723</v>
+        <v>129601607</v>
       </c>
       <c r="B109" t="n">
-        <v>80181</v>
+        <v>79081</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12333,34 +12333,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>555572</v>
+        <v>555709</v>
       </c>
       <c r="R109" t="n">
-        <v>7046171</v>
+        <v>7046133</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -12536,32 +12536,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129601521</v>
+        <v>129601528</v>
       </c>
       <c r="B111" t="n">
-        <v>97640</v>
+        <v>91593</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12571,10 +12571,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>555695</v>
+        <v>555698</v>
       </c>
       <c r="R111" t="n">
-        <v>7046136</v>
+        <v>7046140</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -12633,32 +12633,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129601528</v>
+        <v>129601521</v>
       </c>
       <c r="B112" t="n">
-        <v>91588</v>
+        <v>97645</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12668,10 +12668,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>555698</v>
+        <v>555695</v>
       </c>
       <c r="R112" t="n">
-        <v>7046140</v>
+        <v>7046136</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -12733,7 +12733,7 @@
         <v>129600022</v>
       </c>
       <c r="B113" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>129601553</v>
       </c>
       <c r="B114" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12945,7 +12945,7 @@
         <v>129600513</v>
       </c>
       <c r="B115" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>129602472</v>
       </c>
       <c r="B116" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13168,7 +13168,7 @@
         <v>129600845</v>
       </c>
       <c r="B117" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13262,49 +13262,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129602025</v>
+        <v>129600727</v>
       </c>
       <c r="B118" t="n">
-        <v>98769</v>
+        <v>80215</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>555739</v>
+        <v>555605</v>
       </c>
       <c r="R118" t="n">
-        <v>7046093</v>
+        <v>7046222</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13363,45 +13359,49 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129600727</v>
+        <v>129602025</v>
       </c>
       <c r="B119" t="n">
-        <v>80210</v>
+        <v>98774</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>555605</v>
+        <v>555739</v>
       </c>
       <c r="R119" t="n">
-        <v>7046222</v>
+        <v>7046093</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -13460,10 +13460,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129602058</v>
+        <v>129602598</v>
       </c>
       <c r="B120" t="n">
-        <v>79076</v>
+        <v>80186</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13471,21 +13471,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13495,13 +13495,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>555829</v>
+        <v>555768</v>
       </c>
       <c r="R120" t="n">
-        <v>7045930</v>
+        <v>7045841</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13540,7 +13540,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13555,22 +13555,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129602598</v>
+        <v>129602058</v>
       </c>
       <c r="B121" t="n">
-        <v>80181</v>
+        <v>79081</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13578,21 +13578,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13602,13 +13602,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>555768</v>
+        <v>555829</v>
       </c>
       <c r="R121" t="n">
-        <v>7045841</v>
+        <v>7045930</v>
       </c>
       <c r="S121" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13662,12 +13662,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -14018,7 +14018,7 @@
         <v>129601920</v>
       </c>
       <c r="B125" t="n">
-        <v>92071</v>
+        <v>92076</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3830,48 +3830,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129601128</v>
+        <v>129602543</v>
       </c>
       <c r="B30" t="n">
-        <v>80215</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555698</v>
+        <v>555769</v>
       </c>
       <c r="R30" t="n">
-        <v>7046187</v>
+        <v>7045881</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3898,9 +3903,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3915,44 +3935,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129602332</v>
+        <v>129601128</v>
       </c>
       <c r="B31" t="n">
-        <v>80186</v>
+        <v>80215</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3962,13 +3982,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555835</v>
+        <v>555698</v>
       </c>
       <c r="R31" t="n">
-        <v>7045850</v>
+        <v>7046187</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3995,19 +4015,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4022,22 +4032,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129602543</v>
+        <v>129602332</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4045,39 +4055,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555769</v>
+        <v>555835</v>
       </c>
       <c r="R32" t="n">
-        <v>7045881</v>
+        <v>7045850</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4109,7 +4114,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4119,12 +4124,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4139,12 +4139,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4692,32 +4692,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129601485</v>
+        <v>129602638</v>
       </c>
       <c r="B38" t="n">
-        <v>80215</v>
+        <v>91891</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555696</v>
+        <v>555826</v>
       </c>
       <c r="R38" t="n">
-        <v>7046160</v>
+        <v>7045880</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129601980</v>
+        <v>129602219</v>
       </c>
       <c r="B39" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4800,21 +4800,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555724</v>
+        <v>555697</v>
       </c>
       <c r="R39" t="n">
-        <v>7046089</v>
+        <v>7045963</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4886,10 +4886,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129601909</v>
+        <v>129601980</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4897,42 +4897,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555726</v>
+        <v>555724</v>
       </c>
       <c r="R40" t="n">
-        <v>7046072</v>
+        <v>7046089</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4959,24 +4954,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4991,44 +4971,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129602638</v>
+        <v>129601485</v>
       </c>
       <c r="B41" t="n">
-        <v>91891</v>
+        <v>80215</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5038,10 +5018,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555826</v>
+        <v>555696</v>
       </c>
       <c r="R41" t="n">
-        <v>7045880</v>
+        <v>7046160</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5100,10 +5080,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129602219</v>
+        <v>129601909</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5111,37 +5091,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>555697</v>
+        <v>555726</v>
       </c>
       <c r="R42" t="n">
-        <v>7045963</v>
+        <v>7046072</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5168,9 +5153,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5185,12 +5185,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5545,45 +5545,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129601971</v>
+        <v>129603244</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555791</v>
+        <v>555877</v>
       </c>
       <c r="R46" t="n">
-        <v>7045965</v>
+        <v>7045808</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5615,7 +5619,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5625,7 +5629,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5652,48 +5656,52 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129600640</v>
+        <v>129602134</v>
       </c>
       <c r="B47" t="n">
-        <v>80186</v>
+        <v>98774</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555615</v>
+        <v>555825</v>
       </c>
       <c r="R47" t="n">
-        <v>7046128</v>
+        <v>7045910</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5722,7 +5730,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5732,7 +5740,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5747,22 +5755,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129601113</v>
+        <v>129601971</v>
       </c>
       <c r="B48" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5770,21 +5778,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5794,13 +5802,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>555677</v>
+        <v>555791</v>
       </c>
       <c r="R48" t="n">
-        <v>7046225</v>
+        <v>7045965</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5827,9 +5835,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5844,64 +5862,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129603244</v>
+        <v>129600640</v>
       </c>
       <c r="B49" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>555877</v>
+        <v>555615</v>
       </c>
       <c r="R49" t="n">
-        <v>7045808</v>
+        <v>7046128</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5930,7 +5944,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5940,7 +5954,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5955,64 +5969,60 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129602134</v>
+        <v>129601113</v>
       </c>
       <c r="B50" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555825</v>
+        <v>555677</v>
       </c>
       <c r="R50" t="n">
-        <v>7045910</v>
+        <v>7046225</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6039,19 +6049,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6066,22 +6066,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129600512</v>
+        <v>129602579</v>
       </c>
       <c r="B51" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6089,42 +6089,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555592</v>
+        <v>555842</v>
       </c>
       <c r="R51" t="n">
-        <v>7046249</v>
+        <v>7045881</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6151,24 +6146,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6183,60 +6163,69 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129602579</v>
+        <v>129601611</v>
       </c>
       <c r="B52" t="n">
-        <v>78838</v>
+        <v>98774</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555842</v>
+        <v>555687</v>
       </c>
       <c r="R52" t="n">
-        <v>7045881</v>
+        <v>7046167</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6263,9 +6252,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6280,69 +6279,65 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129601611</v>
+        <v>129600512</v>
       </c>
       <c r="B53" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555687</v>
+        <v>555592</v>
       </c>
       <c r="R53" t="n">
-        <v>7046167</v>
+        <v>7046249</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6371,7 +6366,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6381,7 +6376,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6396,12 +6396,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6616,10 +6616,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129601480</v>
+        <v>129600865</v>
       </c>
       <c r="B56" t="n">
-        <v>80186</v>
+        <v>91593</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6627,21 +6627,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6651,13 +6651,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555697</v>
+        <v>555679</v>
       </c>
       <c r="R56" t="n">
-        <v>7046157</v>
+        <v>7046243</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6684,9 +6684,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6701,44 +6711,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129601061</v>
+        <v>129602023</v>
       </c>
       <c r="B57" t="n">
-        <v>80215</v>
+        <v>91593</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6748,10 +6758,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555707</v>
+        <v>555819</v>
       </c>
       <c r="R57" t="n">
-        <v>7046194</v>
+        <v>7045946</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6783,7 +6793,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6793,7 +6803,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6808,22 +6818,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129602004</v>
+        <v>129602952</v>
       </c>
       <c r="B58" t="n">
-        <v>58106</v>
+        <v>91557</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6831,41 +6841,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555738</v>
+        <v>555778</v>
       </c>
       <c r="R58" t="n">
-        <v>7046093</v>
+        <v>7045842</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6892,9 +6898,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6909,12 +6925,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7022,48 +7038,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129602952</v>
+        <v>129600317</v>
       </c>
       <c r="B60" t="n">
-        <v>91557</v>
+        <v>91891</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>555778</v>
+        <v>555575</v>
       </c>
       <c r="R60" t="n">
-        <v>7045842</v>
+        <v>7046182</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7090,19 +7106,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:49</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7117,22 +7123,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129600317</v>
+        <v>129602459</v>
       </c>
       <c r="B61" t="n">
-        <v>91891</v>
+        <v>91593</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7140,34 +7146,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555575</v>
+        <v>555835</v>
       </c>
       <c r="R61" t="n">
-        <v>7046182</v>
+        <v>7045881</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7226,10 +7232,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129600865</v>
+        <v>129601480</v>
       </c>
       <c r="B62" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7237,21 +7243,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7261,13 +7267,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555679</v>
+        <v>555697</v>
       </c>
       <c r="R62" t="n">
-        <v>7046243</v>
+        <v>7046157</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7294,19 +7300,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7321,44 +7317,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129602023</v>
+        <v>129601061</v>
       </c>
       <c r="B63" t="n">
-        <v>91593</v>
+        <v>80215</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7368,10 +7364,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555819</v>
+        <v>555707</v>
       </c>
       <c r="R63" t="n">
-        <v>7045946</v>
+        <v>7046194</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7403,7 +7399,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7413,7 +7409,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7428,57 +7424,61 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129602459</v>
+        <v>129602004</v>
       </c>
       <c r="B64" t="n">
-        <v>91593</v>
+        <v>58106</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>555835</v>
+        <v>555738</v>
       </c>
       <c r="R64" t="n">
-        <v>7045881</v>
+        <v>7046093</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7751,10 +7751,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129601012</v>
+        <v>129602371</v>
       </c>
       <c r="B67" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7762,37 +7762,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>555680</v>
+        <v>555825</v>
       </c>
       <c r="R67" t="n">
-        <v>7046211</v>
+        <v>7045806</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7819,9 +7824,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7836,19 +7856,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129602371</v>
+        <v>129601541</v>
       </c>
       <c r="B68" t="n">
         <v>57736</v>
@@ -7879,7 +7899,7 @@
       <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7888,13 +7908,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>555825</v>
+        <v>555702</v>
       </c>
       <c r="R68" t="n">
-        <v>7045806</v>
+        <v>7046142</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7921,24 +7941,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7953,22 +7963,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129601541</v>
+        <v>129601012</v>
       </c>
       <c r="B69" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7976,39 +7986,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>555702</v>
+        <v>555680</v>
       </c>
       <c r="R69" t="n">
-        <v>7046142</v>
+        <v>7046211</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8041,11 +8046,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8169,54 +8169,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129600733</v>
+        <v>129601748</v>
       </c>
       <c r="B71" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>555649</v>
+        <v>555703</v>
       </c>
       <c r="R71" t="n">
-        <v>7046243</v>
+        <v>7046100</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8248,7 +8239,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8258,7 +8249,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8285,49 +8276,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129602304</v>
+        <v>129601725</v>
       </c>
       <c r="B72" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>555857</v>
+        <v>555750</v>
       </c>
       <c r="R72" t="n">
-        <v>7045866</v>
+        <v>7046140</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8359,7 +8346,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8369,7 +8356,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8396,45 +8383,54 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129601748</v>
+        <v>129600733</v>
       </c>
       <c r="B73" t="n">
-        <v>80186</v>
+        <v>98774</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>555703</v>
+        <v>555649</v>
       </c>
       <c r="R73" t="n">
-        <v>7046100</v>
+        <v>7046243</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8466,7 +8462,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8476,7 +8472,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8503,45 +8499,49 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129601725</v>
+        <v>129602304</v>
       </c>
       <c r="B74" t="n">
-        <v>80186</v>
+        <v>98774</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>555750</v>
+        <v>555857</v>
       </c>
       <c r="R74" t="n">
-        <v>7046140</v>
+        <v>7045866</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8721,48 +8721,52 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129602315</v>
+        <v>129602094</v>
       </c>
       <c r="B76" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>555729</v>
+        <v>555852</v>
       </c>
       <c r="R76" t="n">
-        <v>7045970</v>
+        <v>7045941</v>
       </c>
       <c r="S76" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8791,7 +8795,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8801,7 +8805,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8816,64 +8820,60 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129602094</v>
+        <v>129602315</v>
       </c>
       <c r="B77" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>555852</v>
+        <v>555729</v>
       </c>
       <c r="R77" t="n">
-        <v>7045941</v>
+        <v>7045970</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8927,12 +8927,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9153,37 +9153,38 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129602172</v>
+        <v>129603240</v>
       </c>
       <c r="B80" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>9</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9192,10 +9193,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555855</v>
+        <v>555865</v>
       </c>
       <c r="R80" t="n">
-        <v>7045892</v>
+        <v>7045842</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9227,7 +9228,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9237,7 +9238,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9252,69 +9258,60 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129601945</v>
+        <v>129601548</v>
       </c>
       <c r="B81" t="n">
-        <v>98774</v>
+        <v>80214</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555730</v>
+        <v>555707</v>
       </c>
       <c r="R81" t="n">
-        <v>7046151</v>
+        <v>7046135</v>
       </c>
       <c r="S81" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9341,19 +9338,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>13:53</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9368,44 +9355,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129601548</v>
+        <v>129600975</v>
       </c>
       <c r="B82" t="n">
-        <v>80214</v>
+        <v>80186</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9415,13 +9402,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555707</v>
+        <v>555633</v>
       </c>
       <c r="R82" t="n">
-        <v>7046135</v>
+        <v>7046096</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9448,9 +9435,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9465,19 +9462,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129600975</v>
+        <v>129601421</v>
       </c>
       <c r="B83" t="n">
         <v>80186</v>
@@ -9512,10 +9509,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555633</v>
+        <v>555653</v>
       </c>
       <c r="R83" t="n">
-        <v>7046096</v>
+        <v>7046187</v>
       </c>
       <c r="S83" t="n">
         <v>3</v>
@@ -9547,7 +9544,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9557,7 +9554,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9584,7 +9581,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129601421</v>
+        <v>129601148</v>
       </c>
       <c r="B84" t="n">
         <v>80186</v>
@@ -9619,13 +9616,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555653</v>
+        <v>555654</v>
       </c>
       <c r="R84" t="n">
-        <v>7046187</v>
+        <v>7046170</v>
       </c>
       <c r="S84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9654,7 +9651,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9664,7 +9661,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9691,48 +9688,52 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129601148</v>
+        <v>129602172</v>
       </c>
       <c r="B85" t="n">
-        <v>80186</v>
+        <v>98774</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555654</v>
+        <v>555855</v>
       </c>
       <c r="R85" t="n">
-        <v>7046170</v>
+        <v>7045892</v>
       </c>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9761,7 +9762,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9771,7 +9772,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9786,50 +9787,54 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129603240</v>
+        <v>129601945</v>
       </c>
       <c r="B86" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9838,13 +9843,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>555865</v>
+        <v>555730</v>
       </c>
       <c r="R86" t="n">
-        <v>7045842</v>
+        <v>7046151</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9873,7 +9878,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9883,12 +9888,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9903,12 +9903,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -10924,10 +10924,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129600756</v>
+        <v>129602416</v>
       </c>
       <c r="B96" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10935,34 +10935,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>555626</v>
+        <v>555801</v>
       </c>
       <c r="R96" t="n">
-        <v>7046163</v>
+        <v>7045860</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10995,6 +11000,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11021,10 +11031,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129602416</v>
+        <v>129600756</v>
       </c>
       <c r="B97" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11032,39 +11042,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>555801</v>
+        <v>555626</v>
       </c>
       <c r="R97" t="n">
-        <v>7045860</v>
+        <v>7046163</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -11097,11 +11102,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11244,10 +11244,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129602252</v>
+        <v>129600791</v>
       </c>
       <c r="B99" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11255,21 +11255,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11279,13 +11279,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>555848</v>
+        <v>555670</v>
       </c>
       <c r="R99" t="n">
-        <v>7045879</v>
+        <v>7046158</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11312,19 +11312,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11339,22 +11329,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129600791</v>
+        <v>129602252</v>
       </c>
       <c r="B100" t="n">
-        <v>80186</v>
+        <v>91593</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11362,21 +11352,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11386,13 +11376,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>555670</v>
+        <v>555848</v>
       </c>
       <c r="R100" t="n">
-        <v>7046158</v>
+        <v>7045879</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11419,9 +11409,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11436,12 +11436,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11682,48 +11682,53 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129601828</v>
+        <v>129602456</v>
       </c>
       <c r="B103" t="n">
-        <v>91557</v>
+        <v>57733</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>555724</v>
+        <v>555809</v>
       </c>
       <c r="R103" t="n">
-        <v>7046097</v>
+        <v>7045823</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11750,9 +11755,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11767,22 +11782,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129600723</v>
+        <v>129601709</v>
       </c>
       <c r="B104" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11790,37 +11805,42 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>555572</v>
+        <v>555739</v>
       </c>
       <c r="R104" t="n">
-        <v>7046171</v>
+        <v>7046139</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11847,9 +11867,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11864,60 +11899,60 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129600507</v>
+        <v>129601828</v>
       </c>
       <c r="B105" t="n">
-        <v>80186</v>
+        <v>91557</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>555608</v>
+        <v>555724</v>
       </c>
       <c r="R105" t="n">
-        <v>7046222</v>
+        <v>7046097</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11944,19 +11979,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11971,22 +11996,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129602456</v>
+        <v>129601607</v>
       </c>
       <c r="B106" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11994,42 +12019,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>555809</v>
+        <v>555709</v>
       </c>
       <c r="R106" t="n">
-        <v>7045823</v>
+        <v>7046133</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12056,19 +12076,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>14:28</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12083,69 +12093,60 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129602437</v>
+        <v>129600723</v>
       </c>
       <c r="B107" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>555757</v>
+        <v>555572</v>
       </c>
       <c r="R107" t="n">
-        <v>7045907</v>
+        <v>7046171</v>
       </c>
       <c r="S107" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12172,19 +12173,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12199,64 +12190,60 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129600807</v>
+        <v>129600507</v>
       </c>
       <c r="B108" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>555633</v>
+        <v>555608</v>
       </c>
       <c r="R108" t="n">
-        <v>7046097</v>
+        <v>7046222</v>
       </c>
       <c r="S108" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12285,7 +12272,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12295,7 +12282,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12310,60 +12297,69 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129601607</v>
+        <v>129602437</v>
       </c>
       <c r="B109" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>555709</v>
+        <v>555757</v>
       </c>
       <c r="R109" t="n">
-        <v>7046133</v>
+        <v>7045907</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12390,9 +12386,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12407,50 +12413,49 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129601709</v>
+        <v>129600807</v>
       </c>
       <c r="B110" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -12459,13 +12464,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>555739</v>
+        <v>555633</v>
       </c>
       <c r="R110" t="n">
-        <v>7046139</v>
+        <v>7046097</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12494,7 +12499,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12504,12 +12509,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12524,12 +12524,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -12633,45 +12633,49 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129601521</v>
+        <v>129600022</v>
       </c>
       <c r="B112" t="n">
-        <v>97645</v>
+        <v>98774</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>555695</v>
+        <v>555560</v>
       </c>
       <c r="R112" t="n">
-        <v>7046136</v>
+        <v>7046091</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -12730,7 +12734,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129600022</v>
+        <v>129601553</v>
       </c>
       <c r="B113" t="n">
         <v>98774</v>
@@ -12760,22 +12764,22 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>555560</v>
+        <v>555704</v>
       </c>
       <c r="R113" t="n">
-        <v>7046091</v>
+        <v>7046148</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12802,9 +12806,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12819,19 +12833,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129601553</v>
+        <v>129600513</v>
       </c>
       <c r="B114" t="n">
         <v>98774</v>
@@ -12861,22 +12875,27 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>555704</v>
+        <v>555590</v>
       </c>
       <c r="R114" t="n">
-        <v>7046148</v>
+        <v>7046134</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12905,7 +12924,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12915,7 +12934,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12930,69 +12949,60 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129600513</v>
+        <v>129601521</v>
       </c>
       <c r="B115" t="n">
-        <v>98774</v>
+        <v>97645</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>555590</v>
+        <v>555695</v>
       </c>
       <c r="R115" t="n">
-        <v>7046134</v>
+        <v>7046136</v>
       </c>
       <c r="S115" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13019,19 +13029,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13046,12 +13046,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
@@ -13165,45 +13165,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129600845</v>
+        <v>129600727</v>
       </c>
       <c r="B117" t="n">
-        <v>80186</v>
+        <v>80215</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>555681</v>
+        <v>555605</v>
       </c>
       <c r="R117" t="n">
-        <v>7046162</v>
+        <v>7046222</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13262,45 +13262,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129600727</v>
+        <v>129600845</v>
       </c>
       <c r="B118" t="n">
-        <v>80215</v>
+        <v>80186</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>555605</v>
+        <v>555681</v>
       </c>
       <c r="R118" t="n">
-        <v>7046222</v>
+        <v>7046162</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13460,10 +13460,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129602598</v>
+        <v>129600978</v>
       </c>
       <c r="B120" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13471,37 +13471,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>555768</v>
+        <v>555668</v>
       </c>
       <c r="R120" t="n">
-        <v>7045841</v>
+        <v>7046211</v>
       </c>
       <c r="S120" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13530,7 +13535,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13540,7 +13545,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13555,22 +13565,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129602058</v>
+        <v>129600621</v>
       </c>
       <c r="B121" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13578,37 +13588,42 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>555829</v>
+        <v>555635</v>
       </c>
       <c r="R121" t="n">
-        <v>7045930</v>
+        <v>7046219</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13635,19 +13650,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>14:04</t>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13662,19 +13672,19 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129600978</v>
+        <v>129600175</v>
       </c>
       <c r="B122" t="n">
         <v>57736</v>
@@ -13710,14 +13720,14 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>555668</v>
+        <v>555493</v>
       </c>
       <c r="R122" t="n">
-        <v>7046211</v>
+        <v>7046125</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13749,7 +13759,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13759,7 +13769,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
@@ -13779,22 +13789,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129600621</v>
+        <v>129602058</v>
       </c>
       <c r="B123" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13802,42 +13812,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>555635</v>
+        <v>555829</v>
       </c>
       <c r="R123" t="n">
-        <v>7046219</v>
+        <v>7045930</v>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13864,14 +13869,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13886,22 +13896,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129600175</v>
+        <v>129602598</v>
       </c>
       <c r="B124" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13909,42 +13919,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>555493</v>
+        <v>555768</v>
       </c>
       <c r="R124" t="n">
-        <v>7046125</v>
+        <v>7045841</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13973,7 +13978,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13983,12 +13988,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14003,12 +14003,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3830,53 +3830,57 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129602543</v>
+        <v>129600015</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555769</v>
+        <v>555553</v>
       </c>
       <c r="R30" t="n">
-        <v>7045881</v>
+        <v>7046074</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3905,7 +3909,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3915,12 +3919,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3935,57 +3934,61 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129601128</v>
+        <v>129602260</v>
       </c>
       <c r="B31" t="n">
-        <v>80215</v>
+        <v>98774</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555698</v>
+        <v>555747</v>
       </c>
       <c r="R31" t="n">
-        <v>7046187</v>
+        <v>7045963</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4044,32 +4047,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129602332</v>
+        <v>129601128</v>
       </c>
       <c r="B32" t="n">
-        <v>80186</v>
+        <v>80215</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4079,13 +4082,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555835</v>
+        <v>555698</v>
       </c>
       <c r="R32" t="n">
-        <v>7045850</v>
+        <v>7046187</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4112,19 +4115,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4139,64 +4132,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129602260</v>
+        <v>129602332</v>
       </c>
       <c r="B33" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555747</v>
+        <v>555835</v>
       </c>
       <c r="R33" t="n">
-        <v>7045963</v>
+        <v>7045850</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4223,9 +4212,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4240,69 +4239,65 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129600015</v>
+        <v>129602543</v>
       </c>
       <c r="B34" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555553</v>
+        <v>555769</v>
       </c>
       <c r="R34" t="n">
-        <v>7046074</v>
+        <v>7045881</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4331,7 +4326,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4341,7 +4336,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4356,12 +4356,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4692,32 +4692,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129602638</v>
+        <v>129601485</v>
       </c>
       <c r="B38" t="n">
-        <v>91891</v>
+        <v>80215</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555826</v>
+        <v>555696</v>
       </c>
       <c r="R38" t="n">
-        <v>7045880</v>
+        <v>7046160</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129602219</v>
+        <v>129602085</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4800,37 +4800,51 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555697</v>
+        <v>555725</v>
       </c>
       <c r="R39" t="n">
-        <v>7045963</v>
+        <v>7046023</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4857,9 +4871,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4874,22 +4898,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129601980</v>
+        <v>129601909</v>
       </c>
       <c r="B40" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4897,37 +4921,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555724</v>
+        <v>555726</v>
       </c>
       <c r="R40" t="n">
-        <v>7046089</v>
+        <v>7046072</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4954,9 +4983,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4971,44 +5015,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129601485</v>
+        <v>129602638</v>
       </c>
       <c r="B41" t="n">
-        <v>80215</v>
+        <v>91891</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5018,10 +5062,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555696</v>
+        <v>555826</v>
       </c>
       <c r="R41" t="n">
-        <v>7046160</v>
+        <v>7045880</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5080,10 +5124,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129601909</v>
+        <v>129601980</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5091,42 +5135,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>555726</v>
+        <v>555724</v>
       </c>
       <c r="R42" t="n">
-        <v>7046072</v>
+        <v>7046089</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5153,24 +5192,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5185,22 +5209,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129602085</v>
+        <v>129602219</v>
       </c>
       <c r="B43" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5208,51 +5232,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>555725</v>
+        <v>555697</v>
       </c>
       <c r="R43" t="n">
-        <v>7046023</v>
+        <v>7045963</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5279,19 +5289,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5306,12 +5306,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5545,52 +5545,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129603244</v>
+        <v>129600640</v>
       </c>
       <c r="B46" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555877</v>
+        <v>555615</v>
       </c>
       <c r="R46" t="n">
-        <v>7045808</v>
+        <v>7046128</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5619,7 +5615,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5629,7 +5625,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5644,64 +5640,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129602134</v>
+        <v>129601113</v>
       </c>
       <c r="B47" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555825</v>
+        <v>555677</v>
       </c>
       <c r="R47" t="n">
-        <v>7045910</v>
+        <v>7046225</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5728,19 +5720,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5755,12 +5737,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5874,48 +5856,52 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129600640</v>
+        <v>129603244</v>
       </c>
       <c r="B49" t="n">
-        <v>80186</v>
+        <v>98774</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>555615</v>
+        <v>555877</v>
       </c>
       <c r="R49" t="n">
-        <v>7046128</v>
+        <v>7045808</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5944,7 +5930,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5954,7 +5940,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5969,60 +5955,64 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129601113</v>
+        <v>129602134</v>
       </c>
       <c r="B50" t="n">
-        <v>80186</v>
+        <v>98774</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555677</v>
+        <v>555825</v>
       </c>
       <c r="R50" t="n">
-        <v>7046225</v>
+        <v>7045910</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6049,9 +6039,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6066,60 +6066,69 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129602579</v>
+        <v>129601611</v>
       </c>
       <c r="B51" t="n">
-        <v>78838</v>
+        <v>98774</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555842</v>
+        <v>555687</v>
       </c>
       <c r="R51" t="n">
-        <v>7045881</v>
+        <v>7046167</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6146,9 +6155,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6163,69 +6182,65 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129601611</v>
+        <v>129600512</v>
       </c>
       <c r="B52" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555687</v>
+        <v>555592</v>
       </c>
       <c r="R52" t="n">
-        <v>7046167</v>
+        <v>7046249</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6254,7 +6269,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6264,7 +6279,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6279,22 +6299,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129600512</v>
+        <v>129602579</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6302,42 +6322,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555592</v>
+        <v>555842</v>
       </c>
       <c r="R53" t="n">
-        <v>7046249</v>
+        <v>7045881</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6364,24 +6379,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6396,12 +6396,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6616,10 +6616,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129600865</v>
+        <v>129601480</v>
       </c>
       <c r="B56" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6627,21 +6627,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6651,13 +6651,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555679</v>
+        <v>555697</v>
       </c>
       <c r="R56" t="n">
-        <v>7046243</v>
+        <v>7046157</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6684,19 +6684,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6711,44 +6701,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129602023</v>
+        <v>129602952</v>
       </c>
       <c r="B57" t="n">
-        <v>91593</v>
+        <v>91557</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6758,10 +6748,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555819</v>
+        <v>555778</v>
       </c>
       <c r="R57" t="n">
-        <v>7045946</v>
+        <v>7045842</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6793,7 +6783,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6803,7 +6793,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6830,32 +6820,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129602952</v>
+        <v>129602459</v>
       </c>
       <c r="B58" t="n">
-        <v>91557</v>
+        <v>91593</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6865,13 +6855,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555778</v>
+        <v>555835</v>
       </c>
       <c r="R58" t="n">
-        <v>7045842</v>
+        <v>7045881</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6898,19 +6888,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:49</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6925,64 +6905,60 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129600524</v>
+        <v>129600865</v>
       </c>
       <c r="B59" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>555564</v>
+        <v>555679</v>
       </c>
       <c r="R59" t="n">
-        <v>7046096</v>
+        <v>7046243</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7009,9 +6985,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7026,22 +7012,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129600317</v>
+        <v>129602023</v>
       </c>
       <c r="B60" t="n">
-        <v>91891</v>
+        <v>91593</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7049,37 +7035,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>555575</v>
+        <v>555819</v>
       </c>
       <c r="R60" t="n">
-        <v>7046182</v>
+        <v>7045946</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7106,9 +7092,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7123,22 +7119,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129602459</v>
+        <v>129600317</v>
       </c>
       <c r="B61" t="n">
-        <v>91593</v>
+        <v>91891</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7146,34 +7142,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555835</v>
+        <v>555575</v>
       </c>
       <c r="R61" t="n">
-        <v>7045881</v>
+        <v>7046182</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7232,32 +7228,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129601480</v>
+        <v>129601061</v>
       </c>
       <c r="B62" t="n">
-        <v>80186</v>
+        <v>80215</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7267,13 +7263,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555697</v>
+        <v>555707</v>
       </c>
       <c r="R62" t="n">
-        <v>7046157</v>
+        <v>7046194</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7300,9 +7296,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7317,22 +7323,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129601061</v>
+        <v>129602004</v>
       </c>
       <c r="B63" t="n">
-        <v>80215</v>
+        <v>58106</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7340,37 +7346,41 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555707</v>
+        <v>555738</v>
       </c>
       <c r="R63" t="n">
-        <v>7046194</v>
+        <v>7046093</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7397,19 +7407,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7424,61 +7424,61 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129602004</v>
+        <v>129600524</v>
       </c>
       <c r="B64" t="n">
-        <v>58106</v>
+        <v>98774</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>555738</v>
+        <v>555564</v>
       </c>
       <c r="R64" t="n">
-        <v>7046093</v>
+        <v>7046096</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7537,10 +7537,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129601936</v>
+        <v>129601012</v>
       </c>
       <c r="B65" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7548,21 +7548,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7572,13 +7572,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>555804</v>
+        <v>555680</v>
       </c>
       <c r="R65" t="n">
-        <v>7046004</v>
+        <v>7046211</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7605,19 +7605,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7632,22 +7622,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129600977</v>
+        <v>129602371</v>
       </c>
       <c r="B66" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7655,34 +7645,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>555704</v>
+        <v>555825</v>
       </c>
       <c r="R66" t="n">
-        <v>7046202</v>
+        <v>7045806</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7714,7 +7709,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7724,7 +7719,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7739,19 +7739,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129602371</v>
+        <v>129601541</v>
       </c>
       <c r="B67" t="n">
         <v>57736</v>
@@ -7782,7 +7782,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7791,13 +7791,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>555825</v>
+        <v>555702</v>
       </c>
       <c r="R67" t="n">
-        <v>7045806</v>
+        <v>7046142</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7824,24 +7824,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7856,22 +7846,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129601541</v>
+        <v>129600977</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7879,42 +7869,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>555702</v>
+        <v>555704</v>
       </c>
       <c r="R68" t="n">
-        <v>7046142</v>
+        <v>7046202</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7941,14 +7926,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7963,22 +7953,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129601012</v>
+        <v>129601936</v>
       </c>
       <c r="B69" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7986,21 +7976,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8010,13 +8000,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>555680</v>
+        <v>555804</v>
       </c>
       <c r="R69" t="n">
-        <v>7046211</v>
+        <v>7046004</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8043,9 +8033,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8060,22 +8060,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129602553</v>
+        <v>129601748</v>
       </c>
       <c r="B70" t="n">
-        <v>91891</v>
+        <v>80186</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8083,21 +8083,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8107,13 +8107,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>555844</v>
+        <v>555703</v>
       </c>
       <c r="R70" t="n">
-        <v>7045852</v>
+        <v>7046100</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8140,9 +8140,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8157,19 +8167,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129601748</v>
+        <v>129601725</v>
       </c>
       <c r="B71" t="n">
         <v>80186</v>
@@ -8204,10 +8214,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>555703</v>
+        <v>555750</v>
       </c>
       <c r="R71" t="n">
-        <v>7046100</v>
+        <v>7046140</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8239,7 +8249,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8249,7 +8259,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8264,22 +8274,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129601725</v>
+        <v>129602553</v>
       </c>
       <c r="B72" t="n">
-        <v>80186</v>
+        <v>91891</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8287,21 +8297,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8311,13 +8321,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>555750</v>
+        <v>555844</v>
       </c>
       <c r="R72" t="n">
-        <v>7046140</v>
+        <v>7045852</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8344,19 +8354,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>13:49</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8371,12 +8371,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8721,52 +8721,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129602094</v>
+        <v>129602315</v>
       </c>
       <c r="B76" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>555852</v>
+        <v>555729</v>
       </c>
       <c r="R76" t="n">
-        <v>7045941</v>
+        <v>7045970</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8795,7 +8791,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8805,7 +8801,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8820,22 +8816,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129602315</v>
+        <v>129601872</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8843,37 +8839,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>555729</v>
+        <v>555721</v>
       </c>
       <c r="R77" t="n">
-        <v>7045970</v>
+        <v>7046072</v>
       </c>
       <c r="S77" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8902,7 +8903,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8912,7 +8913,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8927,50 +8933,49 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129601872</v>
+        <v>129602094</v>
       </c>
       <c r="B78" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8979,10 +8984,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>555721</v>
+        <v>555852</v>
       </c>
       <c r="R78" t="n">
-        <v>7046072</v>
+        <v>7045941</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9014,7 +9019,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9024,12 +9029,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9044,12 +9044,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9153,53 +9153,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129603240</v>
+        <v>129601548</v>
       </c>
       <c r="B80" t="n">
-        <v>57736</v>
+        <v>80214</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555865</v>
+        <v>555707</v>
       </c>
       <c r="R80" t="n">
-        <v>7045842</v>
+        <v>7046135</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9226,24 +9221,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9258,44 +9238,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129601548</v>
+        <v>129600975</v>
       </c>
       <c r="B81" t="n">
-        <v>80214</v>
+        <v>80186</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9305,13 +9285,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555707</v>
+        <v>555633</v>
       </c>
       <c r="R81" t="n">
-        <v>7046135</v>
+        <v>7046096</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9338,9 +9318,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9355,19 +9345,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129600975</v>
+        <v>129601421</v>
       </c>
       <c r="B82" t="n">
         <v>80186</v>
@@ -9402,10 +9392,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>555633</v>
+        <v>555653</v>
       </c>
       <c r="R82" t="n">
-        <v>7046096</v>
+        <v>7046187</v>
       </c>
       <c r="S82" t="n">
         <v>3</v>
@@ -9437,7 +9427,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9447,7 +9437,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9474,7 +9464,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129601421</v>
+        <v>129601148</v>
       </c>
       <c r="B83" t="n">
         <v>80186</v>
@@ -9509,13 +9499,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555653</v>
+        <v>555654</v>
       </c>
       <c r="R83" t="n">
-        <v>7046187</v>
+        <v>7046170</v>
       </c>
       <c r="S83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9544,7 +9534,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9554,7 +9544,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9581,10 +9571,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129601148</v>
+        <v>129603240</v>
       </c>
       <c r="B84" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9592,37 +9582,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555654</v>
+        <v>555865</v>
       </c>
       <c r="R84" t="n">
-        <v>7046170</v>
+        <v>7045842</v>
       </c>
       <c r="S84" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9651,7 +9646,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9661,7 +9656,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9676,12 +9676,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9915,10 +9915,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129600090</v>
+        <v>129602154</v>
       </c>
       <c r="B87" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9926,42 +9926,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>555491</v>
+        <v>555676</v>
       </c>
       <c r="R87" t="n">
-        <v>7046111</v>
+        <v>7045998</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9988,24 +9983,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10020,19 +10000,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129602108</v>
+        <v>129600090</v>
       </c>
       <c r="B88" t="n">
         <v>57736</v>
@@ -10068,14 +10048,14 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>555854</v>
+        <v>555491</v>
       </c>
       <c r="R88" t="n">
-        <v>7045940</v>
+        <v>7046111</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10107,7 +10087,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10117,12 +10097,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10137,54 +10117,50 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129602716</v>
+        <v>129602108</v>
       </c>
       <c r="B89" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10193,13 +10169,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>555762</v>
+        <v>555854</v>
       </c>
       <c r="R89" t="n">
-        <v>7045845</v>
+        <v>7045940</v>
       </c>
       <c r="S89" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10228,7 +10204,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10238,7 +10214,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10253,19 +10234,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129601612</v>
+        <v>129602716</v>
       </c>
       <c r="B90" t="n">
         <v>98774</v>
@@ -10295,7 +10276,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10309,13 +10290,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>555675</v>
+        <v>555762</v>
       </c>
       <c r="R90" t="n">
-        <v>7046143</v>
+        <v>7045845</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10344,7 +10325,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10354,7 +10335,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10369,19 +10350,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129603549</v>
+        <v>129601612</v>
       </c>
       <c r="B91" t="n">
         <v>98774</v>
@@ -10411,7 +10392,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10425,10 +10406,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>555865</v>
+        <v>555675</v>
       </c>
       <c r="R91" t="n">
-        <v>7045842</v>
+        <v>7046143</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10460,7 +10441,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10470,7 +10451,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10497,7 +10478,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129601760</v>
+        <v>129603549</v>
       </c>
       <c r="B92" t="n">
         <v>98774</v>
@@ -10527,7 +10508,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -10541,13 +10522,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>555694</v>
+        <v>555865</v>
       </c>
       <c r="R92" t="n">
-        <v>7046166</v>
+        <v>7045842</v>
       </c>
       <c r="S92" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10576,7 +10557,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10586,7 +10567,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10601,60 +10582,69 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129602154</v>
+        <v>129601760</v>
       </c>
       <c r="B93" t="n">
-        <v>91593</v>
+        <v>98774</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>555676</v>
+        <v>555694</v>
       </c>
       <c r="R93" t="n">
-        <v>7045998</v>
+        <v>7046166</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10681,9 +10671,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10698,22 +10698,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129602047</v>
+        <v>129600756</v>
       </c>
       <c r="B94" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10721,21 +10721,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10745,13 +10745,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>555722</v>
+        <v>555626</v>
       </c>
       <c r="R94" t="n">
-        <v>7046017</v>
+        <v>7046163</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10778,19 +10778,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10805,19 +10795,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129600095</v>
+        <v>129602047</v>
       </c>
       <c r="B95" t="n">
         <v>79081</v>
@@ -10848,14 +10838,14 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>555473</v>
+        <v>555722</v>
       </c>
       <c r="R95" t="n">
-        <v>7046098</v>
+        <v>7046017</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10887,7 +10877,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10897,7 +10887,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10912,22 +10902,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129602416</v>
+        <v>129600095</v>
       </c>
       <c r="B96" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10935,42 +10925,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>555801</v>
+        <v>555473</v>
       </c>
       <c r="R96" t="n">
-        <v>7045860</v>
+        <v>7046098</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10997,14 +10982,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11019,22 +11009,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129600756</v>
+        <v>129602416</v>
       </c>
       <c r="B97" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11042,34 +11032,39 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>555626</v>
+        <v>555801</v>
       </c>
       <c r="R97" t="n">
-        <v>7046163</v>
+        <v>7045860</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -11102,6 +11097,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11244,10 +11244,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129600791</v>
+        <v>129602252</v>
       </c>
       <c r="B99" t="n">
-        <v>80186</v>
+        <v>91593</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11255,21 +11255,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11279,13 +11279,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>555670</v>
+        <v>555848</v>
       </c>
       <c r="R99" t="n">
-        <v>7046158</v>
+        <v>7045879</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11312,9 +11312,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11329,22 +11339,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129602252</v>
+        <v>129600791</v>
       </c>
       <c r="B100" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11352,21 +11362,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11376,13 +11386,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>555848</v>
+        <v>555670</v>
       </c>
       <c r="R100" t="n">
-        <v>7045879</v>
+        <v>7046158</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11409,19 +11419,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11436,12 +11436,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11682,10 +11682,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129602456</v>
+        <v>129601607</v>
       </c>
       <c r="B103" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11693,42 +11693,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>555809</v>
+        <v>555709</v>
       </c>
       <c r="R103" t="n">
-        <v>7045823</v>
+        <v>7046133</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11755,19 +11750,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>14:28</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11782,65 +11767,60 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129601709</v>
+        <v>129601828</v>
       </c>
       <c r="B104" t="n">
-        <v>57736</v>
+        <v>91557</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>555739</v>
+        <v>555724</v>
       </c>
       <c r="R104" t="n">
-        <v>7046139</v>
+        <v>7046097</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11867,24 +11847,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11899,57 +11864,57 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129601828</v>
+        <v>129600723</v>
       </c>
       <c r="B105" t="n">
-        <v>91557</v>
+        <v>80186</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>555724</v>
+        <v>555572</v>
       </c>
       <c r="R105" t="n">
-        <v>7046097</v>
+        <v>7046171</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -12008,10 +11973,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129601607</v>
+        <v>129600507</v>
       </c>
       <c r="B106" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12019,37 +11984,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>555709</v>
+        <v>555608</v>
       </c>
       <c r="R106" t="n">
-        <v>7046133</v>
+        <v>7046222</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12076,9 +12041,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12093,22 +12068,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129600723</v>
+        <v>129602456</v>
       </c>
       <c r="B107" t="n">
-        <v>80186</v>
+        <v>57733</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12116,37 +12091,42 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>555572</v>
+        <v>555809</v>
       </c>
       <c r="R107" t="n">
-        <v>7046171</v>
+        <v>7045823</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12173,9 +12153,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12190,22 +12180,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129600507</v>
+        <v>129601709</v>
       </c>
       <c r="B108" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12213,34 +12203,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>555608</v>
+        <v>555739</v>
       </c>
       <c r="R108" t="n">
-        <v>7046222</v>
+        <v>7046139</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12272,7 +12267,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12282,7 +12277,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12309,7 +12309,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129602437</v>
+        <v>129600807</v>
       </c>
       <c r="B109" t="n">
         <v>98774</v>
@@ -12339,12 +12339,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -12353,10 +12348,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>555757</v>
+        <v>555633</v>
       </c>
       <c r="R109" t="n">
-        <v>7045907</v>
+        <v>7046097</v>
       </c>
       <c r="S109" t="n">
         <v>4</v>
@@ -12388,7 +12383,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12398,7 +12393,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12425,7 +12420,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129600807</v>
+        <v>129602437</v>
       </c>
       <c r="B110" t="n">
         <v>98774</v>
@@ -12455,7 +12450,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -12464,10 +12464,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>555633</v>
+        <v>555757</v>
       </c>
       <c r="R110" t="n">
-        <v>7046097</v>
+        <v>7045907</v>
       </c>
       <c r="S110" t="n">
         <v>4</v>
@@ -12499,7 +12499,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12536,45 +12536,49 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129601528</v>
+        <v>129600022</v>
       </c>
       <c r="B111" t="n">
-        <v>91593</v>
+        <v>98774</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>555698</v>
+        <v>555560</v>
       </c>
       <c r="R111" t="n">
-        <v>7046140</v>
+        <v>7046091</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -12633,7 +12637,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129600022</v>
+        <v>129601553</v>
       </c>
       <c r="B112" t="n">
         <v>98774</v>
@@ -12663,22 +12667,22 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>555560</v>
+        <v>555704</v>
       </c>
       <c r="R112" t="n">
-        <v>7046091</v>
+        <v>7046148</v>
       </c>
       <c r="S112" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12705,9 +12709,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12722,19 +12736,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129601553</v>
+        <v>129600513</v>
       </c>
       <c r="B113" t="n">
         <v>98774</v>
@@ -12764,22 +12778,27 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>555704</v>
+        <v>555590</v>
       </c>
       <c r="R113" t="n">
-        <v>7046148</v>
+        <v>7046134</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12808,7 +12827,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12818,7 +12837,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12833,69 +12852,60 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129600513</v>
+        <v>129601521</v>
       </c>
       <c r="B114" t="n">
-        <v>98774</v>
+        <v>97645</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>555590</v>
+        <v>555695</v>
       </c>
       <c r="R114" t="n">
-        <v>7046134</v>
+        <v>7046136</v>
       </c>
       <c r="S114" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12922,19 +12932,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12949,44 +12949,44 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129601521</v>
+        <v>129601528</v>
       </c>
       <c r="B115" t="n">
-        <v>97645</v>
+        <v>91593</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12996,10 +12996,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>555695</v>
+        <v>555698</v>
       </c>
       <c r="R115" t="n">
-        <v>7046136</v>
+        <v>7046140</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -13058,48 +13058,48 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129602472</v>
+        <v>129600727</v>
       </c>
       <c r="B116" t="n">
-        <v>79081</v>
+        <v>80215</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>555806</v>
+        <v>555605</v>
       </c>
       <c r="R116" t="n">
-        <v>7045826</v>
+        <v>7046222</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13126,19 +13126,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13153,57 +13143,57 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129600727</v>
+        <v>129600845</v>
       </c>
       <c r="B117" t="n">
-        <v>80215</v>
+        <v>80186</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>555605</v>
+        <v>555681</v>
       </c>
       <c r="R117" t="n">
-        <v>7046222</v>
+        <v>7046162</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13262,45 +13252,49 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129600845</v>
+        <v>129602025</v>
       </c>
       <c r="B118" t="n">
-        <v>80186</v>
+        <v>98774</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>555681</v>
+        <v>555739</v>
       </c>
       <c r="R118" t="n">
-        <v>7046162</v>
+        <v>7046093</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13359,52 +13353,48 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129602025</v>
+        <v>129602472</v>
       </c>
       <c r="B119" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>555739</v>
+        <v>555806</v>
       </c>
       <c r="R119" t="n">
-        <v>7046093</v>
+        <v>7045826</v>
       </c>
       <c r="S119" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13431,9 +13421,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13448,22 +13448,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129600978</v>
+        <v>129602058</v>
       </c>
       <c r="B120" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13471,39 +13471,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>555668</v>
+        <v>555829</v>
       </c>
       <c r="R120" t="n">
-        <v>7046211</v>
+        <v>7045930</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13535,7 +13530,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13545,12 +13540,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13577,7 +13567,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129600621</v>
+        <v>129600175</v>
       </c>
       <c r="B121" t="n">
         <v>57736</v>
@@ -13608,7 +13598,7 @@
       <c r="I121" t="inlineStr"/>
       <c r="M121" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -13617,13 +13607,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>555635</v>
+        <v>555493</v>
       </c>
       <c r="R121" t="n">
-        <v>7046219</v>
+        <v>7046125</v>
       </c>
       <c r="S121" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13650,14 +13640,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Ringhack, gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13672,22 +13672,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129600175</v>
+        <v>129602598</v>
       </c>
       <c r="B122" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13695,42 +13695,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>555493</v>
+        <v>555768</v>
       </c>
       <c r="R122" t="n">
-        <v>7046125</v>
+        <v>7045841</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13759,7 +13754,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13769,12 +13764,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13789,22 +13779,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129602058</v>
+        <v>129600978</v>
       </c>
       <c r="B123" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13812,34 +13802,39 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>555829</v>
+        <v>555668</v>
       </c>
       <c r="R123" t="n">
-        <v>7045930</v>
+        <v>7046211</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13871,7 +13866,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13881,7 +13876,12 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13908,10 +13908,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129602598</v>
+        <v>129600621</v>
       </c>
       <c r="B124" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13919,37 +13919,42 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>555768</v>
+        <v>555635</v>
       </c>
       <c r="R124" t="n">
-        <v>7045841</v>
+        <v>7046219</v>
       </c>
       <c r="S124" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13976,19 +13981,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>14:31</t>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14003,12 +14003,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3830,7 +3830,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129600015</v>
+        <v>129602260</v>
       </c>
       <c r="B30" t="n">
         <v>98774</v>
@@ -3860,27 +3860,22 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555553</v>
+        <v>555747</v>
       </c>
       <c r="R30" t="n">
-        <v>7046074</v>
+        <v>7045963</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3907,19 +3902,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3934,19 +3919,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129602260</v>
+        <v>129600015</v>
       </c>
       <c r="B31" t="n">
         <v>98774</v>
@@ -3976,22 +3961,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555747</v>
+        <v>555553</v>
       </c>
       <c r="R31" t="n">
-        <v>7045963</v>
+        <v>7046074</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4018,9 +4008,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,12 +4035,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4692,32 +4692,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129601485</v>
+        <v>129601980</v>
       </c>
       <c r="B38" t="n">
-        <v>80215</v>
+        <v>91593</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555696</v>
+        <v>555724</v>
       </c>
       <c r="R38" t="n">
-        <v>7046160</v>
+        <v>7046089</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129602085</v>
+        <v>129602638</v>
       </c>
       <c r="B39" t="n">
-        <v>57896</v>
+        <v>91891</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4800,51 +4800,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555725</v>
+        <v>555826</v>
       </c>
       <c r="R39" t="n">
-        <v>7046023</v>
+        <v>7045880</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4871,19 +4857,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4898,22 +4874,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129601909</v>
+        <v>129602219</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4921,42 +4897,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555726</v>
+        <v>555697</v>
       </c>
       <c r="R40" t="n">
-        <v>7046072</v>
+        <v>7045963</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4983,24 +4954,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5015,44 +4971,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129602638</v>
+        <v>129601485</v>
       </c>
       <c r="B41" t="n">
-        <v>91891</v>
+        <v>80215</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5062,10 +5018,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555826</v>
+        <v>555696</v>
       </c>
       <c r="R41" t="n">
-        <v>7045880</v>
+        <v>7046160</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5124,10 +5080,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129601980</v>
+        <v>129601909</v>
       </c>
       <c r="B42" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5135,37 +5091,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>555724</v>
+        <v>555726</v>
       </c>
       <c r="R42" t="n">
-        <v>7046089</v>
+        <v>7046072</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5192,9 +5153,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5209,22 +5185,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129602219</v>
+        <v>129602085</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5232,37 +5208,51 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>555697</v>
+        <v>555725</v>
       </c>
       <c r="R43" t="n">
-        <v>7045963</v>
+        <v>7046023</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5289,9 +5279,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5306,12 +5306,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5545,48 +5545,52 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129600640</v>
+        <v>129603244</v>
       </c>
       <c r="B46" t="n">
-        <v>80186</v>
+        <v>98774</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555615</v>
+        <v>555877</v>
       </c>
       <c r="R46" t="n">
-        <v>7046128</v>
+        <v>7045808</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5615,7 +5619,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5625,7 +5629,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5640,60 +5644,64 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129601113</v>
+        <v>129602134</v>
       </c>
       <c r="B47" t="n">
-        <v>80186</v>
+        <v>98774</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555677</v>
+        <v>555825</v>
       </c>
       <c r="R47" t="n">
-        <v>7046225</v>
+        <v>7045910</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5720,9 +5728,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5737,22 +5755,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129601971</v>
+        <v>129600640</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5760,21 +5778,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5784,13 +5802,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>555791</v>
+        <v>555615</v>
       </c>
       <c r="R48" t="n">
-        <v>7045965</v>
+        <v>7046128</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5819,7 +5837,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5829,7 +5847,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5844,61 +5862,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129603244</v>
+        <v>129601971</v>
       </c>
       <c r="B49" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>555877</v>
+        <v>555791</v>
       </c>
       <c r="R49" t="n">
-        <v>7045808</v>
+        <v>7045965</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5930,7 +5944,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5940,7 +5954,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5967,52 +5981,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129602134</v>
+        <v>129601113</v>
       </c>
       <c r="B50" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555825</v>
+        <v>555677</v>
       </c>
       <c r="R50" t="n">
-        <v>7045910</v>
+        <v>7046225</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6039,19 +6049,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6066,69 +6066,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129601611</v>
+        <v>129602579</v>
       </c>
       <c r="B51" t="n">
-        <v>98774</v>
+        <v>78838</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555687</v>
+        <v>555842</v>
       </c>
       <c r="R51" t="n">
-        <v>7046167</v>
+        <v>7045881</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6155,19 +6146,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>13:41</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6182,12 +6163,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6311,48 +6292,57 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129602579</v>
+        <v>129601611</v>
       </c>
       <c r="B53" t="n">
-        <v>78838</v>
+        <v>98774</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555842</v>
+        <v>555687</v>
       </c>
       <c r="R53" t="n">
-        <v>7045881</v>
+        <v>7046167</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6379,9 +6369,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6396,12 +6396,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6616,32 +6616,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129601480</v>
+        <v>129602952</v>
       </c>
       <c r="B56" t="n">
-        <v>80186</v>
+        <v>91557</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6651,13 +6651,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555697</v>
+        <v>555778</v>
       </c>
       <c r="R56" t="n">
-        <v>7046157</v>
+        <v>7045842</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6684,9 +6684,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6701,22 +6711,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129602952</v>
+        <v>129601061</v>
       </c>
       <c r="B57" t="n">
-        <v>91557</v>
+        <v>80215</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6724,21 +6734,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6748,10 +6758,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555778</v>
+        <v>555707</v>
       </c>
       <c r="R57" t="n">
-        <v>7045842</v>
+        <v>7046194</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6783,7 +6793,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6793,7 +6803,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6808,22 +6818,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129602459</v>
+        <v>129601480</v>
       </c>
       <c r="B58" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6831,21 +6841,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6855,10 +6865,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555835</v>
+        <v>555697</v>
       </c>
       <c r="R58" t="n">
-        <v>7045881</v>
+        <v>7046157</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6917,48 +6927,52 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129600865</v>
+        <v>129600524</v>
       </c>
       <c r="B59" t="n">
-        <v>91593</v>
+        <v>98774</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>555679</v>
+        <v>555564</v>
       </c>
       <c r="R59" t="n">
-        <v>7046243</v>
+        <v>7046096</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6985,19 +6999,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7012,22 +7016,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129602023</v>
+        <v>129600317</v>
       </c>
       <c r="B60" t="n">
-        <v>91593</v>
+        <v>91891</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7035,37 +7039,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>555819</v>
+        <v>555575</v>
       </c>
       <c r="R60" t="n">
-        <v>7045946</v>
+        <v>7046182</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7092,19 +7096,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7119,22 +7113,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129600317</v>
+        <v>129602023</v>
       </c>
       <c r="B61" t="n">
-        <v>91891</v>
+        <v>91593</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7142,37 +7136,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555575</v>
+        <v>555819</v>
       </c>
       <c r="R61" t="n">
-        <v>7046182</v>
+        <v>7045946</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7199,9 +7193,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7216,44 +7220,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129601061</v>
+        <v>129600865</v>
       </c>
       <c r="B62" t="n">
-        <v>80215</v>
+        <v>91593</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7263,10 +7267,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555707</v>
+        <v>555679</v>
       </c>
       <c r="R62" t="n">
-        <v>7046194</v>
+        <v>7046243</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7298,7 +7302,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7308,7 +7312,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7323,61 +7327,57 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129602004</v>
+        <v>129602459</v>
       </c>
       <c r="B63" t="n">
-        <v>58106</v>
+        <v>91593</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555738</v>
+        <v>555835</v>
       </c>
       <c r="R63" t="n">
-        <v>7046093</v>
+        <v>7045881</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7436,49 +7436,49 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129600524</v>
+        <v>129602004</v>
       </c>
       <c r="B64" t="n">
-        <v>98774</v>
+        <v>58106</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>555564</v>
+        <v>555738</v>
       </c>
       <c r="R64" t="n">
-        <v>7046096</v>
+        <v>7046093</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7634,10 +7634,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129602371</v>
+        <v>129601936</v>
       </c>
       <c r="B66" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7645,39 +7645,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>555825</v>
+        <v>555804</v>
       </c>
       <c r="R66" t="n">
-        <v>7045806</v>
+        <v>7046004</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7709,7 +7704,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7719,12 +7714,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7751,10 +7741,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129601541</v>
+        <v>129600977</v>
       </c>
       <c r="B67" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7762,42 +7752,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>555702</v>
+        <v>555704</v>
       </c>
       <c r="R67" t="n">
-        <v>7046142</v>
+        <v>7046202</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7824,14 +7809,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7846,22 +7836,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129600977</v>
+        <v>129602371</v>
       </c>
       <c r="B68" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7869,34 +7859,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>555704</v>
+        <v>555825</v>
       </c>
       <c r="R68" t="n">
-        <v>7046202</v>
+        <v>7045806</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7928,7 +7923,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7938,7 +7933,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7953,22 +7953,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129601936</v>
+        <v>129601541</v>
       </c>
       <c r="B69" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7976,37 +7976,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>555804</v>
+        <v>555702</v>
       </c>
       <c r="R69" t="n">
-        <v>7046004</v>
+        <v>7046142</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8033,19 +8038,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>13:57</t>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8060,12 +8060,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8721,48 +8721,52 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129602315</v>
+        <v>129602094</v>
       </c>
       <c r="B76" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>555729</v>
+        <v>555852</v>
       </c>
       <c r="R76" t="n">
-        <v>7045970</v>
+        <v>7045941</v>
       </c>
       <c r="S76" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8791,7 +8795,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8801,7 +8805,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8816,22 +8820,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129601872</v>
+        <v>129602315</v>
       </c>
       <c r="B77" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8839,42 +8843,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>555721</v>
+        <v>555729</v>
       </c>
       <c r="R77" t="n">
-        <v>7046072</v>
+        <v>7045970</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8903,7 +8902,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8913,12 +8912,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8933,49 +8927,50 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129602094</v>
+        <v>129601872</v>
       </c>
       <c r="B78" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8984,10 +8979,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>555852</v>
+        <v>555721</v>
       </c>
       <c r="R78" t="n">
-        <v>7045941</v>
+        <v>7046072</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9019,7 +9014,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9029,7 +9024,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9044,12 +9044,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9915,10 +9915,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129602154</v>
+        <v>129600090</v>
       </c>
       <c r="B87" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9926,37 +9926,42 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>555676</v>
+        <v>555491</v>
       </c>
       <c r="R87" t="n">
-        <v>7045998</v>
+        <v>7046111</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9983,9 +9988,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10000,19 +10020,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129600090</v>
+        <v>129602108</v>
       </c>
       <c r="B88" t="n">
         <v>57736</v>
@@ -10048,14 +10068,14 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>555491</v>
+        <v>555854</v>
       </c>
       <c r="R88" t="n">
-        <v>7046111</v>
+        <v>7045940</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10087,7 +10107,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10097,12 +10117,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10117,22 +10137,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129602108</v>
+        <v>129602154</v>
       </c>
       <c r="B89" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10140,42 +10160,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>555854</v>
+        <v>555676</v>
       </c>
       <c r="R89" t="n">
-        <v>7045940</v>
+        <v>7045998</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10202,24 +10217,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10234,19 +10234,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129602716</v>
+        <v>129601612</v>
       </c>
       <c r="B90" t="n">
         <v>98774</v>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10290,13 +10290,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>555762</v>
+        <v>555675</v>
       </c>
       <c r="R90" t="n">
-        <v>7045845</v>
+        <v>7046143</v>
       </c>
       <c r="S90" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10335,7 +10335,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10350,19 +10350,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129601612</v>
+        <v>129603549</v>
       </c>
       <c r="B91" t="n">
         <v>98774</v>
@@ -10392,7 +10392,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10406,10 +10406,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>555675</v>
+        <v>555865</v>
       </c>
       <c r="R91" t="n">
-        <v>7046143</v>
+        <v>7045842</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10441,7 +10441,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10478,7 +10478,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129603549</v>
+        <v>129601760</v>
       </c>
       <c r="B92" t="n">
         <v>98774</v>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -10522,13 +10522,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>555865</v>
+        <v>555694</v>
       </c>
       <c r="R92" t="n">
-        <v>7045842</v>
+        <v>7046166</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10582,19 +10582,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129601760</v>
+        <v>129602716</v>
       </c>
       <c r="B93" t="n">
         <v>98774</v>
@@ -10624,7 +10624,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -10638,13 +10638,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>555694</v>
+        <v>555762</v>
       </c>
       <c r="R93" t="n">
-        <v>7046166</v>
+        <v>7045845</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10710,10 +10710,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129600756</v>
+        <v>129602047</v>
       </c>
       <c r="B94" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10721,21 +10721,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10745,13 +10745,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>555626</v>
+        <v>555722</v>
       </c>
       <c r="R94" t="n">
-        <v>7046163</v>
+        <v>7046017</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10778,9 +10778,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10795,22 +10805,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129602047</v>
+        <v>129600756</v>
       </c>
       <c r="B95" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10818,21 +10828,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10842,13 +10852,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>555722</v>
+        <v>555626</v>
       </c>
       <c r="R95" t="n">
-        <v>7046017</v>
+        <v>7046163</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10875,19 +10885,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10902,12 +10902,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -11682,10 +11682,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129601607</v>
+        <v>129600723</v>
       </c>
       <c r="B103" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11693,34 +11693,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>555709</v>
+        <v>555572</v>
       </c>
       <c r="R103" t="n">
-        <v>7046133</v>
+        <v>7046171</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -11779,48 +11779,48 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129601828</v>
+        <v>129600507</v>
       </c>
       <c r="B104" t="n">
-        <v>91557</v>
+        <v>80186</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>555724</v>
+        <v>555608</v>
       </c>
       <c r="R104" t="n">
-        <v>7046097</v>
+        <v>7046222</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11847,9 +11847,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11864,22 +11874,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129600723</v>
+        <v>129601607</v>
       </c>
       <c r="B105" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11887,34 +11897,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>555572</v>
+        <v>555709</v>
       </c>
       <c r="R105" t="n">
-        <v>7046171</v>
+        <v>7046133</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11973,10 +11983,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129600507</v>
+        <v>129602456</v>
       </c>
       <c r="B106" t="n">
-        <v>80186</v>
+        <v>57733</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11984,34 +11994,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>555608</v>
+        <v>555809</v>
       </c>
       <c r="R106" t="n">
-        <v>7046222</v>
+        <v>7045823</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12043,7 +12058,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12053,7 +12068,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12080,53 +12095,48 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129602456</v>
+        <v>129601828</v>
       </c>
       <c r="B107" t="n">
-        <v>57733</v>
+        <v>91557</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>555809</v>
+        <v>555724</v>
       </c>
       <c r="R107" t="n">
-        <v>7045823</v>
+        <v>7046097</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12153,19 +12163,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>14:28</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12180,12 +12180,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -12309,7 +12309,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129600807</v>
+        <v>129602437</v>
       </c>
       <c r="B109" t="n">
         <v>98774</v>
@@ -12339,7 +12339,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -12348,10 +12353,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>555633</v>
+        <v>555757</v>
       </c>
       <c r="R109" t="n">
-        <v>7046097</v>
+        <v>7045907</v>
       </c>
       <c r="S109" t="n">
         <v>4</v>
@@ -12383,7 +12388,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12393,7 +12398,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12420,7 +12425,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129602437</v>
+        <v>129600807</v>
       </c>
       <c r="B110" t="n">
         <v>98774</v>
@@ -12450,12 +12455,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -12464,10 +12464,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>555757</v>
+        <v>555633</v>
       </c>
       <c r="R110" t="n">
-        <v>7045907</v>
+        <v>7046097</v>
       </c>
       <c r="S110" t="n">
         <v>4</v>
@@ -12499,7 +12499,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12536,49 +12536,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129600022</v>
+        <v>129601521</v>
       </c>
       <c r="B111" t="n">
-        <v>98774</v>
+        <v>97645</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>555560</v>
+        <v>555695</v>
       </c>
       <c r="R111" t="n">
-        <v>7046091</v>
+        <v>7046136</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -12637,52 +12633,48 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129601553</v>
+        <v>129601528</v>
       </c>
       <c r="B112" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>555704</v>
+        <v>555698</v>
       </c>
       <c r="R112" t="n">
-        <v>7046148</v>
+        <v>7046140</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12709,19 +12701,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>13:44</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12736,19 +12718,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129600513</v>
+        <v>129600022</v>
       </c>
       <c r="B113" t="n">
         <v>98774</v>
@@ -12781,24 +12763,19 @@
           <t>50</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>555590</v>
+        <v>555560</v>
       </c>
       <c r="R113" t="n">
-        <v>7046134</v>
+        <v>7046091</v>
       </c>
       <c r="S113" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12825,19 +12802,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12852,60 +12819,64 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129601521</v>
+        <v>129601553</v>
       </c>
       <c r="B114" t="n">
-        <v>97645</v>
+        <v>98774</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>555695</v>
+        <v>555704</v>
       </c>
       <c r="R114" t="n">
-        <v>7046136</v>
+        <v>7046148</v>
       </c>
       <c r="S114" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12932,9 +12903,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12949,60 +12930,69 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129601528</v>
+        <v>129600513</v>
       </c>
       <c r="B115" t="n">
-        <v>91593</v>
+        <v>98774</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>555698</v>
+        <v>555590</v>
       </c>
       <c r="R115" t="n">
-        <v>7046140</v>
+        <v>7046134</v>
       </c>
       <c r="S115" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13029,9 +13019,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13046,57 +13046,61 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129600727</v>
+        <v>129602025</v>
       </c>
       <c r="B116" t="n">
-        <v>80215</v>
+        <v>98774</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>555605</v>
+        <v>555739</v>
       </c>
       <c r="R116" t="n">
-        <v>7046222</v>
+        <v>7046093</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -13155,45 +13159,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129600845</v>
+        <v>129600727</v>
       </c>
       <c r="B117" t="n">
-        <v>80186</v>
+        <v>80215</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>555681</v>
+        <v>555605</v>
       </c>
       <c r="R117" t="n">
-        <v>7046162</v>
+        <v>7046222</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13252,52 +13256,48 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129602025</v>
+        <v>129602472</v>
       </c>
       <c r="B118" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>555739</v>
+        <v>555806</v>
       </c>
       <c r="R118" t="n">
-        <v>7046093</v>
+        <v>7045826</v>
       </c>
       <c r="S118" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13324,9 +13324,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13341,22 +13351,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129602472</v>
+        <v>129600845</v>
       </c>
       <c r="B119" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13364,21 +13374,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13388,13 +13398,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>555806</v>
+        <v>555681</v>
       </c>
       <c r="R119" t="n">
-        <v>7045826</v>
+        <v>7046162</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13421,19 +13431,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13448,12 +13448,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
@@ -13567,10 +13567,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129600175</v>
+        <v>129602598</v>
       </c>
       <c r="B121" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13578,42 +13578,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>555493</v>
+        <v>555768</v>
       </c>
       <c r="R121" t="n">
-        <v>7046125</v>
+        <v>7045841</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13642,7 +13637,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13652,12 +13647,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13672,22 +13662,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129602598</v>
+        <v>129600978</v>
       </c>
       <c r="B122" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13695,37 +13685,42 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>555768</v>
+        <v>555668</v>
       </c>
       <c r="R122" t="n">
-        <v>7045841</v>
+        <v>7046211</v>
       </c>
       <c r="S122" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13754,7 +13749,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13764,7 +13759,12 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13779,19 +13779,19 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129600978</v>
+        <v>129600621</v>
       </c>
       <c r="B123" t="n">
         <v>57736</v>
@@ -13822,22 +13822,22 @@
       <c r="I123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>555668</v>
+        <v>555635</v>
       </c>
       <c r="R123" t="n">
-        <v>7046211</v>
+        <v>7046219</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13864,24 +13864,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13896,19 +13886,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129600621</v>
+        <v>129600175</v>
       </c>
       <c r="B124" t="n">
         <v>57736</v>
@@ -13939,7 +13929,7 @@
       <c r="I124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -13948,13 +13938,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>555635</v>
+        <v>555493</v>
       </c>
       <c r="R124" t="n">
-        <v>7046219</v>
+        <v>7046125</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13981,14 +13971,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Ringhack, gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14003,12 +14003,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3830,37 +3830,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129602260</v>
+        <v>129602543</v>
       </c>
       <c r="B30" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3869,13 +3870,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555747</v>
+        <v>555769</v>
       </c>
       <c r="R30" t="n">
-        <v>7045963</v>
+        <v>7045881</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3902,9 +3903,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3919,69 +3935,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129600015</v>
+        <v>129602332</v>
       </c>
       <c r="B31" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555553</v>
+        <v>555835</v>
       </c>
       <c r="R31" t="n">
-        <v>7046074</v>
+        <v>7045850</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4010,7 +4017,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4020,7 +4027,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,12 +4042,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4144,48 +4151,52 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129602332</v>
+        <v>129602260</v>
       </c>
       <c r="B33" t="n">
-        <v>80186</v>
+        <v>98778</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555835</v>
+        <v>555747</v>
       </c>
       <c r="R33" t="n">
-        <v>7045850</v>
+        <v>7045963</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4212,19 +4223,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4239,65 +4240,69 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129602543</v>
+        <v>129600015</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>98778</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555769</v>
+        <v>555553</v>
       </c>
       <c r="R34" t="n">
-        <v>7045881</v>
+        <v>7046074</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4326,7 +4331,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4336,12 +4341,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4356,12 +4356,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4371,7 +4371,7 @@
         <v>129602488</v>
       </c>
       <c r="B35" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4465,10 +4465,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129601775</v>
+        <v>129602548</v>
       </c>
       <c r="B36" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4495,7 +4495,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4504,13 +4509,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555746</v>
+        <v>555770</v>
       </c>
       <c r="R36" t="n">
-        <v>7046137</v>
+        <v>7045888</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4539,7 +4544,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4549,7 +4554,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4564,22 +4569,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129602548</v>
+        <v>129601775</v>
       </c>
       <c r="B37" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4606,12 +4611,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4620,13 +4620,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555770</v>
+        <v>555746</v>
       </c>
       <c r="R37" t="n">
-        <v>7045888</v>
+        <v>7046137</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4680,44 +4680,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129601980</v>
+        <v>129601485</v>
       </c>
       <c r="B38" t="n">
-        <v>91593</v>
+        <v>80215</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555724</v>
+        <v>555696</v>
       </c>
       <c r="R38" t="n">
-        <v>7046089</v>
+        <v>7046160</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129602638</v>
+        <v>129602219</v>
       </c>
       <c r="B39" t="n">
-        <v>91891</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4800,21 +4800,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555826</v>
+        <v>555697</v>
       </c>
       <c r="R39" t="n">
-        <v>7045880</v>
+        <v>7045963</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4886,10 +4886,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129602219</v>
+        <v>129602638</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>91895</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4897,21 +4897,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555697</v>
+        <v>555826</v>
       </c>
       <c r="R40" t="n">
-        <v>7045963</v>
+        <v>7045880</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4983,32 +4983,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129601485</v>
+        <v>129601980</v>
       </c>
       <c r="B41" t="n">
-        <v>80215</v>
+        <v>91597</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555696</v>
+        <v>555724</v>
       </c>
       <c r="R41" t="n">
-        <v>7046160</v>
+        <v>7046089</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5318,10 +5318,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129600463</v>
+        <v>129602321</v>
       </c>
       <c r="B44" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5348,27 +5348,22 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>555579</v>
+        <v>555847</v>
       </c>
       <c r="R44" t="n">
-        <v>7046146</v>
+        <v>7045866</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5397,7 +5392,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5407,7 +5402,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5422,22 +5417,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129602321</v>
+        <v>129600463</v>
       </c>
       <c r="B45" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5464,22 +5459,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>555847</v>
+        <v>555579</v>
       </c>
       <c r="R45" t="n">
-        <v>7045866</v>
+        <v>7046146</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5533,64 +5533,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129603244</v>
+        <v>129600640</v>
       </c>
       <c r="B46" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>555877</v>
+        <v>555615</v>
       </c>
       <c r="R46" t="n">
-        <v>7045808</v>
+        <v>7046128</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5619,7 +5615,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5629,7 +5625,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5644,64 +5640,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129602134</v>
+        <v>129601113</v>
       </c>
       <c r="B47" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>555825</v>
+        <v>555677</v>
       </c>
       <c r="R47" t="n">
-        <v>7045910</v>
+        <v>7046225</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5728,19 +5720,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5755,60 +5737,64 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129600640</v>
+        <v>129602134</v>
       </c>
       <c r="B48" t="n">
-        <v>80186</v>
+        <v>98778</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>555615</v>
+        <v>555825</v>
       </c>
       <c r="R48" t="n">
-        <v>7046128</v>
+        <v>7045910</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5837,7 +5823,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5847,7 +5833,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5862,57 +5848,61 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129601971</v>
+        <v>129603244</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>555791</v>
+        <v>555877</v>
       </c>
       <c r="R49" t="n">
-        <v>7045965</v>
+        <v>7045808</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5944,7 +5934,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5954,7 +5944,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5981,10 +5971,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129601113</v>
+        <v>129601971</v>
       </c>
       <c r="B50" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5992,21 +5982,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6016,13 +6006,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555677</v>
+        <v>555791</v>
       </c>
       <c r="R50" t="n">
-        <v>7046225</v>
+        <v>7045965</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6049,9 +6039,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6066,60 +6066,69 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129602579</v>
+        <v>129601611</v>
       </c>
       <c r="B51" t="n">
-        <v>78838</v>
+        <v>98778</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555842</v>
+        <v>555687</v>
       </c>
       <c r="R51" t="n">
-        <v>7045881</v>
+        <v>7046167</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6146,9 +6155,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6163,22 +6182,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129600512</v>
+        <v>129602579</v>
       </c>
       <c r="B52" t="n">
-        <v>57736</v>
+        <v>78838</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6186,42 +6205,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>555592</v>
+        <v>555842</v>
       </c>
       <c r="R52" t="n">
-        <v>7046249</v>
+        <v>7045881</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6248,24 +6262,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6280,69 +6279,65 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129601611</v>
+        <v>129600512</v>
       </c>
       <c r="B53" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555687</v>
+        <v>555592</v>
       </c>
       <c r="R53" t="n">
-        <v>7046167</v>
+        <v>7046249</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6371,7 +6366,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6381,7 +6376,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6396,12 +6396,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6518,7 +6518,7 @@
         <v>129600692</v>
       </c>
       <c r="B55" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6616,32 +6616,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129602952</v>
+        <v>129601480</v>
       </c>
       <c r="B56" t="n">
-        <v>91557</v>
+        <v>80186</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6651,13 +6651,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555778</v>
+        <v>555697</v>
       </c>
       <c r="R56" t="n">
-        <v>7045842</v>
+        <v>7046157</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6684,19 +6684,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>14:49</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6711,22 +6701,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129601061</v>
+        <v>129602004</v>
       </c>
       <c r="B57" t="n">
-        <v>80215</v>
+        <v>58106</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6734,37 +6724,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>103015</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555707</v>
+        <v>555738</v>
       </c>
       <c r="R57" t="n">
-        <v>7046194</v>
+        <v>7046093</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6791,19 +6785,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6818,57 +6802,61 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129601480</v>
+        <v>129600524</v>
       </c>
       <c r="B58" t="n">
-        <v>80186</v>
+        <v>98778</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555697</v>
+        <v>555564</v>
       </c>
       <c r="R58" t="n">
-        <v>7046157</v>
+        <v>7046096</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6927,52 +6915,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129600524</v>
+        <v>129602952</v>
       </c>
       <c r="B59" t="n">
-        <v>98774</v>
+        <v>91561</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>555564</v>
+        <v>555778</v>
       </c>
       <c r="R59" t="n">
-        <v>7046096</v>
+        <v>7045842</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6999,9 +6983,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7016,12 +7010,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7031,7 +7025,7 @@
         <v>129600317</v>
       </c>
       <c r="B60" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7125,10 +7119,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129602023</v>
+        <v>129600865</v>
       </c>
       <c r="B61" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7160,10 +7154,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555819</v>
+        <v>555679</v>
       </c>
       <c r="R61" t="n">
-        <v>7045946</v>
+        <v>7046243</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7195,7 +7189,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7205,7 +7199,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7232,10 +7226,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129600865</v>
+        <v>129602023</v>
       </c>
       <c r="B62" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7267,10 +7261,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555679</v>
+        <v>555819</v>
       </c>
       <c r="R62" t="n">
-        <v>7046243</v>
+        <v>7045946</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7302,7 +7296,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7312,7 +7306,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7342,7 +7336,7 @@
         <v>129602459</v>
       </c>
       <c r="B63" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7436,10 +7430,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129602004</v>
+        <v>129601061</v>
       </c>
       <c r="B64" t="n">
-        <v>58106</v>
+        <v>80215</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7447,41 +7441,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103015</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>555738</v>
+        <v>555707</v>
       </c>
       <c r="R64" t="n">
-        <v>7046093</v>
+        <v>7046194</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7508,9 +7498,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7525,12 +7525,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7540,7 +7540,7 @@
         <v>129601012</v>
       </c>
       <c r="B65" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7634,10 +7634,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129601936</v>
+        <v>129600977</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7645,21 +7645,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>555804</v>
+        <v>555704</v>
       </c>
       <c r="R66" t="n">
-        <v>7046004</v>
+        <v>7046202</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7729,22 +7729,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129600977</v>
+        <v>129601936</v>
       </c>
       <c r="B67" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7752,21 +7752,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>555704</v>
+        <v>555804</v>
       </c>
       <c r="R67" t="n">
-        <v>7046202</v>
+        <v>7046004</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7836,12 +7836,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -8072,7 +8072,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129601748</v>
+        <v>129601725</v>
       </c>
       <c r="B70" t="n">
         <v>80186</v>
@@ -8107,10 +8107,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>555703</v>
+        <v>555750</v>
       </c>
       <c r="R70" t="n">
-        <v>7046100</v>
+        <v>7046140</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8167,22 +8167,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129601725</v>
+        <v>129602553</v>
       </c>
       <c r="B71" t="n">
-        <v>80186</v>
+        <v>91895</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8190,21 +8190,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8214,13 +8214,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>555750</v>
+        <v>555844</v>
       </c>
       <c r="R71" t="n">
-        <v>7046140</v>
+        <v>7045852</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8247,19 +8247,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>13:49</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8274,22 +8264,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129602553</v>
+        <v>129601748</v>
       </c>
       <c r="B72" t="n">
-        <v>91891</v>
+        <v>80186</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8297,21 +8287,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8321,13 +8311,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>555844</v>
+        <v>555703</v>
       </c>
       <c r="R72" t="n">
-        <v>7045852</v>
+        <v>7046100</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8354,9 +8344,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8371,12 +8371,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8386,7 +8386,7 @@
         <v>129600733</v>
       </c>
       <c r="B73" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>129602304</v>
       </c>
       <c r="B74" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>129600581</v>
       </c>
       <c r="B75" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8721,52 +8721,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129602094</v>
+        <v>129602315</v>
       </c>
       <c r="B76" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>555852</v>
+        <v>555729</v>
       </c>
       <c r="R76" t="n">
-        <v>7045941</v>
+        <v>7045970</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8795,7 +8791,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8805,7 +8801,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8820,60 +8816,64 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129602315</v>
+        <v>129602094</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>555729</v>
+        <v>555852</v>
       </c>
       <c r="R77" t="n">
-        <v>7045970</v>
+        <v>7045941</v>
       </c>
       <c r="S77" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8927,12 +8927,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9056,48 +9056,52 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129600219</v>
+        <v>129602172</v>
       </c>
       <c r="B79" t="n">
-        <v>91593</v>
+        <v>98778</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>555572</v>
+        <v>555855</v>
       </c>
       <c r="R79" t="n">
-        <v>7046181</v>
+        <v>7045892</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9124,9 +9128,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9141,60 +9155,69 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129601548</v>
+        <v>129601945</v>
       </c>
       <c r="B80" t="n">
-        <v>80214</v>
+        <v>98778</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555707</v>
+        <v>555730</v>
       </c>
       <c r="R80" t="n">
-        <v>7046135</v>
+        <v>7046151</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9221,9 +9244,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9238,22 +9271,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129600975</v>
+        <v>129600219</v>
       </c>
       <c r="B81" t="n">
-        <v>80186</v>
+        <v>91597</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9261,37 +9294,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555633</v>
+        <v>555572</v>
       </c>
       <c r="R81" t="n">
-        <v>7046096</v>
+        <v>7046181</v>
       </c>
       <c r="S81" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9318,19 +9351,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>13:13</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9345,12 +9368,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9464,32 +9487,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129601148</v>
+        <v>129601548</v>
       </c>
       <c r="B83" t="n">
-        <v>80186</v>
+        <v>80214</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9499,13 +9522,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555654</v>
+        <v>555707</v>
       </c>
       <c r="R83" t="n">
-        <v>7046170</v>
+        <v>7046135</v>
       </c>
       <c r="S83" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9532,19 +9555,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>13:22</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9559,22 +9572,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129603240</v>
+        <v>129600975</v>
       </c>
       <c r="B84" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9582,42 +9595,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555865</v>
+        <v>555633</v>
       </c>
       <c r="R84" t="n">
-        <v>7045842</v>
+        <v>7046096</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9646,7 +9654,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9656,12 +9664,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9676,64 +9679,60 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129602172</v>
+        <v>129601148</v>
       </c>
       <c r="B85" t="n">
-        <v>98774</v>
+        <v>80186</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555855</v>
+        <v>555654</v>
       </c>
       <c r="R85" t="n">
-        <v>7045892</v>
+        <v>7046170</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9762,7 +9761,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9772,7 +9771,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9787,54 +9786,50 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129601945</v>
+        <v>129603240</v>
       </c>
       <c r="B86" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9843,13 +9838,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>555730</v>
+        <v>555865</v>
       </c>
       <c r="R86" t="n">
-        <v>7046151</v>
+        <v>7045842</v>
       </c>
       <c r="S86" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9878,7 +9873,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9888,7 +9883,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9903,22 +9903,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129600090</v>
+        <v>129602154</v>
       </c>
       <c r="B87" t="n">
-        <v>57736</v>
+        <v>91597</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9926,42 +9926,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>555491</v>
+        <v>555676</v>
       </c>
       <c r="R87" t="n">
-        <v>7046111</v>
+        <v>7045998</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9988,24 +9983,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10020,19 +10000,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129602108</v>
+        <v>129600090</v>
       </c>
       <c r="B88" t="n">
         <v>57736</v>
@@ -10068,14 +10048,14 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>555854</v>
+        <v>555491</v>
       </c>
       <c r="R88" t="n">
-        <v>7045940</v>
+        <v>7046111</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10107,7 +10087,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10117,12 +10097,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10137,22 +10117,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129602154</v>
+        <v>129602108</v>
       </c>
       <c r="B89" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10160,37 +10140,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>555676</v>
+        <v>555854</v>
       </c>
       <c r="R89" t="n">
-        <v>7045998</v>
+        <v>7045940</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10217,9 +10202,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10234,22 +10234,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129601612</v>
+        <v>129603549</v>
       </c>
       <c r="B90" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10290,10 +10290,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>555675</v>
+        <v>555865</v>
       </c>
       <c r="R90" t="n">
-        <v>7046143</v>
+        <v>7045842</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10335,7 +10335,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10362,10 +10362,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129603549</v>
+        <v>129601612</v>
       </c>
       <c r="B91" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10406,10 +10406,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>555865</v>
+        <v>555675</v>
       </c>
       <c r="R91" t="n">
-        <v>7045842</v>
+        <v>7046143</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10441,7 +10441,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10478,10 +10478,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129601760</v>
+        <v>129602716</v>
       </c>
       <c r="B92" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -10522,13 +10522,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>555694</v>
+        <v>555762</v>
       </c>
       <c r="R92" t="n">
-        <v>7046166</v>
+        <v>7045845</v>
       </c>
       <c r="S92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10594,10 +10594,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129602716</v>
+        <v>129601760</v>
       </c>
       <c r="B93" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -10638,13 +10638,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>555762</v>
+        <v>555694</v>
       </c>
       <c r="R93" t="n">
-        <v>7045845</v>
+        <v>7046166</v>
       </c>
       <c r="S93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10710,10 +10710,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129602047</v>
+        <v>129600756</v>
       </c>
       <c r="B94" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10721,21 +10721,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10745,13 +10745,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>555722</v>
+        <v>555626</v>
       </c>
       <c r="R94" t="n">
-        <v>7046017</v>
+        <v>7046163</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10778,19 +10778,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10805,22 +10795,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129600756</v>
+        <v>129602047</v>
       </c>
       <c r="B95" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10828,21 +10818,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10852,13 +10842,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>555626</v>
+        <v>555722</v>
       </c>
       <c r="R95" t="n">
-        <v>7046163</v>
+        <v>7046017</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10885,9 +10875,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10902,12 +10902,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -11021,38 +11021,42 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129602416</v>
+        <v>129602185</v>
       </c>
       <c r="B97" t="n">
-        <v>57736</v>
+        <v>98778</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -11061,13 +11065,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>555801</v>
+        <v>555729</v>
       </c>
       <c r="R97" t="n">
-        <v>7045860</v>
+        <v>7045984</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11094,14 +11098,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11116,54 +11125,50 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129602185</v>
+        <v>129602416</v>
       </c>
       <c r="B98" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -11172,13 +11177,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>555729</v>
+        <v>555801</v>
       </c>
       <c r="R98" t="n">
-        <v>7045984</v>
+        <v>7045860</v>
       </c>
       <c r="S98" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11205,19 +11210,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>14:07</t>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11232,22 +11232,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129602252</v>
+        <v>129600791</v>
       </c>
       <c r="B99" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11255,21 +11255,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11279,13 +11279,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>555848</v>
+        <v>555670</v>
       </c>
       <c r="R99" t="n">
-        <v>7045879</v>
+        <v>7046158</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11312,19 +11312,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11339,22 +11329,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129600791</v>
+        <v>129602252</v>
       </c>
       <c r="B100" t="n">
-        <v>80186</v>
+        <v>91597</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11362,21 +11352,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11386,13 +11376,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>555670</v>
+        <v>555848</v>
       </c>
       <c r="R100" t="n">
-        <v>7046158</v>
+        <v>7045879</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11419,9 +11409,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11436,12 +11436,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11682,45 +11682,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129600723</v>
+        <v>129601828</v>
       </c>
       <c r="B103" t="n">
-        <v>80186</v>
+        <v>91561</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>555572</v>
+        <v>555724</v>
       </c>
       <c r="R103" t="n">
-        <v>7046171</v>
+        <v>7046097</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -11779,7 +11779,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129600507</v>
+        <v>129600723</v>
       </c>
       <c r="B104" t="n">
         <v>80186</v>
@@ -11814,13 +11814,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>555608</v>
+        <v>555572</v>
       </c>
       <c r="R104" t="n">
-        <v>7046222</v>
+        <v>7046171</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11847,19 +11847,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11874,22 +11864,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129601607</v>
+        <v>129601709</v>
       </c>
       <c r="B105" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11897,37 +11887,42 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>555709</v>
+        <v>555739</v>
       </c>
       <c r="R105" t="n">
-        <v>7046133</v>
+        <v>7046139</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11954,9 +11949,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11971,22 +11981,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129602456</v>
+        <v>129600507</v>
       </c>
       <c r="B106" t="n">
-        <v>57733</v>
+        <v>80186</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11994,39 +12004,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>555809</v>
+        <v>555608</v>
       </c>
       <c r="R106" t="n">
-        <v>7045823</v>
+        <v>7046222</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12058,7 +12063,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12068,7 +12073,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12095,32 +12100,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129601828</v>
+        <v>129601607</v>
       </c>
       <c r="B107" t="n">
-        <v>91557</v>
+        <v>79081</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12130,10 +12135,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>555724</v>
+        <v>555709</v>
       </c>
       <c r="R107" t="n">
-        <v>7046097</v>
+        <v>7046133</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -12192,10 +12197,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129601709</v>
+        <v>129602456</v>
       </c>
       <c r="B108" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12203,16 +12208,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -12223,7 +12228,7 @@
       <c r="I108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -12232,10 +12237,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>555739</v>
+        <v>555809</v>
       </c>
       <c r="R108" t="n">
-        <v>7046139</v>
+        <v>7045823</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12267,7 +12272,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12277,12 +12282,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12309,10 +12309,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129602437</v>
+        <v>129600807</v>
       </c>
       <c r="B109" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12339,12 +12339,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -12353,10 +12348,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>555757</v>
+        <v>555633</v>
       </c>
       <c r="R109" t="n">
-        <v>7045907</v>
+        <v>7046097</v>
       </c>
       <c r="S109" t="n">
         <v>4</v>
@@ -12388,7 +12383,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12398,7 +12393,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12425,10 +12420,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129600807</v>
+        <v>129602437</v>
       </c>
       <c r="B110" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12455,7 +12450,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -12464,10 +12464,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>555633</v>
+        <v>555757</v>
       </c>
       <c r="R110" t="n">
-        <v>7046097</v>
+        <v>7045907</v>
       </c>
       <c r="S110" t="n">
         <v>4</v>
@@ -12499,7 +12499,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12539,7 +12539,7 @@
         <v>129601521</v>
       </c>
       <c r="B111" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12633,45 +12633,49 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129601528</v>
+        <v>129600022</v>
       </c>
       <c r="B112" t="n">
-        <v>91593</v>
+        <v>98778</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>555698</v>
+        <v>555560</v>
       </c>
       <c r="R112" t="n">
-        <v>7046140</v>
+        <v>7046091</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -12730,10 +12734,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129600022</v>
+        <v>129600513</v>
       </c>
       <c r="B113" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12763,19 +12767,24 @@
           <t>50</t>
         </is>
       </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>555560</v>
+        <v>555590</v>
       </c>
       <c r="R113" t="n">
-        <v>7046091</v>
+        <v>7046134</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12802,9 +12811,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12819,12 +12838,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -12834,7 +12853,7 @@
         <v>129601553</v>
       </c>
       <c r="B114" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12942,57 +12961,48 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129600513</v>
+        <v>129601528</v>
       </c>
       <c r="B115" t="n">
-        <v>98774</v>
+        <v>91597</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>555590</v>
+        <v>555698</v>
       </c>
       <c r="R115" t="n">
-        <v>7046134</v>
+        <v>7046140</v>
       </c>
       <c r="S115" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13019,19 +13029,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>12:55</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13046,61 +13046,57 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129602025</v>
+        <v>129600727</v>
       </c>
       <c r="B116" t="n">
-        <v>98774</v>
+        <v>80215</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>555739</v>
+        <v>555605</v>
       </c>
       <c r="R116" t="n">
-        <v>7046093</v>
+        <v>7046222</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -13159,45 +13155,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129600727</v>
+        <v>129600845</v>
       </c>
       <c r="B117" t="n">
-        <v>80215</v>
+        <v>80186</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>555605</v>
+        <v>555681</v>
       </c>
       <c r="R117" t="n">
-        <v>7046222</v>
+        <v>7046162</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13256,48 +13252,52 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129602472</v>
+        <v>129602025</v>
       </c>
       <c r="B118" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>555806</v>
+        <v>555739</v>
       </c>
       <c r="R118" t="n">
-        <v>7045826</v>
+        <v>7046093</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13324,19 +13324,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>14:29</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13351,22 +13341,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129600845</v>
+        <v>129602472</v>
       </c>
       <c r="B119" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13374,21 +13364,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13398,13 +13388,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>555681</v>
+        <v>555806</v>
       </c>
       <c r="R119" t="n">
-        <v>7046162</v>
+        <v>7045826</v>
       </c>
       <c r="S119" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13431,9 +13421,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13448,22 +13448,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129602058</v>
+        <v>129602598</v>
       </c>
       <c r="B120" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13471,21 +13471,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13495,13 +13495,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>555829</v>
+        <v>555768</v>
       </c>
       <c r="R120" t="n">
-        <v>7045930</v>
+        <v>7045841</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13540,7 +13540,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13555,22 +13555,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129602598</v>
+        <v>129602058</v>
       </c>
       <c r="B121" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13578,21 +13578,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13602,13 +13602,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>555768</v>
+        <v>555829</v>
       </c>
       <c r="R121" t="n">
-        <v>7045841</v>
+        <v>7045930</v>
       </c>
       <c r="S121" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13662,12 +13662,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -14018,7 +14018,7 @@
         <v>129601920</v>
       </c>
       <c r="B125" t="n">
-        <v>92076</v>
+        <v>92080</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/A 41372-2025 artfynd.xlsx
+++ b/artfynd/A 41372-2025 artfynd.xlsx
@@ -3830,53 +3830,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129602543</v>
+        <v>129601128</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555769</v>
+        <v>555698</v>
       </c>
       <c r="R30" t="n">
-        <v>7045881</v>
+        <v>7046187</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3903,24 +3898,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3935,12 +3915,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4054,48 +4034,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129601128</v>
+        <v>129602543</v>
       </c>
       <c r="B32" t="n">
-        <v>80215</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555698</v>
+        <v>555769</v>
       </c>
       <c r="R32" t="n">
-        <v>7046187</v>
+        <v>7045881</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4122,9 +4107,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4139,22 +4139,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129602260</v>
+        <v>129600015</v>
       </c>
       <c r="B33" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4181,22 +4181,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>555747</v>
+        <v>555553</v>
       </c>
       <c r="R33" t="n">
-        <v>7045963</v>
+        <v>7046074</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4223,9 +4228,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4240,22 +4255,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129600015</v>
+        <v>129602260</v>
       </c>
       <c r="B34" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4282,27 +4297,22 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>555553</v>
+        <v>555747</v>
       </c>
       <c r="R34" t="n">
-        <v>7046074</v>
+        <v>7045963</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4329,19 +4339,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4356,12 +4356,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4371,7 +4371,7 @@
         <v>129602488</v>
       </c>
       <c r="B35" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4465,10 +4465,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129602548</v>
+        <v>129601775</v>
       </c>
       <c r="B36" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4495,12 +4495,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4509,13 +4504,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>555770</v>
+        <v>555746</v>
       </c>
       <c r="R36" t="n">
-        <v>7045888</v>
+        <v>7046137</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4544,7 +4539,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4554,7 +4549,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4569,22 +4564,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129601775</v>
+        <v>129602548</v>
       </c>
       <c r="B37" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4611,7 +4606,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4620,13 +4620,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>555746</v>
+        <v>555770</v>
       </c>
       <c r="R37" t="n">
-        <v>7046137</v>
+        <v>7045888</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4680,44 +4680,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129601485</v>
+        <v>129602638</v>
       </c>
       <c r="B38" t="n">
-        <v>80215</v>
+        <v>91897</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4727,10 +4727,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>555696</v>
+        <v>555826</v>
       </c>
       <c r="R38" t="n">
-        <v>7046160</v>
+        <v>7045880</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4789,10 +4789,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129602219</v>
+        <v>129601909</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4800,37 +4800,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>555697</v>
+        <v>555726</v>
       </c>
       <c r="R39" t="n">
-        <v>7045963</v>
+        <v>7046072</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4857,9 +4862,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4874,22 +4894,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129602638</v>
+        <v>129601980</v>
       </c>
       <c r="B40" t="n">
-        <v>91895</v>
+        <v>91599</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4897,21 +4917,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4921,10 +4941,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>555826</v>
+        <v>555724</v>
       </c>
       <c r="R40" t="n">
-        <v>7045880</v>
+        <v>7046089</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4983,10 +5003,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129601980</v>
+        <v>129602219</v>
       </c>
       <c r="B41" t="n">
-        <v>91597</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4994,21 +5014,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5018,10 +5038,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>555724</v>
+        <v>555697</v>
       </c>
       <c r="R41" t="n">
-        <v>7046089</v>
+        <v>7045963</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5080,53 +5100,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129601909</v>
+        <v>129601485</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>80215</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>555726</v>
+        <v>555696</v>
       </c>
       <c r="R42" t="n">
-        <v>7046072</v>
+        <v>7046160</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5153,24 +5168,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5185,12 +5185,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5321,7 +5321,7 @@
         <v>129602321</v>
       </c>
       <c r="B44" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>129600463</v>
       </c>
       <c r="B45" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5749,49 +5749,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129602134</v>
+        <v>129601971</v>
       </c>
       <c r="B48" t="n">
-        <v>98778</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>555825</v>
+        <v>555791</v>
       </c>
       <c r="R48" t="n">
-        <v>7045910</v>
+        <v>7045965</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5823,7 +5819,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5833,7 +5829,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5863,7 +5859,7 @@
         <v>129603244</v>
       </c>
       <c r="B49" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5971,45 +5967,49 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129601971</v>
+        <v>129602134</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>555791</v>
+        <v>555825</v>
       </c>
       <c r="R50" t="n">
-        <v>7045965</v>
+        <v>7045910</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6041,7 +6041,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6078,57 +6078,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129601611</v>
+        <v>129600512</v>
       </c>
       <c r="B51" t="n">
-        <v>98778</v>
+        <v>57736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>555687</v>
+        <v>555592</v>
       </c>
       <c r="R51" t="n">
-        <v>7046167</v>
+        <v>7046249</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6157,7 +6153,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6167,7 +6163,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6182,12 +6183,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6291,53 +6292,57 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129600512</v>
+        <v>129601611</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>555592</v>
+        <v>555687</v>
       </c>
       <c r="R53" t="n">
-        <v>7046249</v>
+        <v>7046167</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6366,7 +6371,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6376,12 +6381,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6396,12 +6396,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6518,7 +6518,7 @@
         <v>129600692</v>
       </c>
       <c r="B55" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6616,10 +6616,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129601480</v>
+        <v>129602023</v>
       </c>
       <c r="B56" t="n">
-        <v>80186</v>
+        <v>91599</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6627,21 +6627,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6651,13 +6651,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>555697</v>
+        <v>555819</v>
       </c>
       <c r="R56" t="n">
-        <v>7046157</v>
+        <v>7045946</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6684,9 +6684,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6701,61 +6711,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129602004</v>
+        <v>129602459</v>
       </c>
       <c r="B57" t="n">
-        <v>58106</v>
+        <v>91599</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>555738</v>
+        <v>555835</v>
       </c>
       <c r="R57" t="n">
-        <v>7046093</v>
+        <v>7045881</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6814,52 +6820,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129600524</v>
+        <v>129602952</v>
       </c>
       <c r="B58" t="n">
-        <v>98778</v>
+        <v>91563</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>555564</v>
+        <v>555778</v>
       </c>
       <c r="R58" t="n">
-        <v>7046096</v>
+        <v>7045842</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6886,9 +6888,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6903,44 +6915,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129602952</v>
+        <v>129600865</v>
       </c>
       <c r="B59" t="n">
-        <v>91561</v>
+        <v>91599</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6950,10 +6962,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>555778</v>
+        <v>555679</v>
       </c>
       <c r="R59" t="n">
-        <v>7045842</v>
+        <v>7046243</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6985,7 +6997,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6995,7 +7007,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7025,7 +7037,7 @@
         <v>129600317</v>
       </c>
       <c r="B60" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7119,10 +7131,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129600865</v>
+        <v>129601480</v>
       </c>
       <c r="B61" t="n">
-        <v>91597</v>
+        <v>80186</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7130,21 +7142,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7154,13 +7166,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>555679</v>
+        <v>555697</v>
       </c>
       <c r="R61" t="n">
-        <v>7046243</v>
+        <v>7046157</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7187,19 +7199,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7214,44 +7216,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129602023</v>
+        <v>129601061</v>
       </c>
       <c r="B62" t="n">
-        <v>91597</v>
+        <v>80215</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7261,10 +7263,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>555819</v>
+        <v>555707</v>
       </c>
       <c r="R62" t="n">
-        <v>7045946</v>
+        <v>7046194</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7296,7 +7298,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7306,7 +7308,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7321,57 +7323,61 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129602459</v>
+        <v>129602004</v>
       </c>
       <c r="B63" t="n">
-        <v>91597</v>
+        <v>58106</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>555835</v>
+        <v>555738</v>
       </c>
       <c r="R63" t="n">
-        <v>7045881</v>
+        <v>7046093</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7430,48 +7436,52 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129601061</v>
+        <v>129600524</v>
       </c>
       <c r="B64" t="n">
-        <v>80215</v>
+        <v>98780</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>555707</v>
+        <v>555564</v>
       </c>
       <c r="R64" t="n">
-        <v>7046194</v>
+        <v>7046096</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7498,19 +7508,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7525,22 +7525,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129601012</v>
+        <v>129602371</v>
       </c>
       <c r="B65" t="n">
-        <v>91597</v>
+        <v>57736</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7548,37 +7548,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>555680</v>
+        <v>555825</v>
       </c>
       <c r="R65" t="n">
-        <v>7046211</v>
+        <v>7045806</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7605,9 +7610,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7622,22 +7642,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129600977</v>
+        <v>129601541</v>
       </c>
       <c r="B66" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7645,37 +7665,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>555704</v>
+        <v>555702</v>
       </c>
       <c r="R66" t="n">
-        <v>7046202</v>
+        <v>7046142</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7702,19 +7727,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:13</t>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack, gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7729,22 +7749,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129601936</v>
+        <v>129601012</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7752,21 +7772,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7776,13 +7796,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>555804</v>
+        <v>555680</v>
       </c>
       <c r="R67" t="n">
-        <v>7046004</v>
+        <v>7046211</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7809,19 +7829,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7836,22 +7846,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129602371</v>
+        <v>129601936</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7859,39 +7869,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>555825</v>
+        <v>555804</v>
       </c>
       <c r="R68" t="n">
-        <v>7045806</v>
+        <v>7046004</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7923,7 +7928,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7933,12 +7938,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7965,10 +7965,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129601541</v>
+        <v>129600977</v>
       </c>
       <c r="B69" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7976,42 +7976,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>555702</v>
+        <v>555704</v>
       </c>
       <c r="R69" t="n">
-        <v>7046142</v>
+        <v>7046202</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8038,14 +8033,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack, gran</t>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8060,19 +8060,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129601725</v>
+        <v>129601748</v>
       </c>
       <c r="B70" t="n">
         <v>80186</v>
@@ -8107,10 +8107,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>555750</v>
+        <v>555703</v>
       </c>
       <c r="R70" t="n">
-        <v>7046140</v>
+        <v>7046100</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8167,12 +8167,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8182,7 +8182,7 @@
         <v>129602553</v>
       </c>
       <c r="B71" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129601748</v>
+        <v>129601725</v>
       </c>
       <c r="B72" t="n">
         <v>80186</v>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>555703</v>
+        <v>555750</v>
       </c>
       <c r="R72" t="n">
-        <v>7046100</v>
+        <v>7046140</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8371,22 +8371,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129600733</v>
+        <v>129602304</v>
       </c>
       <c r="B73" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8413,24 +8413,19 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>555649</v>
+        <v>555857</v>
       </c>
       <c r="R73" t="n">
-        <v>7046243</v>
+        <v>7045866</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8462,7 +8457,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8472,7 +8467,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8487,22 +8482,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129602304</v>
+        <v>129600733</v>
       </c>
       <c r="B74" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8529,19 +8524,24 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>555857</v>
+        <v>555649</v>
       </c>
       <c r="R74" t="n">
-        <v>7045866</v>
+        <v>7046243</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8598,12 +8598,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8613,7 +8613,7 @@
         <v>129600581</v>
       </c>
       <c r="B75" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8828,37 +8828,38 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129602094</v>
+        <v>129601872</v>
       </c>
       <c r="B77" t="n">
-        <v>98778</v>
+        <v>57736</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8867,10 +8868,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>555852</v>
+        <v>555721</v>
       </c>
       <c r="R77" t="n">
-        <v>7045941</v>
+        <v>7046072</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8902,7 +8903,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8912,7 +8913,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8927,50 +8933,49 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129601872</v>
+        <v>129602094</v>
       </c>
       <c r="B78" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8979,10 +8984,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>555721</v>
+        <v>555852</v>
       </c>
       <c r="R78" t="n">
-        <v>7046072</v>
+        <v>7045941</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9014,7 +9019,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9024,12 +9029,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9044,64 +9044,60 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129602172</v>
+        <v>129600219</v>
       </c>
       <c r="B79" t="n">
-        <v>98778</v>
+        <v>91599</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>555855</v>
+        <v>555572</v>
       </c>
       <c r="R79" t="n">
-        <v>7045892</v>
+        <v>7046181</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9128,19 +9124,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9155,69 +9141,60 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129601945</v>
+        <v>129601548</v>
       </c>
       <c r="B80" t="n">
-        <v>98778</v>
+        <v>80214</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>555730</v>
+        <v>555707</v>
       </c>
       <c r="R80" t="n">
-        <v>7046151</v>
+        <v>7046135</v>
       </c>
       <c r="S80" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9244,19 +9221,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>13:53</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9271,22 +9238,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129600219</v>
+        <v>129600975</v>
       </c>
       <c r="B81" t="n">
-        <v>91597</v>
+        <v>80186</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9294,37 +9261,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>555572</v>
+        <v>555633</v>
       </c>
       <c r="R81" t="n">
-        <v>7046181</v>
+        <v>7046096</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9351,9 +9318,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9368,12 +9345,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9487,32 +9464,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129601548</v>
+        <v>129601148</v>
       </c>
       <c r="B83" t="n">
-        <v>80214</v>
+        <v>80186</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9522,13 +9499,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>555707</v>
+        <v>555654</v>
       </c>
       <c r="R83" t="n">
-        <v>7046135</v>
+        <v>7046170</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9555,9 +9532,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9572,22 +9559,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129600975</v>
+        <v>129603240</v>
       </c>
       <c r="B84" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9595,37 +9582,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>555633</v>
+        <v>555865</v>
       </c>
       <c r="R84" t="n">
-        <v>7046096</v>
+        <v>7045842</v>
       </c>
       <c r="S84" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9654,7 +9646,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9664,7 +9656,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9679,60 +9676,64 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129601148</v>
+        <v>129602172</v>
       </c>
       <c r="B85" t="n">
-        <v>80186</v>
+        <v>98780</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>555654</v>
+        <v>555855</v>
       </c>
       <c r="R85" t="n">
-        <v>7046170</v>
+        <v>7045892</v>
       </c>
       <c r="S85" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9761,7 +9762,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9771,7 +9772,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9786,50 +9787,54 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129603240</v>
+        <v>129601945</v>
       </c>
       <c r="B86" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9838,13 +9843,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>555865</v>
+        <v>555730</v>
       </c>
       <c r="R86" t="n">
-        <v>7045842</v>
+        <v>7046151</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9873,7 +9878,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9883,12 +9888,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9903,60 +9903,69 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129602154</v>
+        <v>129602716</v>
       </c>
       <c r="B87" t="n">
-        <v>91597</v>
+        <v>98780</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>555676</v>
+        <v>555762</v>
       </c>
       <c r="R87" t="n">
-        <v>7045998</v>
+        <v>7045845</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9983,9 +9992,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10000,62 +10019,66 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129600090</v>
+        <v>129601612</v>
       </c>
       <c r="B88" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>555491</v>
+        <v>555675</v>
       </c>
       <c r="R88" t="n">
-        <v>7046111</v>
+        <v>7046143</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10087,7 +10110,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10097,12 +10120,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10129,38 +10147,42 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129602108</v>
+        <v>129603549</v>
       </c>
       <c r="B89" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10169,10 +10191,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>555854</v>
+        <v>555865</v>
       </c>
       <c r="R89" t="n">
-        <v>7045940</v>
+        <v>7045842</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10204,7 +10226,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10214,12 +10236,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10234,22 +10251,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129603549</v>
+        <v>129601760</v>
       </c>
       <c r="B90" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10276,7 +10293,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10290,13 +10307,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>555865</v>
+        <v>555694</v>
       </c>
       <c r="R90" t="n">
-        <v>7045842</v>
+        <v>7046166</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10325,7 +10342,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10335,7 +10352,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10350,66 +10367,62 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Peter von Troil</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129601612</v>
+        <v>129600090</v>
       </c>
       <c r="B91" t="n">
-        <v>98778</v>
+        <v>57736</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>555675</v>
+        <v>555491</v>
       </c>
       <c r="R91" t="n">
-        <v>7046143</v>
+        <v>7046111</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10441,7 +10454,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10451,7 +10464,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10478,57 +10496,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129602716</v>
+        <v>129602154</v>
       </c>
       <c r="B92" t="n">
-        <v>98778</v>
+        <v>91599</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>555762</v>
+        <v>555676</v>
       </c>
       <c r="R92" t="n">
-        <v>7045845</v>
+        <v>7045998</v>
       </c>
       <c r="S92" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10555,19 +10564,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10582,54 +10581,50 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129601760</v>
+        <v>129602108</v>
       </c>
       <c r="B93" t="n">
-        <v>98778</v>
+        <v>57736</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10638,13 +10633,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>555694</v>
+        <v>555854</v>
       </c>
       <c r="R93" t="n">
-        <v>7046166</v>
+        <v>7045940</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10673,7 +10668,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10683,7 +10678,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10698,22 +10698,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129600756</v>
+        <v>129602047</v>
       </c>
       <c r="B94" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10721,21 +10721,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10745,13 +10745,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>555626</v>
+        <v>555722</v>
       </c>
       <c r="R94" t="n">
-        <v>7046163</v>
+        <v>7046017</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10778,9 +10778,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10795,19 +10805,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129602047</v>
+        <v>129600095</v>
       </c>
       <c r="B95" t="n">
         <v>79081</v>
@@ -10838,14 +10848,14 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Grössjöberget, Grössjöberget, Ång</t>
+          <t>Ålhusberget, Ålhusberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>555722</v>
+        <v>555473</v>
       </c>
       <c r="R95" t="n">
-        <v>7046017</v>
+        <v>7046098</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10877,7 +10887,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10887,7 +10897,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10902,22 +10912,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129600095</v>
+        <v>129600756</v>
       </c>
       <c r="B96" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10925,37 +10935,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Ålhusberget, Ålhusberget, Ång</t>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>555473</v>
+        <v>555626</v>
       </c>
       <c r="R96" t="n">
-        <v>7046098</v>
+        <v>7046163</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10982,19 +10992,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>12:36</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>12:36</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11009,54 +11009,50 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129602185</v>
+        <v>129602416</v>
       </c>
       <c r="B97" t="n">
-        <v>98778</v>
+        <v>57736</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -11065,13 +11061,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>555729</v>
+        <v>555801</v>
       </c>
       <c r="R97" t="n">
-        <v>7045984</v>
+        <v>7045860</v>
       </c>
       <c r="S97" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11098,19 +11094,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>14:07</t>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11125,50 +11116,54 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Peter von Troil</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129602416</v>
+        <v>129602185</v>
       </c>
       <c r="B98" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -11177,13 